--- a/xlsx/hw5.xlsx
+++ b/xlsx/hw5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keith\source\repos\xlladdins\xll_ml\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E73522-289B-4D7D-8FBB-81A9149DA706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCAE566-A9F2-441B-86DB-F04CCA4FE5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13996" activeTab="1" xr2:uid="{5E38A752-04D7-4C78-952F-E31FCF3159F7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13996" activeTab="2" xr2:uid="{5E38A752-04D7-4C78-952F-E31FCF3159F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Elementary" sheetId="1" r:id="rId1"/>
@@ -610,3451 +610,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Simulation!$C$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>B_</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Simulation!$B$10:$B$72</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.0000000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.0000000000000002E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.2E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.6E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.4E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.8000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.2000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.6000000000000004E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.3999999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4.8000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5.2000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5.6000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6.4000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6.8000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7.2000000000000008E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.5999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>8.4000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>8.7999999999999995E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>9.1999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>9.6000000000000002E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.10400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.108</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.112</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.11600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.124</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.128</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.13200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.13600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.14000000000000001</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.14400000000000002</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.14799999999999999</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.152</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.156</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.16</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.16400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.16800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.17200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.17599999999999999</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.184</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.188</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.192</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.19600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.20400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.20800000000000002</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.21199999999999999</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.216</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.22</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.224</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.22800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.23200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.23600000000000002</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.24</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.24399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.248</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Simulation!$C$10:$C$72</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.2089576551553746E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.2817260497733744E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-3.1951730483285035E-3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.10787987527032183</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.10648555722598418</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.11091546145198063</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.17072663836317631</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.19605995490899578</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.19112609286611534</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.24587537237107607</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.25487440997103938</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.27630031710585445</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.31132305629372864</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.37324050506127127</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.35415252345245807</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.5161568190806769</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.51734446621196939</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.47751968217527263</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.48211368867873877</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.48740210154083191</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.45905365800037878</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.42893998765311886</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.54688048000656653</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.57718958712773238</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.49128049548836805</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.53969718813836931</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.46490717595721726</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.46229450136284828</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.4331895013841775</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.5251928318102389</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.50681037343756852</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.44712508188580213</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.46946742433312155</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.44388229787344613</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.61659233353201059</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.67890796267445475</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.67658447398497079</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.68229123567249228</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.59885606217113718</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.69351148281152941</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.66568800991491428</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.62935490331474286</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.60957847243184127</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.62700674757993413</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.64132511897383726</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.65782831248675533</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.64235078789571765</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.662384765376407</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.73119859294068623</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.79290798755025516</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.78282330367305986</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.71992655556273177</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.77959706827084396</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.78364741119686943</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.78852309851795421</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.82432001732875915</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.66729348735168936</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.7662468424471256</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.8004005467730847</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.79221234774450988</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.78814415576952479</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.78714587266686697</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0BBA-4CEB-9F25-45B1CDADE32E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Simulation!$D$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>R_</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Simulation!$B$10:$B$72</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.0000000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.0000000000000002E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.2E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.6E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.4E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.8000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.2000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.6000000000000004E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.3999999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4.8000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5.2000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5.6000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6.4000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6.8000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7.2000000000000008E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.5999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>8.4000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>8.7999999999999995E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>9.1999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>9.6000000000000002E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.10400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.108</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.112</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.11600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.124</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.128</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.13200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.13600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.14000000000000001</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.14400000000000002</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.14799999999999999</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.152</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.156</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.16</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.16400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.16800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.17200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.17599999999999999</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.184</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.188</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.192</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.19600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.20400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.20800000000000002</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.21199999999999999</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.216</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.22</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.224</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.22800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.23200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.23600000000000002</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.24</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.24399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.248</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Simulation!$D$10:$D$72</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0BBA-4CEB-9F25-45B1CDADE32E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Simulation!$G$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>N</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Simulation!$B$10:$B$72</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.0000000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.0000000000000002E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.2E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.6E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.4E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.8000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.2000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.6000000000000004E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.3999999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4.8000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5.2000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5.6000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6.4000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6.8000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7.2000000000000008E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.5999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>8.4000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>8.7999999999999995E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>9.1999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>9.6000000000000002E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.10400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.108</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.112</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.11600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.124</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.128</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.13200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.13600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.14000000000000001</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.14400000000000002</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.14799999999999999</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.152</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.156</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.16</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.16400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.16800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.17200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.17599999999999999</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.184</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.188</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.192</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.19600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.20400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.20800000000000002</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.21199999999999999</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.216</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.22</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.224</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.22800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.23200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.23600000000000002</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.24</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.24399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.248</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Simulation!$G$10:$G$72</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="63"/>
-                <c:pt idx="0">
-                  <c:v>-0.48006119416162751</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.1183245928421153E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-1.5630828917487183E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-2.9627071117111936E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8.9817035300763848E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-8.6788758552319711E-4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.8371821631886793E-3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.8067140347521853E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2.0434938681452131E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-2.9192088230024504E-3</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4.2661298618480892E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7.9345362962651156E-3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.7009603557336217E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2.62165529395606E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4.217086699102901E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>-1.0034653164481655E-2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>8.9539301010200856E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2.6697278178560713E-3</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-1.6046039796756617E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>4.500672361136826E-3</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>4.8407041283230479E-3</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>-1.142207339403073E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>-1.3435096911645683E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>5.7265326198289668E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1.3202786124157539E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>-3.1335093979545203E-2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2.272448666186605E-2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>-2.9674730702079433E-2</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1.5940173918307932E-3</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>-1.1973012539879313E-2</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>4.5129441532622161E-2</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>-4.3689952241133811E-3</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>-2.3957614318918186E-2</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1.4049851690700776E-2</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>-8.9064222971892426E-3</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>6.3258071146853223E-2</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1.3093858499386934E-2</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1.3728890275054861E-3</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2.3869226940715915E-3</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>-1.1316727701769724E-2</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1.5558248761982141E-2</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>-1.3782317811195655E-3</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>-2.651912840507864E-3</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>-7.2975839770689221E-4</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>4.1357617728178253E-3</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>3.0821017018252683E-3</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2.6426533779264072E-3</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2.402109798330665E-4</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2.1951796816402913E-3</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2.5057889595631044E-3</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>7.6442275416133132E-4</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>7.7459112652944473E-5</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>-1.2543450409330248E-4</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>2.5355368213780816E-4</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>2.9614984785597542E-5</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1.2096397129124359E-5</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>4.1360811772195305E-6</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>-6.2001238569919792E-6</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>6.4887856552897638E-6</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>1.4116335600444785E-8</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>2.399530574237474E-11</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>7.2164496600635175E-15</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-0BBA-4CEB-9F25-45B1CDADE32E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="7"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Simulation!$J$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>V</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Simulation!$B$10:$B$72</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.0000000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.0000000000000002E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.2E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.6E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.4E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.8000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.2000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.6000000000000004E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.3999999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4.8000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5.2000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5.6000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6.4000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6.8000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7.2000000000000008E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.5999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>8.4000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>8.7999999999999995E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>9.1999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>9.6000000000000002E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.10400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.108</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.112</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.11600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.124</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.128</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.13200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.13600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.14000000000000001</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.14400000000000002</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.14799999999999999</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.152</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.156</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.16</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.16400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.16800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.17200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.17599999999999999</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.184</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.188</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.192</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.19600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.20400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.20800000000000002</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.21199999999999999</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.216</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.22</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.224</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.22800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.23200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.23600000000000002</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.24</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.24399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.248</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Simulation!$J$10:$J$72</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="63"/>
-                <c:pt idx="0">
-                  <c:v>3.987761167674492</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.4889038412130162</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.6630303411861931</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.9949420298187803</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.9123106273980568</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.9267627070595736</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.8942257023917222</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.4161779972196484</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2.2387056190069501</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2.2744813978623384</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.9048394816493825</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.8536936255531238</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.731778806236612</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.5423835315481575</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.2371188199090106</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1.3165735686164162</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.61289525916570398</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.61097160583581456</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.70645617288205109</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.69505706528194366</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.68224258630844048</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.75436968477084676</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.83807804348919746</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.4780441146081138</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.42333021935716264</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.55502153063301485</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.44874550131482138</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.57700911545074263</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.5840656428627149</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.65192394471958082</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.41584614597898373</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.44585490867273059</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.54686090029077228</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.49862244694543456</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.54774690982476493</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.18314526400801423</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.13795073492425924</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.1391361273832965</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.13699219491761849</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.16606182541001102</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.10914467529719118</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.11627218161501496</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.12663735691887523</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.13350548640236304</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.12743055853593699</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.12375201567204841</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.12060947766544072</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.12275590002365067</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.12020772359768273</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.11468953229835124</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.11324412771602875</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.11330567324249768</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.11356100794393292</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.11314998777612861</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.11314606521304393</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.11314434062136085</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.11314066452649721</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.11314176632386945</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.11312704057593874</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.11312702946327456</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.11312702946808614</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.11312702946808689</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-0BBA-4CEB-9F25-45B1CDADE32E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="8"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Simulation!$K$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>A</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Simulation!$B$10:$B$72</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.0000000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.0000000000000002E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.2E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.6E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.4E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.8000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.2000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.6000000000000004E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.3999999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4.8000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5.2000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5.6000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6.4000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6.8000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7.2000000000000008E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.5999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>8.4000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>8.7999999999999995E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>9.1999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>9.6000000000000002E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.10400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.108</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.112</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.11600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.124</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.128</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.13200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.13600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.14000000000000001</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.14400000000000002</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.14799999999999999</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.152</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.156</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.16</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.16400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.16800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.17200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.17599999999999999</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.184</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.188</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.192</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.19600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.20400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.20800000000000002</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.21199999999999999</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.216</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.22</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.224</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.22800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.23200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.23600000000000002</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.24</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.24399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.248</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Simulation!$K$10:$K$72</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
-                <c:pt idx="0">
-                  <c:v>-3.987761167674492</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.11312702946808689</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-0BBA-4CEB-9F25-45B1CDADE32E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="9"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Simulation!$L$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>intrinsic</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Simulation!$B$10:$B$72</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.0000000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.0000000000000002E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.2E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.6E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.4E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.8000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.2000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.6000000000000004E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.3999999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4.8000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5.2000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5.6000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6.4000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6.8000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7.2000000000000008E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.5999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>8.4000000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>8.7999999999999995E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>9.1999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>9.6000000000000002E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.10400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.108</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.112</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.11600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.124</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.128</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.13200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.13600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.14000000000000001</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.14400000000000002</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.14799999999999999</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.152</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.156</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.16</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.16400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.16800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.17200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.17599999999999999</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.184</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.188</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.192</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.19600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.20400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.20800000000000002</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.21199999999999999</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.216</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.22</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.224</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.22800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.23200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.23600000000000002</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.24</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.24399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.248</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Simulation!$L$10:$L$72</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.786483719237026E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-0BBA-4CEB-9F25-45B1CDADE32E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="933509279"/>
-        <c:axId val="933508799"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="933509279"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="933508799"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="933508799"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="933509279"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>419099</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>666749</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>42863</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D34F078-D460-E079-092D-9E09E3F45727}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4436,18 +991,18 @@
       </c>
       <c r="D4">
         <f ca="1">RAND()</f>
-        <v>0.94093689632341027</v>
+        <v>0.50705860915592771</v>
       </c>
       <c r="E4">
         <f ca="1">-F4*D4</f>
-        <v>-2.8228106889702307</v>
+        <v>-1.5211758274677831</v>
       </c>
       <c r="F4" s="20">
         <v>3</v>
       </c>
       <c r="G4">
         <f ca="1">E4</f>
-        <v>-2.8228106889702307</v>
+        <v>-1.5211758274677831</v>
       </c>
       <c r="H4">
         <f>F4</f>
@@ -4471,11 +1026,11 @@
       </c>
       <c r="D5">
         <f ca="1">RAND()</f>
-        <v>0.47974202563498158</v>
+        <v>0.18183783962827582</v>
       </c>
       <c r="E5">
         <f ca="1">-E4</f>
-        <v>2.8228106889702307</v>
+        <v>1.5211758274677831</v>
       </c>
       <c r="F5" s="21">
         <f>-F4</f>
@@ -4495,11 +1050,11 @@
       </c>
       <c r="J5">
         <f ca="1">-SUMPRODUCT(E5:F5,C5:D5)</f>
-        <v>-1.3835846120652859</v>
+        <v>-0.97566230858295566</v>
       </c>
       <c r="K5">
         <f ca="1">F4*(D5-D4)</f>
-        <v>-1.3835846120652859</v>
+        <v>-0.97566230858295566</v>
       </c>
       <c r="L5" s="6">
         <f ca="1">J5-K5</f>
@@ -4532,7 +1087,7 @@
     <row r="1" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="18" cm="1">
         <f t="array" aca="1" ref="B1" ca="1">_xll.MONTE.COUNT()</f>
-        <v>30423</v>
+        <v>10441</v>
       </c>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -4582,7 +1137,7 @@
       </c>
       <c r="G3" s="8" cm="1">
         <f t="array" aca="1" ref="G3" ca="1">_xlfn.TAKE(S_,-1)</f>
-        <v>116.47065589180895</v>
+        <v>106.19284045436892</v>
       </c>
       <c r="N3" s="7">
         <v>1</v>
@@ -4612,11 +1167,11 @@
       </c>
       <c r="H4" s="11">
         <f t="array" aca="1" ref="H4:I4" ca="1">_xll.MONTE.STDEV(G4)</f>
-        <v>3.9575119032771537</v>
+        <v>3.940636698271593</v>
       </c>
       <c r="I4" s="11">
         <f ca="1"/>
-        <v>5.4631643688741045</v>
+        <v>5.4540603594786763</v>
       </c>
       <c r="M4">
         <v>1E-3</v>
@@ -4643,7 +1198,7 @@
       </c>
       <c r="G5" s="11" cm="1">
         <f t="array" aca="1" ref="G5" ca="1">_xlfn.TAKE(A,-1)</f>
-        <v>0.11312702946808689</v>
+        <v>5.9557150775633221E-2</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
@@ -4673,19 +1228,19 @@
       </c>
       <c r="G6" s="11">
         <f ca="1">payoff-hedge</f>
-        <v>-0.11312702946808689</v>
+        <v>-5.9557150775633221E-2</v>
       </c>
       <c r="H6" s="8">
         <f t="array" aca="1" ref="H6:I6" ca="1">_xll.MONTE.STDEV(error)</f>
-        <v>-1.7636457908396786E-2</v>
+        <v>-1.4968078938005986E-2</v>
       </c>
       <c r="I6" s="13">
         <f ca="1"/>
-        <v>0.43896459953411276</v>
+        <v>0.43658700690594882</v>
       </c>
       <c r="J6" s="17">
         <f ca="1">I6/put</f>
-        <v>0.11007795629598849</v>
+        <v>0.10948173387237969</v>
       </c>
       <c r="K6" s="16" t="s">
         <v>30</v>
@@ -4817,7 +1372,7 @@
       </c>
       <c r="C11">
         <f ca="1"/>
-        <v>5.2089576551553746E-2</v>
+        <v>1.0570239487426679E-2</v>
       </c>
       <c r="D11">
         <f ca="1"/>
@@ -4825,27 +1380,27 @@
       </c>
       <c r="E11" s="12">
         <f ca="1"/>
-        <v>101.03915361734803</v>
+        <v>100.20361179762185</v>
       </c>
       <c r="F11" s="11">
         <f ca="1"/>
-        <v>-4.161120311822768</v>
+        <v>-0.80218814356188028</v>
       </c>
       <c r="G11" s="8">
         <f ca="1"/>
-        <v>4.1183245928421153E-2</v>
+        <v>8.0055811279740596E-3</v>
       </c>
       <c r="H11" s="11">
         <f ca="1"/>
-        <v>47.832760272014475</v>
+        <v>51.191692440275368</v>
       </c>
       <c r="I11" s="8">
         <f ca="1"/>
-        <v>-0.43887794823320636</v>
+        <v>-0.47205561303365345</v>
       </c>
       <c r="J11" s="8">
         <f ca="1"/>
-        <v>3.4889038412130162</v>
+        <v>3.8900150449627589</v>
       </c>
       <c r="K11">
         <f ca="1"/>
@@ -4857,7 +1412,7 @@
       </c>
       <c r="M11" s="22">
         <f ca="1" xml:space="preserve"> - G11*E11</f>
-        <v>-4.161120311822768</v>
+        <v>-0.80218814356188028</v>
       </c>
       <c r="N11" s="22">
         <f ca="1">F11-M11</f>
@@ -4870,7 +1425,7 @@
       </c>
       <c r="C12">
         <f ca="1"/>
-        <v>3.2817260497733744E-2</v>
+        <v>9.6500231423624037E-3</v>
       </c>
       <c r="D12">
         <f ca="1"/>
@@ -4878,27 +1433,27 @@
       </c>
       <c r="E12" s="12">
         <f ca="1"/>
-        <v>100.64239980304919</v>
+        <v>100.17715720112868</v>
       </c>
       <c r="F12" s="11">
         <f ca="1"/>
-        <v>1.5731241331668075</v>
+        <v>0.11641661046079653</v>
       </c>
       <c r="G12" s="8">
         <f ca="1"/>
-        <v>-1.5630828917487183E-2</v>
+        <v>-1.1621073477565691E-3</v>
       </c>
       <c r="H12" s="11">
         <f ca="1"/>
-        <v>49.405884405181283</v>
+        <v>51.308109050736164</v>
       </c>
       <c r="I12" s="8">
         <f ca="1"/>
-        <v>-0.45450877715069354</v>
+        <v>-0.47321772038141002</v>
       </c>
       <c r="J12" s="8">
         <f ca="1"/>
-        <v>3.6630303411861931</v>
+        <v>3.9025030857278935</v>
       </c>
       <c r="K12">
         <f ca="1"/>
@@ -4915,7 +1470,7 @@
       </c>
       <c r="C13">
         <f ca="1"/>
-        <v>-3.1951730483285035E-3</v>
+        <v>-1.9103651635405554E-2</v>
       </c>
       <c r="D13">
         <f ca="1"/>
@@ -4923,27 +1478,27 @@
       </c>
       <c r="E13" s="12">
         <f ca="1"/>
-        <v>99.91213516280763</v>
+        <v>99.594750328971074</v>
       </c>
       <c r="F13" s="11">
         <f ca="1"/>
-        <v>2.9601039339310016</v>
+        <v>2.3826209887818721</v>
       </c>
       <c r="G13" s="8">
         <f ca="1"/>
-        <v>-2.9627071117111936E-2</v>
+        <v>-2.3923158408569178E-2</v>
       </c>
       <c r="H13" s="11">
         <f ca="1"/>
-        <v>52.365988339112285</v>
+        <v>53.690730039518037</v>
       </c>
       <c r="I13" s="8">
         <f ca="1"/>
-        <v>-0.48413584826780548</v>
+        <v>-0.4971408787899792</v>
       </c>
       <c r="J13" s="8">
         <f ca="1"/>
-        <v>3.9949420298187803</v>
+        <v>4.178108338104785</v>
       </c>
       <c r="K13">
         <f ca="1"/>
@@ -4951,7 +1506,7 @@
       </c>
       <c r="L13">
         <f ca="1"/>
-        <v>8.786483719237026E-2</v>
+        <v>0.40524967102892617</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -4960,7 +1515,7 @@
       </c>
       <c r="C14">
         <f ca="1"/>
-        <v>0.10787987527032183</v>
+        <v>-1.1890813914420324E-2</v>
       </c>
       <c r="D14">
         <f ca="1"/>
@@ -4968,27 +1523,27 @@
       </c>
       <c r="E14" s="12">
         <f ca="1"/>
-        <v>102.14834924671462</v>
+        <v>99.730547398671661</v>
       </c>
       <c r="F14" s="11">
         <f ca="1"/>
-        <v>-9.1746618902069201</v>
+        <v>-0.52982138860798333</v>
       </c>
       <c r="G14" s="8">
         <f ca="1"/>
-        <v>8.9817035300763848E-2</v>
+        <v>5.3125286326768939E-3</v>
       </c>
       <c r="H14" s="11">
         <f ca="1"/>
-        <v>43.191326448905365</v>
+        <v>53.160908650910052</v>
       </c>
       <c r="I14" s="8">
         <f ca="1"/>
-        <v>-0.39431881296704163</v>
+        <v>-0.49182835015730231</v>
       </c>
       <c r="J14" s="8">
         <f ca="1"/>
-        <v>2.9123106273980568</v>
+        <v>4.1105980635367345</v>
       </c>
       <c r="K14">
         <f ca="1"/>
@@ -4996,11 +1551,11 @@
       </c>
       <c r="L14">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.26945260132833937</v>
       </c>
       <c r="M14" s="22">
         <f ca="1">f*EXP(sigma*C14-sigma^2*B14/2)</f>
-        <v>102.14834924671462</v>
+        <v>99.730547398671661</v>
       </c>
       <c r="N14" s="23">
         <f ca="1">E14-M14</f>
@@ -5013,7 +1568,7 @@
       </c>
       <c r="C15">
         <f ca="1"/>
-        <v>0.10648555722598418</v>
+        <v>0.11384089833221395</v>
       </c>
       <c r="D15">
         <f ca="1"/>
@@ -5021,27 +1576,27 @@
       </c>
       <c r="E15" s="12">
         <f ca="1"/>
-        <v>102.11169849816734</v>
+        <v>102.26202231403074</v>
       </c>
       <c r="F15" s="11">
         <f ca="1"/>
-        <v>8.8621475463247126E-2</v>
+        <v>-10.48549244961926</v>
       </c>
       <c r="G15" s="8">
         <f ca="1"/>
-        <v>-8.6788758552319711E-4</v>
+        <v>0.10253554753122274</v>
       </c>
       <c r="H15" s="11">
         <f ca="1"/>
-        <v>43.279947924368614</v>
+        <v>42.675416201290794</v>
       </c>
       <c r="I15" s="8">
         <f ca="1"/>
-        <v>-0.39518670055256483</v>
+        <v>-0.38929280262607957</v>
       </c>
       <c r="J15" s="8">
         <f ca="1"/>
-        <v>2.9267627070595736</v>
+        <v>2.8655469324510818</v>
       </c>
       <c r="K15">
         <f ca="1"/>
@@ -5058,7 +1613,7 @@
       </c>
       <c r="C16">
         <f ca="1"/>
-        <v>0.11091546145198063</v>
+        <v>0.14798176549826633</v>
       </c>
       <c r="D16">
         <f ca="1"/>
@@ -5066,27 +1621,27 @@
       </c>
       <c r="E16" s="12">
         <f ca="1"/>
-        <v>102.19403174628108</v>
+        <v>102.95443781860251</v>
       </c>
       <c r="F16" s="11">
         <f ca="1"/>
-        <v>-0.39213711580116739</v>
+        <v>-2.8351900773136824</v>
       </c>
       <c r="G16" s="8">
         <f ca="1"/>
-        <v>3.8371821631886793E-3</v>
+        <v>2.7538298857102794E-2</v>
       </c>
       <c r="H16" s="11">
         <f ca="1"/>
-        <v>42.887810808567444</v>
+        <v>39.840226123977111</v>
       </c>
       <c r="I16" s="8">
         <f ca="1"/>
-        <v>-0.39134951838937615</v>
+        <v>-0.36175450376897678</v>
       </c>
       <c r="J16" s="8">
         <f ca="1"/>
-        <v>2.8942257023917222</v>
+        <v>2.5959945600945815</v>
       </c>
       <c r="K16">
         <f ca="1"/>
@@ -5098,7 +1653,7 @@
       </c>
       <c r="M16" s="22" cm="1">
         <f t="array" aca="1" ref="M16" ca="1">_xll.OPTION.BLACK.PUT_DELTA(E16,sigma*SQRT(t - B16),k)</f>
-        <v>-0.39134951838937615</v>
+        <v>-0.36175450376897678</v>
       </c>
       <c r="N16" s="23">
         <f ca="1">I16-M16</f>
@@ -5111,7 +1666,7 @@
       </c>
       <c r="C17">
         <f ca="1"/>
-        <v>0.17072663836317631</v>
+        <v>0.2439146914254427</v>
       </c>
       <c r="D17">
         <f ca="1"/>
@@ -5119,27 +1674,27 @@
       </c>
       <c r="E17" s="12">
         <f ca="1"/>
-        <v>103.41556820591317</v>
+        <v>104.94045817057381</v>
       </c>
       <c r="F17" s="11">
         <f ca="1"/>
-        <v>-4.9708906310723471</v>
+        <v>-7.726128573934532</v>
       </c>
       <c r="G17" s="8">
         <f ca="1"/>
-        <v>4.8067140347521853E-2</v>
+        <v>7.3623926449570276E-2</v>
       </c>
       <c r="H17" s="11">
         <f ca="1"/>
-        <v>37.916920177495101</v>
+        <v>32.11409755004258</v>
       </c>
       <c r="I17" s="8">
         <f ca="1"/>
-        <v>-0.3432823780418543</v>
+        <v>-0.2881305773194065</v>
       </c>
       <c r="J17" s="8">
         <f ca="1"/>
-        <v>2.4161779972196484</v>
+        <v>1.8775427531921203</v>
       </c>
       <c r="K17">
         <f ca="1"/>
@@ -5156,7 +1711,7 @@
       </c>
       <c r="C18">
         <f ca="1"/>
-        <v>0.19605995490899578</v>
+        <v>0.23450021060815388</v>
       </c>
       <c r="D18">
         <f ca="1"/>
@@ -5164,27 +1719,27 @@
       </c>
       <c r="E18" s="12">
         <f ca="1"/>
-        <v>103.93255477313818</v>
+        <v>104.73467298139198</v>
       </c>
       <c r="F18" s="11">
         <f ca="1"/>
-        <v>-2.1238553837957435</v>
+        <v>0.60230231891726416</v>
       </c>
       <c r="G18" s="8">
         <f ca="1"/>
-        <v>2.0434938681452131E-2</v>
+        <v>-5.7507442547156673E-3</v>
       </c>
       <c r="H18" s="11">
         <f ca="1"/>
-        <v>35.793064793699358</v>
+        <v>32.716399868959847</v>
       </c>
       <c r="I18" s="8">
         <f ca="1"/>
-        <v>-0.32284743936040217</v>
+        <v>-0.29388132157412217</v>
       </c>
       <c r="J18" s="8">
         <f ca="1"/>
-        <v>2.2387056190069501</v>
+        <v>1.9368357585548672</v>
       </c>
       <c r="K18">
         <f ca="1"/>
@@ -5201,7 +1756,7 @@
       </c>
       <c r="C19">
         <f ca="1"/>
-        <v>0.19112609286611534</v>
+        <v>0.13155959211507812</v>
       </c>
       <c r="D19">
         <f ca="1"/>
@@ -5209,27 +1764,27 @@
       </c>
       <c r="E19" s="12">
         <f ca="1"/>
-        <v>103.82174150812899</v>
+        <v>102.59222030876154</v>
       </c>
       <c r="F19" s="11">
         <f ca="1"/>
-        <v>0.30307734383000989</v>
+        <v>8.1577166694131105</v>
       </c>
       <c r="G19" s="8">
         <f ca="1"/>
-        <v>-2.9192088230024504E-3</v>
+        <v>-7.9515938390470997E-2</v>
       </c>
       <c r="H19" s="11">
         <f ca="1"/>
-        <v>36.09614213752937</v>
+        <v>40.874116538372959</v>
       </c>
       <c r="I19" s="8">
         <f ca="1"/>
-        <v>-0.32576664818340462</v>
+        <v>-0.37339725996459316</v>
       </c>
       <c r="J19" s="8">
         <f ca="1"/>
-        <v>2.2744813978623384</v>
+        <v>2.5664625813975093</v>
       </c>
       <c r="K19">
         <f ca="1"/>
@@ -5246,7 +1801,7 @@
       </c>
       <c r="C20">
         <f ca="1"/>
-        <v>0.24587537237107607</v>
+        <v>0.19752777212954131</v>
       </c>
       <c r="D20">
         <f ca="1"/>
@@ -5254,27 +1809,27 @@
       </c>
       <c r="E20" s="12">
         <f ca="1"/>
-        <v>104.95642462647217</v>
+        <v>103.94643729018649</v>
       </c>
       <c r="F20" s="11">
         <f ca="1"/>
-        <v>-4.4775773729180113</v>
+        <v>-5.5667785951393727</v>
       </c>
       <c r="G20" s="8">
         <f ca="1"/>
-        <v>4.2661298618480892E-2</v>
+        <v>5.3554299120407933E-2</v>
       </c>
       <c r="H20" s="11">
         <f ca="1"/>
-        <v>31.618564764611357</v>
+        <v>35.307337943233584</v>
       </c>
       <c r="I20" s="8">
         <f ca="1"/>
-        <v>-0.28310534956492373</v>
+        <v>-0.31984296084418523</v>
       </c>
       <c r="J20" s="8">
         <f ca="1"/>
-        <v>1.9048394816493825</v>
+        <v>2.0608016711359127</v>
       </c>
       <c r="K20">
         <f ca="1"/>
@@ -5286,14 +1841,14 @@
       </c>
       <c r="M20" s="7">
         <f t="array" aca="1" ref="M20:M21" ca="1">_xll.MONTE.STDEV(C20)</f>
-        <v>-5.8297060940817164E-4</v>
+        <v>-3.682849923316224E-3</v>
       </c>
       <c r="N20" s="7">
         <v>0</v>
       </c>
       <c r="O20" s="7">
         <f t="array" aca="1" ref="O20:O21" ca="1">_xll.MONTE.STDEV(E20)</f>
-        <v>99.988056302569603</v>
+        <v>99.928175749452592</v>
       </c>
       <c r="P20" s="7">
         <f>f*EXP(mu*B20)</f>
@@ -5306,7 +1861,7 @@
       </c>
       <c r="C21">
         <f ca="1"/>
-        <v>0.25487440997103938</v>
+        <v>0.15712315267085941</v>
       </c>
       <c r="D21">
         <f ca="1"/>
@@ -5314,27 +1869,27 @@
       </c>
       <c r="E21" s="12">
         <f ca="1"/>
-        <v>105.13708478063337</v>
+        <v>103.10159038124907</v>
       </c>
       <c r="F21" s="11">
         <f ca="1"/>
-        <v>-0.83421401527543815</v>
+        <v>3.240845210041265</v>
       </c>
       <c r="G21" s="8">
         <f ca="1"/>
-        <v>7.9345362962651156E-3</v>
+        <v>-3.1433513276150904E-2</v>
       </c>
       <c r="H21" s="11">
         <f ca="1"/>
-        <v>30.784350749335918</v>
+        <v>38.548183153274849</v>
       </c>
       <c r="I21" s="8">
         <f ca="1"/>
-        <v>-0.27517081326865861</v>
+        <v>-0.35127647412033614</v>
       </c>
       <c r="J21" s="8">
         <f ca="1"/>
-        <v>1.8536936255531238</v>
+        <v>2.3310200079505137</v>
       </c>
       <c r="K21">
         <f ca="1"/>
@@ -5346,7 +1901,7 @@
       </c>
       <c r="M21" s="7">
         <f ca="1"/>
-        <v>0.19962321993442431</v>
+        <v>0.20232311453400736</v>
       </c>
       <c r="N21" s="7">
         <f>SQRT(B20)</f>
@@ -5354,7 +1909,7 @@
       </c>
       <c r="O21" s="7">
         <f ca="1"/>
-        <v>3.9949920098784206</v>
+        <v>4.0412704612687227</v>
       </c>
       <c r="P21" s="7"/>
     </row>
@@ -5364,7 +1919,7 @@
       </c>
       <c r="C22">
         <f ca="1"/>
-        <v>0.27630031710585445</v>
+        <v>0.27658291732044243</v>
       </c>
       <c r="D22">
         <f ca="1"/>
@@ -5372,27 +1927,27 @@
       </c>
       <c r="E22" s="12">
         <f ca="1"/>
-        <v>105.58013619974402</v>
+        <v>105.58610376221513</v>
       </c>
       <c r="F22" s="11">
         <f ca="1"/>
-        <v>-1.7958762602872083</v>
+        <v>-9.8531293577049386</v>
       </c>
       <c r="G22" s="8">
         <f ca="1"/>
-        <v>1.7009603557336217E-2</v>
+        <v>9.3318429287765459E-2</v>
       </c>
       <c r="H22" s="11">
         <f ca="1"/>
-        <v>28.988474489048709</v>
+        <v>28.695053795569912</v>
       </c>
       <c r="I22" s="8">
         <f ca="1"/>
-        <v>-0.25816120971132239</v>
+        <v>-0.25795804483257068</v>
       </c>
       <c r="J22" s="8">
         <f ca="1"/>
-        <v>1.731778806236612</v>
+        <v>1.45826890757996</v>
       </c>
       <c r="K22">
         <f ca="1"/>
@@ -5409,7 +1964,7 @@
       </c>
       <c r="C23">
         <f ca="1"/>
-        <v>0.31132305629372864</v>
+        <v>0.30080512919534746</v>
       </c>
       <c r="D23">
         <f ca="1"/>
@@ -5417,27 +1972,27 @@
       </c>
       <c r="E23" s="12">
         <f ca="1"/>
-        <v>106.31376800639785</v>
+        <v>106.09036297227692</v>
       </c>
       <c r="F23" s="11">
         <f ca="1"/>
-        <v>-2.7871805271438932</v>
+        <v>-1.9881387455944044</v>
       </c>
       <c r="G23" s="8">
         <f ca="1"/>
-        <v>2.62165529395606E-2</v>
+        <v>1.874005036738291E-2</v>
       </c>
       <c r="H23" s="11">
         <f ca="1"/>
-        <v>26.201293961904817</v>
+        <v>26.706915049975507</v>
       </c>
       <c r="I23" s="8">
         <f ca="1"/>
-        <v>-0.23194465677176179</v>
+        <v>-0.23921799446518777</v>
       </c>
       <c r="J23" s="8">
         <f ca="1"/>
-        <v>1.5423835315481575</v>
+        <v>1.3281911876636059</v>
       </c>
       <c r="K23">
         <f ca="1"/>
@@ -5454,7 +2009,7 @@
       </c>
       <c r="C24">
         <f ca="1"/>
-        <v>0.37324050506127127</v>
+        <v>0.21880316989657339</v>
       </c>
       <c r="D24">
         <f ca="1"/>
@@ -5462,27 +2017,27 @@
       </c>
       <c r="E24" s="12">
         <f ca="1"/>
-        <v>107.62987813321804</v>
+        <v>104.35628064445481</v>
       </c>
       <c r="F24" s="11">
         <f ca="1"/>
-        <v>-4.5388452750166</v>
+        <v>6.2089444014754882</v>
       </c>
       <c r="G24" s="8">
         <f ca="1"/>
-        <v>4.217086699102901E-2</v>
+        <v>-5.9497563185770874E-2</v>
       </c>
       <c r="H24" s="11">
         <f ca="1"/>
-        <v>21.662448686888219</v>
+        <v>32.915859451450999</v>
       </c>
       <c r="I24" s="8">
         <f ca="1"/>
-        <v>-0.18977378978073278</v>
+        <v>-0.29871555765095864</v>
       </c>
       <c r="J24" s="8">
         <f ca="1"/>
-        <v>1.2371188199090106</v>
+        <v>1.7430148843627364</v>
       </c>
       <c r="K24">
         <f ca="1"/>
@@ -5499,7 +2054,7 @@
       </c>
       <c r="C25">
         <f ca="1"/>
-        <v>0.35415252345245807</v>
+        <v>4.4187135085260287E-2</v>
       </c>
       <c r="D25">
         <f ca="1"/>
@@ -5507,27 +2062,27 @@
       </c>
       <c r="E25" s="12">
         <f ca="1"/>
-        <v>107.21119677158634</v>
+        <v>100.76666665536476</v>
       </c>
       <c r="F25" s="11">
         <f ca="1"/>
-        <v>1.0758271749518642</v>
+        <v>15.023751695241897</v>
       </c>
       <c r="G25" s="8">
         <f ca="1"/>
-        <v>-1.0034653164481655E-2</v>
+        <v>-0.14909445944684369</v>
       </c>
       <c r="H25" s="11">
         <f ca="1"/>
-        <v>22.738275861840084</v>
+        <v>47.939611146692897</v>
       </c>
       <c r="I25" s="8">
         <f ca="1"/>
-        <v>-0.19980844294521444</v>
+        <v>-0.44781001709780233</v>
       </c>
       <c r="J25" s="8">
         <f ca="1"/>
-        <v>1.3165735686164162</v>
+        <v>2.8152884288654576</v>
       </c>
       <c r="K25">
         <f ca="1"/>
@@ -5544,7 +2099,7 @@
       </c>
       <c r="C26">
         <f ca="1"/>
-        <v>0.5161568190806769</v>
+        <v>9.2712700741800408E-2</v>
       </c>
       <c r="D26">
         <f ca="1"/>
@@ -5552,27 +2107,27 @@
       </c>
       <c r="E26" s="12">
         <f ca="1"/>
-        <v>110.73296141315183</v>
+        <v>101.74123988666912</v>
       </c>
       <c r="F26" s="11">
         <f ca="1"/>
-        <v>-9.9149519637231585</v>
+        <v>-4.4672763536693134</v>
       </c>
       <c r="G26" s="8">
         <f ca="1"/>
-        <v>8.9539301010200856E-2</v>
+        <v>4.3908216163332292E-2</v>
       </c>
       <c r="H26" s="11">
         <f ca="1"/>
-        <v>12.823323898116925</v>
+        <v>43.472334793023585</v>
       </c>
       <c r="I26" s="8">
         <f ca="1"/>
-        <v>-0.11026914193501358</v>
+        <v>-0.40390180093447003</v>
       </c>
       <c r="J26" s="8">
         <f ca="1"/>
-        <v>0.61289525916570398</v>
+        <v>2.3788647734919905</v>
       </c>
       <c r="K26">
         <f ca="1"/>
@@ -5589,7 +2144,7 @@
       </c>
       <c r="C27">
         <f ca="1"/>
-        <v>0.51734446621196939</v>
+        <v>0.14180755318005117</v>
       </c>
       <c r="D27">
         <f ca="1"/>
@@ -5597,27 +2152,27 @@
       </c>
       <c r="E27" s="12">
         <f ca="1"/>
-        <v>110.75040648705132</v>
+        <v>102.73693547434601</v>
       </c>
       <c r="F27" s="11">
         <f ca="1"/>
-        <v>-0.29567344103734838</v>
+        <v>-4.5359028134167731</v>
       </c>
       <c r="G27" s="8">
         <f ca="1"/>
-        <v>2.6697278178560713E-3</v>
+        <v>4.4150653243393789E-2</v>
       </c>
       <c r="H27" s="11">
         <f ca="1"/>
-        <v>12.527650457079577</v>
+        <v>38.936431979606809</v>
       </c>
       <c r="I27" s="8">
         <f ca="1"/>
-        <v>-0.10759941411715751</v>
+        <v>-0.35975114769107625</v>
       </c>
       <c r="J27" s="8">
         <f ca="1"/>
-        <v>0.61097160583581456</v>
+        <v>1.9767015324467891</v>
       </c>
       <c r="K27">
         <f ca="1"/>
@@ -5634,7 +2189,7 @@
       </c>
       <c r="C28">
         <f ca="1"/>
-        <v>0.47751968217527263</v>
+        <v>0.1088449142298322</v>
       </c>
       <c r="D28">
         <f ca="1"/>
@@ -5642,27 +2197,27 @@
       </c>
       <c r="E28" s="12">
         <f ca="1"/>
-        <v>109.86299861564535</v>
+        <v>102.05370239811604</v>
       </c>
       <c r="F28" s="11">
         <f ca="1"/>
-        <v>1.7628660479776626</v>
+        <v>2.9385851055174705</v>
       </c>
       <c r="G28" s="8">
         <f ca="1"/>
-        <v>-1.6046039796756617E-2</v>
+        <v>-2.8794497764068561E-2</v>
       </c>
       <c r="H28" s="11">
         <f ca="1"/>
-        <v>14.290516505057241</v>
+        <v>41.875017085124277</v>
       </c>
       <c r="I28" s="8">
         <f ca="1"/>
-        <v>-0.12364545391391413</v>
+        <v>-0.38854564545514481</v>
       </c>
       <c r="J28" s="8">
         <f ca="1"/>
-        <v>0.70645617288205109</v>
+        <v>2.2224954157610171</v>
       </c>
       <c r="K28">
         <f ca="1"/>
@@ -5679,7 +2234,7 @@
       </c>
       <c r="C29">
         <f ca="1"/>
-        <v>0.48211368867873877</v>
+        <v>0.12947690149019384</v>
       </c>
       <c r="D29">
         <f ca="1"/>
@@ -5687,27 +2242,27 @@
       </c>
       <c r="E29" s="12">
         <f ca="1"/>
-        <v>109.95519050171376</v>
+        <v>102.46748884710233</v>
       </c>
       <c r="F29" s="11">
         <f ca="1"/>
-        <v>-0.49487228685459755</v>
+        <v>-1.9791257291352438</v>
       </c>
       <c r="G29" s="8">
         <f ca="1"/>
-        <v>4.500672361136826E-3</v>
+        <v>1.9314669964132836E-2</v>
       </c>
       <c r="H29" s="11">
         <f ca="1"/>
-        <v>13.795644218202643</v>
+        <v>39.895891355989036</v>
       </c>
       <c r="I29" s="8">
         <f ca="1"/>
-        <v>-0.1191447815527773</v>
+        <v>-0.36923097549101197</v>
       </c>
       <c r="J29" s="8">
         <f ca="1"/>
-        <v>0.69505706528194366</v>
+        <v>2.0617204928590525</v>
       </c>
       <c r="K29">
         <f ca="1"/>
@@ -5724,7 +2279,7 @@
       </c>
       <c r="C30">
         <f ca="1"/>
-        <v>0.48740210154083191</v>
+        <v>0.1815435997714332</v>
       </c>
       <c r="D30">
         <f ca="1"/>
@@ -5732,27 +2287,27 @@
       </c>
       <c r="E30" s="12">
         <f ca="1"/>
-        <v>110.06274434340533</v>
+        <v>103.53180973723302</v>
       </c>
       <c r="F30" s="11">
         <f ca="1"/>
-        <v>-0.53278118091768634</v>
+        <v>-4.8907513265215385</v>
       </c>
       <c r="G30" s="8">
         <f ca="1"/>
-        <v>4.8407041283230479E-3</v>
+        <v>4.7239117513104611E-2</v>
       </c>
       <c r="H30" s="11">
         <f ca="1"/>
-        <v>13.262863037284957</v>
+        <v>35.005140029467498</v>
       </c>
       <c r="I30" s="8">
         <f ca="1"/>
-        <v>-0.11430407742445425</v>
+        <v>-0.32199185797790736</v>
       </c>
       <c r="J30" s="8">
         <f ca="1"/>
-        <v>0.68224258630844048</v>
+        <v>1.6687402523606352</v>
       </c>
       <c r="K30">
         <f ca="1"/>
@@ -5769,7 +2324,7 @@
       </c>
       <c r="C31">
         <f ca="1"/>
-        <v>0.45905365800037878</v>
+        <v>0.13129339866010115</v>
       </c>
       <c r="D31">
         <f ca="1"/>
@@ -5777,27 +2332,27 @@
       </c>
       <c r="E31" s="12">
         <f ca="1"/>
-        <v>109.43173362106187</v>
+        <v>102.48832254725441</v>
       </c>
       <c r="F31" s="11">
         <f ca="1"/>
-        <v>1.2499372930557888</v>
+        <v>4.5139151061057055</v>
       </c>
       <c r="G31" s="8">
         <f ca="1"/>
-        <v>-1.142207339403073E-2</v>
+        <v>-4.4043213840527728E-2</v>
       </c>
       <c r="H31" s="11">
         <f ca="1"/>
-        <v>14.512800330340745</v>
+        <v>39.519055135573204</v>
       </c>
       <c r="I31" s="8">
         <f ca="1"/>
-        <v>-0.12572615081848498</v>
+        <v>-0.36603507181843509</v>
       </c>
       <c r="J31" s="8">
         <f ca="1"/>
-        <v>0.75436968477084676</v>
+        <v>2.0047346314379979</v>
       </c>
       <c r="K31">
         <f ca="1"/>
@@ -5814,7 +2369,7 @@
       </c>
       <c r="C32">
         <f ca="1"/>
-        <v>0.42893998765311886</v>
+        <v>0.11767599000023436</v>
       </c>
       <c r="D32">
         <f ca="1"/>
@@ -5822,27 +2377,27 @@
       </c>
       <c r="E32" s="12">
         <f ca="1"/>
-        <v>108.76593451583672</v>
+        <v>102.20140078513391</v>
       </c>
       <c r="F32" s="11">
         <f ca="1"/>
-        <v>1.4612808709059746</v>
+        <v>1.222208864793187</v>
       </c>
       <c r="G32" s="8">
         <f ca="1"/>
-        <v>-1.3435096911645683E-2</v>
+        <v>-1.1958826937829681E-2</v>
       </c>
       <c r="H32" s="11">
         <f ca="1"/>
-        <v>15.974081201246721</v>
+        <v>40.741264000366392</v>
       </c>
       <c r="I32" s="8">
         <f ca="1"/>
-        <v>-0.13916124773013067</v>
+        <v>-0.37799389875626477</v>
       </c>
       <c r="J32" s="8">
         <f ca="1"/>
-        <v>0.83807804348919746</v>
+        <v>2.1097580592420471</v>
       </c>
       <c r="K32">
         <f ca="1"/>
@@ -5859,7 +2414,7 @@
       </c>
       <c r="C33">
         <f ca="1"/>
-        <v>0.54688048000656653</v>
+        <v>4.6145283947534838E-2</v>
       </c>
       <c r="D33">
         <f ca="1"/>
@@ -5867,27 +2422,27 @@
       </c>
       <c r="E33" s="12">
         <f ca="1"/>
-        <v>111.35310540395122</v>
+        <v>100.74164232321678</v>
       </c>
       <c r="F33" s="11">
         <f ca="1"/>
-        <v>-6.3766719041497986</v>
+        <v>6.9736725132514445</v>
       </c>
       <c r="G33" s="8">
         <f ca="1"/>
-        <v>5.7265326198289668E-2</v>
+        <v>-6.922333557832322E-2</v>
       </c>
       <c r="H33" s="11">
         <f ca="1"/>
-        <v>9.597409297096922</v>
+        <v>47.714936513617836</v>
       </c>
       <c r="I33" s="8">
         <f ca="1"/>
-        <v>-8.1895921531840998E-2</v>
+        <v>-0.44721723433458799</v>
       </c>
       <c r="J33" s="8">
         <f ca="1"/>
-        <v>0.4780441146081138</v>
+        <v>2.6615378515045478</v>
       </c>
       <c r="K33">
         <f ca="1"/>
@@ -5904,7 +2459,7 @@
       </c>
       <c r="C34">
         <f ca="1"/>
-        <v>0.57718958712773238</v>
+        <v>0.13106043341461404</v>
       </c>
       <c r="D34">
         <f ca="1"/>
@@ -5912,27 +2467,27 @@
       </c>
       <c r="E34" s="12">
         <f ca="1"/>
-        <v>112.02119600269585</v>
+        <v>102.45895431496534</v>
       </c>
       <c r="F34" s="11">
         <f ca="1"/>
-        <v>-1.4789918921959246</v>
+        <v>-8.5634925307338889</v>
       </c>
       <c r="G34" s="8">
         <f ca="1"/>
-        <v>1.3202786124157539E-2</v>
+        <v>8.3579737739750581E-2</v>
       </c>
       <c r="H34" s="11">
         <f ca="1"/>
-        <v>8.1184174049009972</v>
+        <v>39.151443982883947</v>
       </c>
       <c r="I34" s="8">
         <f ca="1"/>
-        <v>-6.8693135407683459E-2</v>
+        <v>-0.36363749659483741</v>
       </c>
       <c r="J34" s="8">
         <f ca="1"/>
-        <v>0.42333021935716264</v>
+        <v>1.8935263320651359</v>
       </c>
       <c r="K34">
         <f ca="1"/>
@@ -5949,7 +2504,7 @@
       </c>
       <c r="C35">
         <f ca="1"/>
-        <v>0.49128049548836805</v>
+        <v>0.18992040056174278</v>
       </c>
       <c r="D35">
         <f ca="1"/>
@@ -5957,27 +2512,27 @@
       </c>
       <c r="E35" s="12">
         <f ca="1"/>
-        <v>110.10410034977092</v>
+        <v>103.66393431776801</v>
       </c>
       <c r="F35" s="11">
         <f ca="1"/>
-        <v>3.4501223319933474</v>
+        <v>-5.83157270937724</v>
       </c>
       <c r="G35" s="8">
         <f ca="1"/>
-        <v>-3.1335093979545203E-2</v>
+        <v>5.6254595658132456E-2</v>
       </c>
       <c r="H35" s="11">
         <f ca="1"/>
-        <v>11.568539736894344</v>
+        <v>33.319871273506706</v>
       </c>
       <c r="I35" s="8">
         <f ca="1"/>
-        <v>-0.10002822938722866</v>
+        <v>-0.30738290093670495</v>
       </c>
       <c r="J35" s="8">
         <f ca="1"/>
-        <v>0.55502153063301485</v>
+        <v>1.4553504203991317</v>
       </c>
       <c r="K35">
         <f ca="1"/>
@@ -5994,7 +2549,7 @@
       </c>
       <c r="C36">
         <f ca="1"/>
-        <v>0.53969718813836931</v>
+        <v>0.17059370153070766</v>
       </c>
       <c r="D36">
         <f ca="1"/>
@@ -6002,27 +2557,27 @@
       </c>
       <c r="E36" s="12">
         <f ca="1"/>
-        <v>111.16656071690167</v>
+        <v>103.25575061241874</v>
       </c>
       <c r="F36" s="11">
         <f ca="1"/>
-        <v>-2.5262030262567543</v>
+        <v>1.6819071965339163</v>
       </c>
       <c r="G36" s="8">
         <f ca="1"/>
-        <v>2.272448666186605E-2</v>
+        <v>-1.6288750859476397E-2</v>
       </c>
       <c r="H36" s="11">
         <f ca="1"/>
-        <v>9.0423367106375903</v>
+        <v>35.00177847004062</v>
       </c>
       <c r="I36" s="8">
         <f ca="1"/>
-        <v>-7.7303742725362612E-2</v>
+        <v>-0.32367165179618135</v>
       </c>
       <c r="J36" s="8">
         <f ca="1"/>
-        <v>0.44874550131482138</v>
+        <v>1.5808191118644856</v>
       </c>
       <c r="K36">
         <f ca="1"/>
@@ -6039,7 +2594,7 @@
       </c>
       <c r="C37">
         <f ca="1"/>
-        <v>0.46490717595721726</v>
+        <v>0.19393707863599449</v>
       </c>
       <c r="D37">
         <f ca="1"/>
@@ -6047,27 +2602,27 @@
       </c>
       <c r="E37" s="12">
         <f ca="1"/>
-        <v>109.50734462187243</v>
+        <v>103.73064647554276</v>
       </c>
       <c r="F37" s="11">
         <f ca="1"/>
-        <v>3.2496009615538708</v>
+        <v>-2.4294207933435925</v>
       </c>
       <c r="G37" s="8">
         <f ca="1"/>
-        <v>-2.9674730702079433E-2</v>
+        <v>2.3420472887117239E-2</v>
       </c>
       <c r="H37" s="11">
         <f ca="1"/>
-        <v>12.291937672191461</v>
+        <v>32.572357676697024</v>
       </c>
       <c r="I37" s="8">
         <f ca="1"/>
-        <v>-0.10697847342744204</v>
+        <v>-0.30025117890906411</v>
       </c>
       <c r="J37" s="8">
         <f ca="1"/>
-        <v>0.57700911545074263</v>
+        <v>1.4271087834159566</v>
       </c>
       <c r="K37">
         <f ca="1"/>
@@ -6084,7 +2639,7 @@
       </c>
       <c r="C38">
         <f ca="1"/>
-        <v>0.46229450136284828</v>
+        <v>0.17099699734336438</v>
       </c>
       <c r="D38">
         <f ca="1"/>
@@ -6092,27 +2647,27 @@
       </c>
       <c r="E38" s="12">
         <f ca="1"/>
-        <v>109.44138249710198</v>
+        <v>103.24755853967895</v>
       </c>
       <c r="F38" s="11">
         <f ca="1"/>
-        <v>-0.17445146708638673</v>
+        <v>2.0534700018870131</v>
       </c>
       <c r="G38" s="8">
         <f ca="1"/>
-        <v>1.5940173918307932E-3</v>
+        <v>-1.9888799608736962E-2</v>
       </c>
       <c r="H38" s="11">
         <f ca="1"/>
-        <v>12.117486205105074</v>
+        <v>34.625827678584038</v>
       </c>
       <c r="I38" s="8">
         <f ca="1"/>
-        <v>-0.10538445603561125</v>
+        <v>-0.32013997851780107</v>
       </c>
       <c r="J38" s="8">
         <f ca="1"/>
-        <v>0.5840656428627149</v>
+        <v>1.5721565056758138</v>
       </c>
       <c r="K38">
         <f ca="1"/>
@@ -6129,7 +2684,7 @@
       </c>
       <c r="C39">
         <f ca="1"/>
-        <v>0.4331895013841775</v>
+        <v>0.1674825430027958</v>
       </c>
       <c r="D39">
         <f ca="1"/>
@@ -6137,27 +2692,27 @@
       </c>
       <c r="E39" s="12">
         <f ca="1"/>
-        <v>108.79747062992932</v>
+        <v>103.16675860183693</v>
       </c>
       <c r="F39" s="11">
         <f ca="1"/>
-        <v>1.3026334801592949</v>
+        <v>0.1796400001016174</v>
       </c>
       <c r="G39" s="8">
         <f ca="1"/>
-        <v>-1.1973012539879313E-2</v>
+        <v>-1.7412585462234231E-3</v>
       </c>
       <c r="H39" s="11">
         <f ca="1"/>
-        <v>13.420119685264369</v>
+        <v>34.805467678685659</v>
       </c>
       <c r="I39" s="8">
         <f ca="1"/>
-        <v>-0.11735746857549056</v>
+        <v>-0.32188123706402449</v>
       </c>
       <c r="J39" s="8">
         <f ca="1"/>
-        <v>0.65192394471958082</v>
+        <v>1.598023796040799</v>
       </c>
       <c r="K39">
         <f ca="1"/>
@@ -6174,7 +2729,7 @@
       </c>
       <c r="C40">
         <f ca="1"/>
-        <v>0.5251928318102389</v>
+        <v>0.23508076271824754</v>
       </c>
       <c r="D40">
         <f ca="1"/>
@@ -6182,27 +2737,27 @@
       </c>
       <c r="E40" s="12">
         <f ca="1"/>
-        <v>110.80908353881496</v>
+        <v>104.56264218258417</v>
       </c>
       <c r="F40" s="11">
         <f ca="1"/>
-        <v>-5.0007520568483947</v>
+        <v>-6.8565264829055765</v>
       </c>
       <c r="G40" s="8">
         <f ca="1"/>
-        <v>4.5129441532622161E-2</v>
+        <v>6.5573385865029254E-2</v>
       </c>
       <c r="H40" s="11">
         <f ca="1"/>
-        <v>8.4193676284159746</v>
+        <v>27.948941195780083</v>
       </c>
       <c r="I40" s="8">
         <f ca="1"/>
-        <v>-7.2228027042868403E-2</v>
+        <v>-0.25630785119899524</v>
       </c>
       <c r="J40" s="8">
         <f ca="1"/>
-        <v>0.41584614597898373</v>
+        <v>1.1487150622725153</v>
       </c>
       <c r="K40">
         <f ca="1"/>
@@ -6219,7 +2774,7 @@
       </c>
       <c r="C41">
         <f ca="1"/>
-        <v>0.50681037343756852</v>
+        <v>0.19423050513462889</v>
       </c>
       <c r="D41">
         <f ca="1"/>
@@ -6227,27 +2782,27 @@
       </c>
       <c r="E41" s="12">
         <f ca="1"/>
-        <v>110.39361098719816</v>
+        <v>103.70354367408432</v>
       </c>
       <c r="F41" s="11">
         <f ca="1"/>
-        <v>0.48230915917569922</v>
+        <v>3.6944745822141503</v>
       </c>
       <c r="G41" s="8">
         <f ca="1"/>
-        <v>-4.3689952241133811E-3</v>
+        <v>-3.562534558920194E-2</v>
       </c>
       <c r="H41" s="11">
         <f ca="1"/>
-        <v>8.9016767875916738</v>
+        <v>31.643415777994235</v>
       </c>
       <c r="I41" s="8">
         <f ca="1"/>
-        <v>-7.6597022266981785E-2</v>
+        <v>-0.29193319678819718</v>
       </c>
       <c r="J41" s="8">
         <f ca="1"/>
-        <v>0.44585490867273059</v>
+        <v>1.3689087549543792</v>
       </c>
       <c r="K41">
         <f ca="1"/>
@@ -6264,7 +2819,7 @@
       </c>
       <c r="C42">
         <f ca="1"/>
-        <v>0.44712508188580213</v>
+        <v>2.7090583458080186E-2</v>
       </c>
       <c r="D42">
         <f ca="1"/>
@@ -6272,27 +2827,27 @@
       </c>
       <c r="E42" s="12">
         <f ca="1"/>
-        <v>109.07494364702428</v>
+        <v>100.28622050011549</v>
       </c>
       <c r="F42" s="11">
         <f ca="1"/>
-        <v>2.613175431753143</v>
+        <v>17.834808846545787</v>
       </c>
       <c r="G42" s="8">
         <f ca="1"/>
-        <v>-2.3957614318918186E-2</v>
+        <v>-0.17783907657109532</v>
       </c>
       <c r="H42" s="11">
         <f ca="1"/>
-        <v>11.514852219344817</v>
+        <v>49.478224624540019</v>
       </c>
       <c r="I42" s="8">
         <f ca="1"/>
-        <v>-0.10055463658589997</v>
+        <v>-0.4697722733592925</v>
       </c>
       <c r="J42" s="8">
         <f ca="1"/>
-        <v>0.54686090029077228</v>
+        <v>2.3665388335894804</v>
       </c>
       <c r="K42">
         <f ca="1"/>
@@ -6309,7 +2864,7 @@
       </c>
       <c r="C43">
         <f ca="1"/>
-        <v>0.46946742433312155</v>
+        <v>-4.5897536299875058E-2</v>
       </c>
       <c r="D43">
         <f ca="1"/>
@@ -6317,27 +2872,27 @@
       </c>
       <c r="E43" s="12">
         <f ca="1"/>
-        <v>109.55466745671781</v>
+        <v>98.825006872821149</v>
       </c>
       <c r="F43" s="11">
         <f ca="1"/>
-        <v>-1.539226829790928</v>
+        <v>8.3985842306233618</v>
       </c>
       <c r="G43" s="8">
         <f ca="1"/>
-        <v>1.4049851690700776E-2</v>
+        <v>-8.4984403203043346E-2</v>
       </c>
       <c r="H43" s="11">
         <f ca="1"/>
-        <v>9.9756253895538887</v>
+        <v>57.876808855163382</v>
       </c>
       <c r="I43" s="8">
         <f ca="1"/>
-        <v>-8.6504784895199194E-2</v>
+        <v>-0.55475667656233585</v>
       </c>
       <c r="J43" s="8">
         <f ca="1"/>
-        <v>0.49862244694543456</v>
+        <v>3.0529764811471196</v>
       </c>
       <c r="K43">
         <f ca="1"/>
@@ -6345,7 +2900,7 @@
       </c>
       <c r="L43">
         <f ca="1"/>
-        <v>0</v>
+        <v>1.1749931271788512</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -6354,7 +2909,7 @@
       </c>
       <c r="C44">
         <f ca="1"/>
-        <v>0.44388229787344613</v>
+        <v>8.3831227005368464E-2</v>
       </c>
       <c r="D44">
         <f ca="1"/>
@@ -6362,27 +2917,27 @@
       </c>
       <c r="E44" s="12">
         <f ca="1"/>
-        <v>108.986786004393</v>
+        <v>101.41453574128651</v>
       </c>
       <c r="F44" s="11">
         <f ca="1"/>
-        <v>0.97068234096851824</v>
+        <v>-15.240353788182336</v>
       </c>
       <c r="G44" s="8">
         <f ca="1"/>
-        <v>-8.9064222971892426E-3</v>
+        <v>0.15027780462419343</v>
       </c>
       <c r="H44" s="11">
         <f ca="1"/>
-        <v>10.946307730522406</v>
+        <v>42.636455066981043</v>
       </c>
       <c r="I44" s="8">
         <f ca="1"/>
-        <v>-9.5411207192388436E-2</v>
+        <v>-0.40447887193814241</v>
       </c>
       <c r="J44" s="8">
         <f ca="1"/>
-        <v>0.54774690982476493</v>
+        <v>1.616418052215046</v>
       </c>
       <c r="K44">
         <f ca="1"/>
@@ -6399,7 +2954,7 @@
       </c>
       <c r="C45">
         <f ca="1"/>
-        <v>0.61659233353201059</v>
+        <v>6.9209358111326905E-2</v>
       </c>
       <c r="D45">
         <f ca="1"/>
@@ -6407,27 +2962,27 @@
       </c>
       <c r="E45" s="12">
         <f ca="1"/>
-        <v>112.80815727246178</v>
+        <v>101.1103058083702</v>
       </c>
       <c r="F45" s="11">
         <f ca="1"/>
-        <v>-7.1360264386867955</v>
+        <v>1.6588771564875977</v>
       </c>
       <c r="G45" s="8">
         <f ca="1"/>
-        <v>6.3258071146853223E-2</v>
+        <v>-1.6406608042820015E-2</v>
       </c>
       <c r="H45" s="11">
         <f ca="1"/>
-        <v>3.8102812918356106</v>
+        <v>44.295332223468641</v>
       </c>
       <c r="I45" s="8">
         <f ca="1"/>
-        <v>-3.2153136045535213E-2</v>
+        <v>-0.42088547998096243</v>
       </c>
       <c r="J45" s="8">
         <f ca="1"/>
-        <v>0.18314526400801423</v>
+        <v>1.7394726322908554</v>
       </c>
       <c r="K45">
         <f ca="1"/>
@@ -6444,7 +2999,7 @@
       </c>
       <c r="C46">
         <f ca="1"/>
-        <v>0.67890796267445475</v>
+        <v>5.3076080761499701E-2</v>
       </c>
       <c r="D46">
         <f ca="1"/>
@@ -6452,27 +3007,27 @@
       </c>
       <c r="E46" s="12">
         <f ca="1"/>
-        <v>114.21375979346473</v>
+        <v>100.77652102237596</v>
       </c>
       <c r="F46" s="11">
         <f ca="1"/>
-        <v>-1.4954988094185959</v>
+        <v>1.9111485806755801</v>
       </c>
       <c r="G46" s="8">
         <f ca="1"/>
-        <v>1.3093858499386934E-2</v>
+        <v>-1.8964224615882874E-2</v>
       </c>
       <c r="H46" s="11">
         <f ca="1"/>
-        <v>2.3147824824170149</v>
+        <v>46.206480804144221</v>
       </c>
       <c r="I46" s="8">
         <f ca="1"/>
-        <v>-1.9059277546148279E-2</v>
+        <v>-0.4398497045968453</v>
       </c>
       <c r="J46" s="8">
         <f ca="1"/>
-        <v>0.13795073492425924</v>
+        <v>1.8799578021543866</v>
       </c>
       <c r="K46">
         <f ca="1"/>
@@ -6489,7 +3044,7 @@
       </c>
       <c r="C47">
         <f ca="1"/>
-        <v>0.67658447398497079</v>
+        <v>3.1431246078661962E-2</v>
       </c>
       <c r="D47">
         <f ca="1"/>
@@ -6497,27 +3052,27 @@
       </c>
       <c r="E47" s="12">
         <f ca="1"/>
-        <v>114.15156475715409</v>
+        <v>100.33317873213257</v>
       </c>
       <c r="F47" s="11">
         <f ca="1"/>
-        <v>-0.1567174307276788</v>
+        <v>2.6762655840504777</v>
       </c>
       <c r="G47" s="8">
         <f ca="1"/>
-        <v>1.3728890275054861E-3</v>
+        <v>-2.6673784463617123E-2</v>
       </c>
       <c r="H47" s="11">
         <f ca="1"/>
-        <v>2.158065051689336</v>
+        <v>48.882746388194697</v>
       </c>
       <c r="I47" s="8">
         <f ca="1"/>
-        <v>-1.7686388518642793E-2</v>
+        <v>-0.46652348906046243</v>
       </c>
       <c r="J47" s="8">
         <f ca="1"/>
-        <v>0.1391361273832965</v>
+        <v>2.0749617775532272</v>
       </c>
       <c r="K47">
         <f ca="1"/>
@@ -6534,7 +3089,7 @@
       </c>
       <c r="C48">
         <f ca="1"/>
-        <v>0.68229123567249228</v>
+        <v>6.7568945143510306E-2</v>
       </c>
       <c r="D48">
         <f ca="1"/>
@@ -6542,27 +3097,27 @@
       </c>
       <c r="E48" s="12">
         <f ca="1"/>
-        <v>114.27278410407833</v>
+        <v>101.05288311557099</v>
       </c>
       <c r="F48" s="11">
         <f ca="1"/>
-        <v>-0.27276030169276799</v>
+        <v>-4.5708545774636047</v>
       </c>
       <c r="G48" s="8">
         <f ca="1"/>
-        <v>2.3869226940715915E-3</v>
+        <v>4.5232302498841748E-2</v>
       </c>
       <c r="H48" s="11">
         <f ca="1"/>
-        <v>1.8853047499965681</v>
+        <v>44.31189181073109</v>
       </c>
       <c r="I48" s="8">
         <f ca="1"/>
-        <v>-1.5299465824571201E-2</v>
+        <v>-0.42129118656162068</v>
       </c>
       <c r="J48" s="8">
         <f ca="1"/>
-        <v>0.13699219491761849</v>
+        <v>1.7392027774994219</v>
       </c>
       <c r="K48">
         <f ca="1"/>
@@ -6579,7 +3134,7 @@
       </c>
       <c r="C49">
         <f ca="1"/>
-        <v>0.59885606217113718</v>
+        <v>6.4569380979022442E-2</v>
       </c>
       <c r="D49">
         <f ca="1"/>
@@ -6587,27 +3142,27 @@
       </c>
       <c r="E49" s="12">
         <f ca="1"/>
-        <v>112.37274191791875</v>
+        <v>100.98419931568384</v>
       </c>
       <c r="F49" s="11">
         <f ca="1"/>
-        <v>1.271691721386331</v>
+        <v>0.32461629299261652</v>
       </c>
       <c r="G49" s="8">
         <f ca="1"/>
-        <v>-1.1316727701769724E-2</v>
+        <v>-3.2145255910565051E-3</v>
       </c>
       <c r="H49" s="11">
         <f ca="1"/>
-        <v>3.1569964713828993</v>
+        <v>44.636508103723706</v>
       </c>
       <c r="I49" s="8">
         <f ca="1"/>
-        <v>-2.6616193526340926E-2</v>
+        <v>-0.42450571215267718</v>
       </c>
       <c r="J49" s="8">
         <f ca="1"/>
-        <v>0.16606182541001102</v>
+        <v>1.7681386570514448</v>
       </c>
       <c r="K49">
         <f ca="1"/>
@@ -6624,7 +3179,7 @@
       </c>
       <c r="C50">
         <f ca="1"/>
-        <v>0.69351148281152941</v>
+        <v>7.2227660424275877E-2</v>
       </c>
       <c r="D50">
         <f ca="1"/>
@@ -6632,27 +3187,27 @@
       </c>
       <c r="E50" s="12">
         <f ca="1"/>
-        <v>114.51118256520706</v>
+        <v>101.13090007707169</v>
       </c>
       <c r="F50" s="11">
         <f ca="1"/>
-        <v>-1.7815934643782436</v>
+        <v>-1.0686851626404281</v>
       </c>
       <c r="G50" s="8">
         <f ca="1"/>
-        <v>1.5558248761982141E-2</v>
+        <v>1.0567345507910886E-2</v>
       </c>
       <c r="H50" s="11">
         <f ca="1"/>
-        <v>1.3754030070046557</v>
+        <v>43.567822941083278</v>
       </c>
       <c r="I50" s="8">
         <f ca="1"/>
-        <v>-1.1057944764358785E-2</v>
+        <v>-0.4139383666447663</v>
       </c>
       <c r="J50" s="8">
         <f ca="1"/>
-        <v>0.10914467529719118</v>
+        <v>1.7058633458651542</v>
       </c>
       <c r="K50">
         <f ca="1"/>
@@ -6669,7 +3224,7 @@
       </c>
       <c r="C51">
         <f ca="1"/>
-        <v>0.66568800991491428</v>
+        <v>0.11674648122295003</v>
       </c>
       <c r="D51">
         <f ca="1"/>
@@ -6677,27 +3232,27 @@
       </c>
       <c r="E51" s="12">
         <f ca="1"/>
-        <v>113.86662279666884</v>
+        <v>102.02720385978898</v>
       </c>
       <c r="F51" s="11">
         <f ca="1"/>
-        <v>0.15693459834712262</v>
+        <v>-5.99995800462872</v>
       </c>
       <c r="G51" s="8">
         <f ca="1"/>
-        <v>-1.3782317811195655E-3</v>
+        <v>5.8807433484839688E-2</v>
       </c>
       <c r="H51" s="11">
         <f ca="1"/>
-        <v>1.5323376053517783</v>
+        <v>37.567864936454555</v>
       </c>
       <c r="I51" s="8">
         <f ca="1"/>
-        <v>-1.243617654547835E-2</v>
+        <v>-0.35513093315992661</v>
       </c>
       <c r="J51" s="8">
         <f ca="1"/>
-        <v>0.11627218161501496</v>
+        <v>1.3348488220296275</v>
       </c>
       <c r="K51">
         <f ca="1"/>
@@ -6714,7 +3269,7 @@
       </c>
       <c r="C52">
         <f ca="1"/>
-        <v>0.62935490331474286</v>
+        <v>0.15333688299694814</v>
       </c>
       <c r="D52">
         <f ca="1"/>
@@ -6722,27 +3277,27 @@
       </c>
       <c r="E52" s="12">
         <f ca="1"/>
-        <v>113.03315317954372</v>
+        <v>102.76836401230453</v>
       </c>
       <c r="F52" s="11">
         <f ca="1"/>
-        <v>0.29975407031992429</v>
+        <v>-4.9849966940534918</v>
       </c>
       <c r="G52" s="8">
         <f ca="1"/>
-        <v>-2.651912840507864E-3</v>
+        <v>4.8507113467882335E-2</v>
       </c>
       <c r="H52" s="11">
         <f ca="1"/>
-        <v>1.8320916756717027</v>
+        <v>32.582868242401062</v>
       </c>
       <c r="I52" s="8">
         <f ca="1"/>
-        <v>-1.5088089385986214E-2</v>
+        <v>-0.30662381969204427</v>
       </c>
       <c r="J52" s="8">
         <f ca="1"/>
-        <v>0.12663735691887523</v>
+        <v>1.071639925445826</v>
       </c>
       <c r="K52">
         <f ca="1"/>
@@ -6759,7 +3314,7 @@
       </c>
       <c r="C53">
         <f ca="1"/>
-        <v>0.60957847243184127</v>
+        <v>0.17281910037395992</v>
       </c>
       <c r="D53">
         <f ca="1"/>
@@ -6767,27 +3322,27 @@
       </c>
       <c r="E53" s="12">
         <f ca="1"/>
-        <v>112.57795111201972</v>
+        <v>103.16132304061512</v>
       </c>
       <c r="F53" s="11">
         <f ca="1"/>
-        <v>8.2154705220632354E-2</v>
+        <v>-2.826113909072475</v>
       </c>
       <c r="G53" s="8">
         <f ca="1"/>
-        <v>-7.2975839770689221E-4</v>
+        <v>2.739509174344168E-2</v>
       </c>
       <c r="H53" s="11">
         <f ca="1"/>
-        <v>1.9142463808923351</v>
+        <v>29.756754333328587</v>
       </c>
       <c r="I53" s="8">
         <f ca="1"/>
-        <v>-1.5817847783693106E-2</v>
+        <v>-0.2792287279486026</v>
       </c>
       <c r="J53" s="8">
         <f ca="1"/>
-        <v>0.13350548640236304</v>
+        <v>0.95114932720276002</v>
       </c>
       <c r="K53">
         <f ca="1"/>
@@ -6804,7 +3359,7 @@
       </c>
       <c r="C54">
         <f ca="1"/>
-        <v>0.62700674757993413</v>
+        <v>0.20236569666031617</v>
       </c>
       <c r="D54">
         <f ca="1"/>
@@ -6812,27 +3367,27 @@
       </c>
       <c r="E54" s="12">
         <f ca="1"/>
-        <v>112.96200638613159</v>
+        <v>103.76443949894161</v>
       </c>
       <c r="F54" s="11">
         <f ca="1"/>
-        <v>-0.46718394779256611</v>
+        <v>-4.0741786210405477</v>
       </c>
       <c r="G54" s="8">
         <f ca="1"/>
-        <v>4.1357617728178253E-3</v>
+        <v>3.9263726963822743E-2</v>
       </c>
       <c r="H54" s="11">
         <f ca="1"/>
-        <v>1.447062433099769</v>
+        <v>25.682575712288038</v>
       </c>
       <c r="I54" s="8">
         <f ca="1"/>
-        <v>-1.1682086010875281E-2</v>
+        <v>-0.23996500098477985</v>
       </c>
       <c r="J54" s="8">
         <f ca="1"/>
-        <v>0.12743055853593699</v>
+        <v>0.78274188573938375</v>
       </c>
       <c r="K54">
         <f ca="1"/>
@@ -6849,7 +3404,7 @@
       </c>
       <c r="C55">
         <f ca="1"/>
-        <v>0.64132511897383726</v>
+        <v>0.24673109089851386</v>
       </c>
       <c r="D55">
         <f ca="1"/>
@@ -6857,27 +3412,27 @@
       </c>
       <c r="E55" s="12">
         <f ca="1"/>
-        <v>113.2768938865715</v>
+        <v>104.68087162226105</v>
       </c>
       <c r="F55" s="11">
         <f ca="1"/>
-        <v>-0.34913090742528236</v>
+        <v>-5.5999022657134887</v>
       </c>
       <c r="G55" s="8">
         <f ca="1"/>
-        <v>3.0821017018252683E-3</v>
+        <v>5.3494990812845256E-2</v>
       </c>
       <c r="H55" s="11">
         <f ca="1"/>
-        <v>1.0979315256744866</v>
+        <v>20.08267344657455</v>
       </c>
       <c r="I55" s="8">
         <f ca="1"/>
-        <v>-8.5999843090500128E-3</v>
+        <v>-0.1864700101719346</v>
       </c>
       <c r="J55" s="8">
         <f ca="1"/>
-        <v>0.12375201567204841</v>
+        <v>0.56283025036455214</v>
       </c>
       <c r="K55">
         <f ca="1"/>
@@ -6894,7 +3449,7 @@
       </c>
       <c r="C56">
         <f ca="1"/>
-        <v>0.65782831248675533</v>
+        <v>0.26682296351729523</v>
       </c>
       <c r="D56">
         <f ca="1"/>
@@ -6902,27 +3457,27 @@
       </c>
       <c r="E56" s="12">
         <f ca="1"/>
-        <v>113.6423059493936</v>
+        <v>105.09395700872382</v>
       </c>
       <c r="F56" s="11">
         <f ca="1"/>
-        <v>-0.30031722369251124</v>
+        <v>-2.7362221257260768</v>
       </c>
       <c r="G56" s="8">
         <f ca="1"/>
-        <v>2.6426533779264072E-3</v>
+        <v>2.6035960616640819E-2</v>
       </c>
       <c r="H56" s="11">
         <f ca="1"/>
-        <v>0.79761430198197536</v>
+        <v>17.346451320848473</v>
       </c>
       <c r="I56" s="8">
         <f ca="1"/>
-        <v>-5.9573309311236056E-3</v>
+        <v>-0.16043404955529378</v>
       </c>
       <c r="J56" s="8">
         <f ca="1"/>
-        <v>0.12060947766544072</v>
+        <v>0.4858022141489613</v>
       </c>
       <c r="K56">
         <f ca="1"/>
@@ -6939,7 +3494,7 @@
       </c>
       <c r="C57">
         <f ca="1"/>
-        <v>0.64235078789571765</v>
+        <v>0.25425282938647992</v>
       </c>
       <c r="D57">
         <f ca="1"/>
@@ -6947,27 +3502,27 @@
       </c>
       <c r="E57" s="12">
         <f ca="1"/>
-        <v>113.28200661685256</v>
+        <v>104.82169374674926</v>
       </c>
       <c r="F57" s="11">
         <f ca="1"/>
-        <v>-2.7211581806890074E-2</v>
+        <v>0.5727808069488235</v>
       </c>
       <c r="G57" s="8">
         <f ca="1"/>
-        <v>2.402109798330665E-4</v>
+        <v>-5.4643345902487539E-3</v>
       </c>
       <c r="H57" s="11">
         <f ca="1"/>
-        <v>0.77040272017508526</v>
+        <v>17.919232127797297</v>
       </c>
       <c r="I57" s="8">
         <f ca="1"/>
-        <v>-5.7171199512905391E-3</v>
+        <v>-0.16589838414554253</v>
       </c>
       <c r="J57" s="8">
         <f ca="1"/>
-        <v>0.12275590002365067</v>
+        <v>0.52948251181267381</v>
       </c>
       <c r="K57">
         <f ca="1"/>
@@ -6984,7 +3539,7 @@
       </c>
       <c r="C58">
         <f ca="1"/>
-        <v>0.662384765376407</v>
+        <v>0.25542284574852964</v>
       </c>
       <c r="D58">
         <f ca="1"/>
@@ -6992,27 +3547,27 @@
       </c>
       <c r="E58" s="12">
         <f ca="1"/>
-        <v>113.72771642313234</v>
+        <v>104.83783787369809</v>
       </c>
       <c r="F58" s="11">
         <f ca="1"/>
-        <v>-0.24965277233140898</v>
+        <v>-0.8844914107639823</v>
       </c>
       <c r="G58" s="8">
         <f ca="1"/>
-        <v>2.1951796816402913E-3</v>
+        <v>8.4367574599312212E-3</v>
       </c>
       <c r="H58" s="11">
         <f ca="1"/>
-        <v>0.52074994784367634</v>
+        <v>17.034740717033316</v>
       </c>
       <c r="I58" s="8">
         <f ca="1"/>
-        <v>-3.5219402696502478E-3</v>
+        <v>-0.15746162668561131</v>
       </c>
       <c r="J58" s="8">
         <f ca="1"/>
-        <v>0.12020772359768273</v>
+        <v>0.52680422723842568</v>
       </c>
       <c r="K58">
         <f ca="1"/>
@@ -7029,7 +3584,7 @@
       </c>
       <c r="C59">
         <f ca="1"/>
-        <v>0.73119859294068623</v>
+        <v>0.23903040396952602</v>
       </c>
       <c r="D59">
         <f ca="1"/>
@@ -7037,27 +3592,27 @@
       </c>
       <c r="E59" s="12">
         <f ca="1"/>
-        <v>115.29452076302522</v>
+        <v>104.48633181086082</v>
       </c>
       <c r="F59" s="11">
         <f ca="1"/>
-        <v>-0.28890373722610768</v>
+        <v>0.95933538367490601</v>
       </c>
       <c r="G59" s="8">
         <f ca="1"/>
-        <v>2.5057889595631044E-3</v>
+        <v>-9.1814438027308376E-3</v>
       </c>
       <c r="H59" s="11">
         <f ca="1"/>
-        <v>0.23184621061756866</v>
+        <v>17.99407610070822</v>
       </c>
       <c r="I59" s="8">
         <f ca="1"/>
-        <v>-1.0161513100871433E-3</v>
+        <v>-0.16664307048834215</v>
       </c>
       <c r="J59" s="8">
         <f ca="1"/>
-        <v>0.11468953229835124</v>
+        <v>0.58215294368263315</v>
       </c>
       <c r="K59">
         <f ca="1"/>
@@ -7074,7 +3629,7 @@
       </c>
       <c r="C60">
         <f ca="1"/>
-        <v>0.79290798755025516</v>
+        <v>0.25917663718609779</v>
       </c>
       <c r="D60">
         <f ca="1"/>
@@ -7082,27 +3637,27 @@
       </c>
       <c r="E60" s="12">
         <f ca="1"/>
-        <v>116.71695122980141</v>
+        <v>104.89978999282914</v>
       </c>
       <c r="F60" s="11">
         <f ca="1"/>
-        <v>-8.9221093316398575E-2</v>
+        <v>-3.065651046076483</v>
       </c>
       <c r="G60" s="8">
         <f ca="1"/>
-        <v>7.6442275416133132E-4</v>
+        <v>2.9224568002338691E-2</v>
       </c>
       <c r="H60" s="11">
         <f ca="1"/>
-        <v>0.14262511730117008</v>
+        <v>14.928425054631738</v>
       </c>
       <c r="I60" s="8">
         <f ca="1"/>
-        <v>-2.51728555925812E-4</v>
+        <v>-0.13741850248600346</v>
       </c>
       <c r="J60" s="8">
         <f ca="1"/>
-        <v>0.11324412771602875</v>
+        <v>0.51325300272090679</v>
       </c>
       <c r="K60">
         <f ca="1"/>
@@ -7119,7 +3674,7 @@
       </c>
       <c r="C61">
         <f ca="1"/>
-        <v>0.78282330367305986</v>
+        <v>0.22153407632619898</v>
       </c>
       <c r="D61">
         <f ca="1"/>
@@ -7127,27 +3682,27 @@
       </c>
       <c r="E61" s="12">
         <f ca="1"/>
-        <v>116.47245959379066</v>
+        <v>104.10468727385663</v>
       </c>
       <c r="F61" s="11">
         <f ca="1"/>
-        <v>-9.0218533686409544E-3</v>
+        <v>3.2585188807843708</v>
       </c>
       <c r="G61" s="8">
         <f ca="1"/>
-        <v>7.7459112652944473E-5</v>
+        <v>-3.1300405064495773E-2</v>
       </c>
       <c r="H61" s="11">
         <f ca="1"/>
-        <v>0.13360326393252914</v>
+        <v>18.18694393541611</v>
       </c>
       <c r="I61" s="8">
         <f ca="1"/>
-        <v>-1.7426944327286753E-4</v>
+        <v>-0.16871890755049923</v>
       </c>
       <c r="J61" s="8">
         <f ca="1"/>
-        <v>0.11330567324249768</v>
+        <v>0.62251482768466104</v>
       </c>
       <c r="K61">
         <f ca="1"/>
@@ -7164,7 +3719,7 @@
       </c>
       <c r="C62">
         <f ca="1"/>
-        <v>0.71992655556273177</v>
+        <v>0.34986740327129229</v>
       </c>
       <c r="D62">
         <f ca="1"/>
@@ -7172,27 +3727,27 @@
       </c>
       <c r="E62" s="12">
         <f ca="1"/>
-        <v>115.00728763570127</v>
+        <v>106.80274907979674</v>
       </c>
       <c r="F62" s="11">
         <f ca="1"/>
-        <v>1.4425882091699987E-2</v>
+        <v>-12.470615196331172</v>
       </c>
       <c r="G62" s="8">
         <f ca="1"/>
-        <v>-1.2543450409330248E-4</v>
+        <v>0.11676305435746659</v>
       </c>
       <c r="H62" s="11">
         <f ca="1"/>
-        <v>0.14802914602422912</v>
+        <v>5.716328739084938</v>
       </c>
       <c r="I62" s="8">
         <f ca="1"/>
-        <v>-2.9970394736617001E-4</v>
+        <v>-5.1955853193032642E-2</v>
       </c>
       <c r="J62" s="8">
         <f ca="1"/>
-        <v>0.11356100794393292</v>
+        <v>0.16730078728271636</v>
       </c>
       <c r="K62">
         <f ca="1"/>
@@ -7209,7 +3764,7 @@
       </c>
       <c r="C63">
         <f ca="1"/>
-        <v>0.77959706827084396</v>
+        <v>0.30804756201138606</v>
       </c>
       <c r="D63">
         <f ca="1"/>
@@ -7217,27 +3772,27 @@
       </c>
       <c r="E63" s="12">
         <f ca="1"/>
-        <v>116.37870823731966</v>
+        <v>105.90470691302096</v>
       </c>
       <c r="F63" s="11">
         <f ca="1"/>
-        <v>-2.9508249996014063E-2</v>
+        <v>1.6972433372242102</v>
       </c>
       <c r="G63" s="8">
         <f ca="1"/>
-        <v>2.5355368213780816E-4</v>
+        <v>-1.6026136955538228E-2</v>
       </c>
       <c r="H63" s="11">
         <f ca="1"/>
-        <v>0.11852089602821506</v>
+        <v>7.4135720763091477</v>
       </c>
       <c r="I63" s="8">
         <f ca="1"/>
-        <v>-4.6150265228361853E-5</v>
+        <v>-6.798199014857087E-2</v>
       </c>
       <c r="J63" s="8">
         <f ca="1"/>
-        <v>0.11314998777612861</v>
+        <v>0.21395933426087144</v>
       </c>
       <c r="K63">
         <f ca="1"/>
@@ -7254,7 +3809,7 @@
       </c>
       <c r="C64">
         <f ca="1"/>
-        <v>0.78364741119686943</v>
+        <v>0.35157195070483821</v>
       </c>
       <c r="D64">
         <f ca="1"/>
@@ -7262,27 +3817,27 @@
       </c>
       <c r="E64" s="12">
         <f ca="1"/>
-        <v>116.46370369867336</v>
+        <v>106.82207245815043</v>
       </c>
       <c r="F64" s="11">
         <f ca="1"/>
-        <v>-3.4490708131105518E-3</v>
+        <v>-3.4905051893575996</v>
       </c>
       <c r="G64" s="8">
         <f ca="1"/>
-        <v>2.9614984785597542E-5</v>
+        <v>3.2675879703841837E-2</v>
       </c>
       <c r="H64" s="11">
         <f ca="1"/>
-        <v>0.11507182521510451</v>
+        <v>3.9230668869515481</v>
       </c>
       <c r="I64" s="8">
         <f ca="1"/>
-        <v>-1.6535280442764311E-5</v>
+        <v>-3.5306110444729033E-2</v>
       </c>
       <c r="J64" s="8">
         <f ca="1"/>
-        <v>0.11314606521304393</v>
+        <v>0.15159499880924177</v>
       </c>
       <c r="K64">
         <f ca="1"/>
@@ -7299,7 +3854,7 @@
       </c>
       <c r="C65">
         <f ca="1"/>
-        <v>0.78852309851795421</v>
+        <v>0.46611710373429643</v>
       </c>
       <c r="D65">
         <f ca="1"/>
@@ -7307,27 +3862,27 @@
       </c>
       <c r="E65" s="12">
         <f ca="1"/>
-        <v>116.56800139649965</v>
+        <v>109.28876580006653</v>
       </c>
       <c r="F65" s="11">
         <f ca="1"/>
-        <v>-1.4100528374403826E-3</v>
+        <v>-3.3209073419850448</v>
       </c>
       <c r="G65" s="8">
         <f ca="1"/>
-        <v>1.2096397129124359E-5</v>
+        <v>3.0386538979315869E-2</v>
       </c>
       <c r="H65" s="11">
         <f ca="1"/>
-        <v>0.11366177237766413</v>
+        <v>0.60215954496650337</v>
       </c>
       <c r="I65" s="8">
         <f ca="1"/>
-        <v>-4.4388833136399519E-6</v>
+        <v>-4.9195714654131639E-3</v>
       </c>
       <c r="J65" s="8">
         <f ca="1"/>
-        <v>0.11314434062136085</v>
+        <v>6.4505651246274054E-2</v>
       </c>
       <c r="K65">
         <f ca="1"/>
@@ -7344,7 +3899,7 @@
       </c>
       <c r="C66">
         <f ca="1"/>
-        <v>0.82432001732875915</v>
+        <v>0.49721089244020522</v>
       </c>
       <c r="D66">
         <f ca="1"/>
@@ -7352,27 +3907,27 @@
       </c>
       <c r="E66" s="12">
         <f ca="1"/>
-        <v>117.39615897666158</v>
+        <v>109.96172651520659</v>
       </c>
       <c r="F66" s="11">
         <f ca="1"/>
-        <v>-4.855600434212416E-4</v>
+        <v>-0.37224789265676761</v>
       </c>
       <c r="G66" s="8">
         <f ca="1"/>
-        <v>4.1360811772195305E-6</v>
+        <v>3.3852496177866898E-3</v>
       </c>
       <c r="H66" s="11">
         <f ca="1"/>
-        <v>0.1131762123342429</v>
+        <v>0.22991165230973576</v>
       </c>
       <c r="I66" s="8">
         <f ca="1"/>
-        <v>-3.0280213642042142E-7</v>
+        <v>-1.5343218476264742E-3</v>
       </c>
       <c r="J66" s="8">
         <f ca="1"/>
-        <v>0.11314066452649721</v>
+        <v>6.1194972914726919E-2</v>
       </c>
       <c r="K66">
         <f ca="1"/>
@@ -7389,7 +3944,7 @@
       </c>
       <c r="C67">
         <f ca="1"/>
-        <v>0.66729348735168936</v>
+        <v>0.52923357277271632</v>
       </c>
       <c r="D67">
         <f ca="1"/>
@@ -7397,27 +3952,27 @@
       </c>
       <c r="E67" s="12">
         <f ca="1"/>
-        <v>113.7574879115588</v>
+        <v>110.65938728531806</v>
       </c>
       <c r="F67" s="11">
         <f ca="1"/>
-        <v>7.0531051471193237E-4</v>
+        <v>-0.13629339697629025</v>
       </c>
       <c r="G67" s="8">
         <f ca="1"/>
-        <v>-6.2001238569919792E-6</v>
+        <v>1.2316478549160847E-3</v>
       </c>
       <c r="H67" s="11">
         <f ca="1"/>
-        <v>0.11388152284895482</v>
+        <v>9.3618255333445505E-2</v>
       </c>
       <c r="I67" s="8">
         <f ca="1"/>
-        <v>-6.5029259934124006E-6</v>
+        <v>-3.0267399271038942E-4</v>
       </c>
       <c r="J67" s="8">
         <f ca="1"/>
-        <v>0.11314176632386945</v>
+        <v>6.0124536752912988E-2</v>
       </c>
       <c r="K67">
         <f ca="1"/>
@@ -7434,7 +3989,7 @@
       </c>
       <c r="C68">
         <f ca="1"/>
-        <v>0.7662468424471256</v>
+        <v>0.4937014162954958</v>
       </c>
       <c r="D68">
         <f ca="1"/>
@@ -7442,27 +3997,27 @@
       </c>
       <c r="E68" s="12">
         <f ca="1"/>
-        <v>116.02196823097711</v>
+        <v>109.86699185929547</v>
       </c>
       <c r="F68" s="11">
         <f ca="1"/>
-        <v>-7.5284168315564899E-4</v>
+        <v>-9.5767088279430455E-3</v>
       </c>
       <c r="G68" s="8">
         <f ca="1"/>
-        <v>6.4887856552897638E-6</v>
+        <v>8.7166387882975371E-5</v>
       </c>
       <c r="H68" s="11">
         <f ca="1"/>
-        <v>0.11312868116579917</v>
+        <v>8.4041546505502454E-2</v>
       </c>
       <c r="I68" s="8">
         <f ca="1"/>
-        <v>-1.414033812263682E-8</v>
+        <v>-2.1550760482741405E-4</v>
       </c>
       <c r="J68" s="8">
         <f ca="1"/>
-        <v>0.11312704057593874</v>
+        <v>6.0364374240312692E-2</v>
       </c>
       <c r="K68">
         <f ca="1"/>
@@ -7479,7 +4034,7 @@
       </c>
       <c r="C69">
         <f ca="1"/>
-        <v>0.8004005467730847</v>
+        <v>0.44571247597793906</v>
       </c>
       <c r="D69">
         <f ca="1"/>
@@ -7487,27 +4042,27 @@
       </c>
       <c r="E69" s="12">
         <f ca="1"/>
-        <v>116.80785213792116</v>
+        <v>108.80885088767852</v>
       </c>
       <c r="F69" s="11">
         <f ca="1"/>
-        <v>-1.648898841546027E-6</v>
+        <v>-4.7083683763562796E-3</v>
       </c>
       <c r="G69" s="8">
         <f ca="1"/>
-        <v>1.4116335600444785E-8</v>
+        <v>4.3271924461518729E-5</v>
       </c>
       <c r="H69" s="11">
         <f ca="1"/>
-        <v>0.11312703226695763</v>
+        <v>7.933317812914617E-2</v>
       </c>
       <c r="I69" s="8">
         <f ca="1"/>
-        <v>-2.4002522192034803E-11</v>
+        <v>-1.7223568036589532E-4</v>
       </c>
       <c r="J69" s="8">
         <f ca="1"/>
-        <v>0.11312702946327456</v>
+        <v>6.0592411666675609E-2</v>
       </c>
       <c r="K69">
         <f ca="1"/>
@@ -7524,7 +4079,7 @@
       </c>
       <c r="C70">
         <f ca="1"/>
-        <v>0.79221234774450988</v>
+        <v>0.31190112515968615</v>
       </c>
       <c r="D70">
         <f ca="1"/>
@@ -7532,27 +4087,27 @@
       </c>
       <c r="E70" s="12">
         <f ca="1"/>
-        <v>116.60739053117157</v>
+        <v>105.92702472354769</v>
       </c>
       <c r="F70" s="11">
         <f ca="1"/>
-        <v>-2.7980299876159553E-9</v>
+        <v>0.18643585876324351</v>
       </c>
       <c r="G70" s="8">
         <f ca="1"/>
-        <v>2.399530574237474E-11</v>
+        <v>-1.7600405491404181E-3</v>
       </c>
       <c r="H70" s="11">
         <f ca="1"/>
-        <v>0.11312702946892764</v>
+        <v>0.26576903689238968</v>
       </c>
       <c r="I70" s="8">
         <f ca="1"/>
-        <v>-7.2164496600635175E-15</v>
+        <v>-1.9322762295063134E-3</v>
       </c>
       <c r="J70" s="8">
         <f ca="1"/>
-        <v>0.11312702946808614</v>
+        <v>6.1088764956750918E-2</v>
       </c>
       <c r="K70">
         <f ca="1"/>
@@ -7569,7 +4124,7 @@
       </c>
       <c r="C71">
         <f ca="1"/>
-        <v>0.78814415576952479</v>
+        <v>0.34974236315913937</v>
       </c>
       <c r="D71">
         <f ca="1"/>
@@ -7577,27 +4132,27 @@
       </c>
       <c r="E71" s="12">
         <f ca="1"/>
-        <v>116.50323223670969</v>
+        <v>106.72320980729164</v>
       </c>
       <c r="F71" s="11">
         <f ca="1"/>
-        <v>-8.4073971067090469E-13</v>
+        <v>-0.20484328675106836</v>
       </c>
       <c r="G71" s="8">
         <f ca="1"/>
-        <v>7.2164496600635175E-15</v>
+        <v>1.9193883609849305E-3</v>
       </c>
       <c r="H71" s="11">
         <f ca="1"/>
-        <v>0.11312702946808689</v>
+        <v>6.0925750141321316E-2</v>
       </c>
       <c r="I71" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>-1.2887868521382906E-5</v>
       </c>
       <c r="J71" s="8">
         <f ca="1"/>
-        <v>0.11312702946808689</v>
+        <v>5.9550315445144976E-2</v>
       </c>
       <c r="K71">
         <f ca="1"/>
@@ -7614,7 +4169,7 @@
       </c>
       <c r="C72">
         <f ca="1"/>
-        <v>0.78714587266686697</v>
+        <v>0.32523252431649596</v>
       </c>
       <c r="D72">
         <f ca="1"/>
@@ -7622,15 +4177,15 @@
       </c>
       <c r="E72" s="12">
         <f ca="1"/>
-        <v>116.47065589180895</v>
+        <v>106.19284045436892</v>
       </c>
       <c r="F72" s="11">
         <f ca="1"/>
-        <v>-0.11312702946808689</v>
+        <v>-6.0925750141321316E-2</v>
       </c>
       <c r="G72" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1.2887868521382906E-5</v>
       </c>
       <c r="H72" s="11">
         <f ca="1"/>
@@ -7646,7 +4201,7 @@
       </c>
       <c r="K72">
         <f ca="1"/>
-        <v>0.11312702946808689</v>
+        <v>5.9557150775633221E-2</v>
       </c>
       <c r="L72">
         <f ca="1"/>
@@ -8408,8 +4963,7 @@
     <mergeCell ref="H8:I8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8428,7 +4982,7 @@
     <row r="1" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="18" cm="1">
         <f t="array" aca="1" ref="B1" ca="1">_xll.MONTE.COUNT()</f>
-        <v>30423</v>
+        <v>10441</v>
       </c>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -8478,7 +5032,7 @@
       </c>
       <c r="G3" s="8" cm="1">
         <f t="array" aca="1" ref="G3" ca="1">_xlfn.TAKE(S_,-1)</f>
-        <v>86.096052238557803</v>
+        <v>97.017723233977435</v>
       </c>
       <c r="N3" s="7">
         <v>1</v>
@@ -8504,15 +5058,15 @@
       </c>
       <c r="G4" s="11">
         <f ca="1">MAX(k - last,0)</f>
-        <v>13.903947761442197</v>
+        <v>2.9822767660225651</v>
       </c>
       <c r="H4" s="11">
         <f t="array" aca="1" ref="H4:I4" ca="1">_xll.MONTE.STDEV(G4)</f>
-        <v>3.9910715169122772</v>
+        <v>3.9698955412770243</v>
       </c>
       <c r="I4" s="11">
         <f ca="1"/>
-        <v>5.477247715942906</v>
+        <v>5.4744558475318081</v>
       </c>
       <c r="M4">
         <v>1E-3</v>
@@ -8539,7 +5093,7 @@
       </c>
       <c r="G5" s="11" cm="1">
         <f t="array" aca="1" ref="G5" ca="1">_xlfn.TAKE(A,-1)</f>
-        <v>-6.0750531706379434</v>
+        <v>1.7754076462248207</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
@@ -8569,19 +5123,19 @@
       </c>
       <c r="G6" s="11">
         <f ca="1">payoff-hedge</f>
-        <v>19.97900093208014</v>
+        <v>1.2068691197977444</v>
       </c>
       <c r="H6" s="8">
         <f t="array" aca="1" ref="H6:I6" ca="1">_xll.MONTE.STDEV(error)</f>
-        <v>1.1384613596372654E-2</v>
+        <v>-4.9406313496674494E-2</v>
       </c>
       <c r="I6" s="13">
         <f ca="1"/>
-        <v>11.977489491704732</v>
+        <v>11.9850450694938</v>
       </c>
       <c r="J6" s="17">
         <f ca="1">I6/put</f>
-        <v>3.0035623970654042</v>
+        <v>3.0054570887160263</v>
       </c>
       <c r="K6" s="16" t="s">
         <v>30</v>
@@ -8713,7 +5267,7 @@
       </c>
       <c r="C11">
         <f ca="1"/>
-        <v>7.6313612401421163E-2</v>
+        <v>-3.6216919301546975E-2</v>
       </c>
       <c r="D11">
         <f ca="1"/>
@@ -8721,27 +5275,27 @@
       </c>
       <c r="E11" s="12">
         <f ca="1"/>
-        <v>101.52985655397329</v>
+        <v>99.270336677371986</v>
       </c>
       <c r="F11" s="11">
         <f ca="1"/>
-        <v>101.52985655397329</v>
+        <v>0</v>
       </c>
       <c r="G11" s="8">
         <f ca="1"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="11">
         <f ca="1"/>
-        <v>5.5176177216477811</v>
+        <v>-96.012238832325508</v>
       </c>
       <c r="I11" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="8">
         <f ca="1"/>
-        <v>5.5176177216477811</v>
+        <v>3.2580978450464784</v>
       </c>
       <c r="K11">
         <f ca="1"/>
@@ -8749,11 +5303,11 @@
       </c>
       <c r="L11">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.72966332262801359</v>
       </c>
       <c r="M11" s="22">
         <f ca="1" xml:space="preserve"> - G11*E11</f>
-        <v>101.52985655397329</v>
+        <v>0</v>
       </c>
       <c r="N11" s="22">
         <f ca="1">F11-M11</f>
@@ -8766,7 +5320,7 @@
       </c>
       <c r="C12">
         <f ca="1"/>
-        <v>-7.9193757865060332E-3</v>
+        <v>-4.9262360379045494E-2</v>
       </c>
       <c r="D12">
         <f ca="1"/>
@@ -8774,19 +5328,19 @@
       </c>
       <c r="E12" s="12">
         <f ca="1"/>
-        <v>99.825764450948284</v>
+        <v>99.003748584958885</v>
       </c>
       <c r="F12" s="11">
         <f ca="1"/>
-        <v>-99.825764450948284</v>
+        <v>0</v>
       </c>
       <c r="G12" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>-96.012238832325508</v>
       </c>
       <c r="I12" s="8">
         <f ca="1"/>
@@ -8794,7 +5348,7 @@
       </c>
       <c r="J12" s="8">
         <f ca="1"/>
-        <v>5.5176177216477811</v>
+        <v>2.9915097526333767</v>
       </c>
       <c r="K12">
         <f ca="1"/>
@@ -8802,7 +5356,7 @@
       </c>
       <c r="L12">
         <f ca="1"/>
-        <v>0.17423554905171557</v>
+        <v>0.99625141504111525</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -8811,7 +5365,7 @@
       </c>
       <c r="C13">
         <f ca="1"/>
-        <v>-3.6669109387069514E-2</v>
+        <v>-0.12832838464763496</v>
       </c>
       <c r="D13">
         <f ca="1"/>
@@ -8819,7 +5373,7 @@
       </c>
       <c r="E13" s="12">
         <f ca="1"/>
-        <v>99.245478723915411</v>
+        <v>97.442699622045964</v>
       </c>
       <c r="F13" s="11">
         <f ca="1"/>
@@ -8831,7 +5385,7 @@
       </c>
       <c r="H13" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>-96.012238832325508</v>
       </c>
       <c r="I13" s="8">
         <f ca="1"/>
@@ -8839,7 +5393,7 @@
       </c>
       <c r="J13" s="8">
         <f ca="1"/>
-        <v>4.9373319946149081</v>
+        <v>1.4304607897204562</v>
       </c>
       <c r="K13">
         <f ca="1"/>
@@ -8847,7 +5401,7 @@
       </c>
       <c r="L13">
         <f ca="1"/>
-        <v>0.75452127608458852</v>
+        <v>2.5573003779540358</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -8856,7 +5410,7 @@
       </c>
       <c r="C14">
         <f ca="1"/>
-        <v>-0.1003255401829648</v>
+        <v>-8.0617468857331481E-2</v>
       </c>
       <c r="D14">
         <f ca="1"/>
@@ -8864,7 +5418,7 @@
       </c>
       <c r="E14" s="12">
         <f ca="1"/>
-        <v>97.982126359662786</v>
+        <v>98.369096248659488</v>
       </c>
       <c r="F14" s="11">
         <f ca="1"/>
@@ -8876,7 +5430,7 @@
       </c>
       <c r="H14" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>-96.012238832325508</v>
       </c>
       <c r="I14" s="8">
         <f ca="1"/>
@@ -8884,7 +5438,7 @@
       </c>
       <c r="J14" s="8">
         <f ca="1"/>
-        <v>3.6739796303622825</v>
+        <v>2.3568574163339804</v>
       </c>
       <c r="K14">
         <f ca="1"/>
@@ -8892,11 +5446,11 @@
       </c>
       <c r="L14">
         <f ca="1"/>
-        <v>2.0178736403372142</v>
+        <v>1.6309037513405116</v>
       </c>
       <c r="M14" s="22">
         <f ca="1">f*EXP(sigma*C14-sigma^2*B14/2)</f>
-        <v>97.982126359662786</v>
+        <v>98.369096248659488</v>
       </c>
       <c r="N14" s="23">
         <f ca="1">E14-M14</f>
@@ -8909,7 +5463,7 @@
       </c>
       <c r="C15">
         <f ca="1"/>
-        <v>-2.9050393242552569E-2</v>
+        <v>-3.3911359535823374E-2</v>
       </c>
       <c r="D15">
         <f ca="1"/>
@@ -8917,7 +5471,7 @@
       </c>
       <c r="E15" s="12">
         <f ca="1"/>
-        <v>99.380916403643226</v>
+        <v>99.284345896880779</v>
       </c>
       <c r="F15" s="11">
         <f ca="1"/>
@@ -8929,7 +5483,7 @@
       </c>
       <c r="H15" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>-96.012238832325508</v>
       </c>
       <c r="I15" s="8">
         <f ca="1"/>
@@ -8937,7 +5491,7 @@
       </c>
       <c r="J15" s="8">
         <f ca="1"/>
-        <v>5.0727696743427231</v>
+        <v>3.2721070645552714</v>
       </c>
       <c r="K15">
         <f ca="1"/>
@@ -8945,7 +5499,7 @@
       </c>
       <c r="L15">
         <f ca="1"/>
-        <v>0.61908359635677357</v>
+        <v>0.71565410311922051</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -8954,7 +5508,7 @@
       </c>
       <c r="C16">
         <f ca="1"/>
-        <v>-7.5248747822205496E-3</v>
+        <v>-2.5490900654778791E-2</v>
       </c>
       <c r="D16">
         <f ca="1"/>
@@ -8962,7 +5516,7 @@
       </c>
       <c r="E16" s="12">
         <f ca="1"/>
-        <v>99.801699380348296</v>
+        <v>99.4437349027599</v>
       </c>
       <c r="F16" s="11">
         <f ca="1"/>
@@ -8974,7 +5528,7 @@
       </c>
       <c r="H16" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>-96.012238832325508</v>
       </c>
       <c r="I16" s="8">
         <f ca="1"/>
@@ -8982,7 +5536,7 @@
       </c>
       <c r="J16" s="8">
         <f ca="1"/>
-        <v>5.4935526510477928</v>
+        <v>3.4314960704343918</v>
       </c>
       <c r="K16">
         <f ca="1"/>
@@ -8990,15 +5544,15 @@
       </c>
       <c r="L16">
         <f ca="1"/>
-        <v>0.19830061965170387</v>
+        <v>0.5562650972401002</v>
       </c>
       <c r="M16" s="22" cm="1">
         <f t="array" aca="1" ref="M16" ca="1">_xll.OPTION.BLACK.PUT_DELTA(E16,sigma*SQRT(t - B16),k)</f>
-        <v>-0.48936453085623854</v>
+        <v>-0.50443993372722107</v>
       </c>
       <c r="N16" s="23">
         <f ca="1">I16-M16</f>
-        <v>1.4893645308562387</v>
+        <v>1.504439933727221</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -9007,7 +5561,7 @@
       </c>
       <c r="C17">
         <f ca="1"/>
-        <v>-6.7718696118700308E-2</v>
+        <v>3.031388143083983E-2</v>
       </c>
       <c r="D17">
         <f ca="1"/>
@@ -9015,27 +5569,27 @@
       </c>
       <c r="E17" s="12">
         <f ca="1"/>
-        <v>98.599525257501</v>
+        <v>100.55179443690217</v>
       </c>
       <c r="F17" s="11">
         <f ca="1"/>
-        <v>0</v>
+        <v>100.55179443690217</v>
       </c>
       <c r="G17" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H17" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I17" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="8">
         <f ca="1"/>
-        <v>4.2913785282004966</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K17">
         <f ca="1"/>
@@ -9043,7 +5597,7 @@
       </c>
       <c r="L17">
         <f ca="1"/>
-        <v>1.4004747424990001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -9052,7 +5606,7 @@
       </c>
       <c r="C18">
         <f ca="1"/>
-        <v>-0.14795811138683448</v>
+        <v>4.3245171878774545E-2</v>
       </c>
       <c r="D18">
         <f ca="1"/>
@@ -9060,7 +5614,7 @@
       </c>
       <c r="E18" s="12">
         <f ca="1"/>
-        <v>97.022078277361516</v>
+        <v>100.80411924860448</v>
       </c>
       <c r="F18" s="11">
         <f ca="1"/>
@@ -9072,15 +5626,15 @@
       </c>
       <c r="H18" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I18" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="8">
         <f ca="1"/>
-        <v>2.7139315480610122</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K18">
         <f ca="1"/>
@@ -9088,7 +5642,7 @@
       </c>
       <c r="L18">
         <f ca="1"/>
-        <v>2.9779217226384844</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -9097,7 +5651,7 @@
       </c>
       <c r="C19">
         <f ca="1"/>
-        <v>-0.12309814732047163</v>
+        <v>0.1356757314912205</v>
       </c>
       <c r="D19">
         <f ca="1"/>
@@ -9105,7 +5659,7 @@
       </c>
       <c r="E19" s="12">
         <f ca="1"/>
-        <v>97.497872428932524</v>
+        <v>102.67671185742864</v>
       </c>
       <c r="F19" s="11">
         <f ca="1"/>
@@ -9117,15 +5671,15 @@
       </c>
       <c r="H19" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I19" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="8">
         <f ca="1"/>
-        <v>3.1897256996320209</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K19">
         <f ca="1"/>
@@ -9133,7 +5687,7 @@
       </c>
       <c r="L19">
         <f ca="1"/>
-        <v>2.5021275710674757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -9142,7 +5696,7 @@
       </c>
       <c r="C20">
         <f ca="1"/>
-        <v>-0.16134882216504773</v>
+        <v>0.14965677803554564</v>
       </c>
       <c r="D20">
         <f ca="1"/>
@@ -9150,7 +5704,7 @@
       </c>
       <c r="E20" s="12">
         <f ca="1"/>
-        <v>96.747106216449453</v>
+        <v>102.95598240490982</v>
       </c>
       <c r="F20" s="11">
         <f ca="1"/>
@@ -9162,15 +5716,15 @@
       </c>
       <c r="H20" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I20" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="8">
         <f ca="1"/>
-        <v>2.4389594871489493</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K20">
         <f ca="1"/>
@@ -9178,18 +5732,18 @@
       </c>
       <c r="L20">
         <f ca="1"/>
-        <v>3.2528937835505474</v>
+        <v>0</v>
       </c>
       <c r="M20" s="7">
         <f t="array" aca="1" ref="M20:M21" ca="1">_xll.MONTE.STDEV(C20)</f>
-        <v>1.8371037544200202E-3</v>
+        <v>2.9585807742571026E-3</v>
       </c>
       <c r="N20" s="7">
         <v>0</v>
       </c>
       <c r="O20" s="7">
         <f t="array" aca="1" ref="O20:O21" ca="1">_xll.MONTE.STDEV(E20)</f>
-        <v>100.03623890021302</v>
+        <v>100.05839124834462</v>
       </c>
       <c r="P20" s="7">
         <f>f*EXP(mu*B20)</f>
@@ -9202,7 +5756,7 @@
       </c>
       <c r="C21">
         <f ca="1"/>
-        <v>-0.10568963358868332</v>
+        <v>0.31472117443703507</v>
       </c>
       <c r="D21">
         <f ca="1"/>
@@ -9210,7 +5764,7 @@
       </c>
       <c r="E21" s="12">
         <f ca="1"/>
-        <v>97.822269857182391</v>
+        <v>106.4030690424518</v>
       </c>
       <c r="F21" s="11">
         <f ca="1"/>
@@ -9222,15 +5776,15 @@
       </c>
       <c r="H21" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I21" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="8">
         <f ca="1"/>
-        <v>3.5141231278818879</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K21">
         <f ca="1"/>
@@ -9238,11 +5792,11 @@
       </c>
       <c r="L21">
         <f ca="1"/>
-        <v>2.1777301428176088</v>
+        <v>0</v>
       </c>
       <c r="M21" s="7">
         <f ca="1"/>
-        <v>0.19933976469065384</v>
+        <v>0.19902845775862468</v>
       </c>
       <c r="N21" s="7">
         <f>SQRT(B20)</f>
@@ -9250,7 +5804,7 @@
       </c>
       <c r="O21" s="7">
         <f ca="1"/>
-        <v>3.9913633252644436</v>
+        <v>3.983453566034624</v>
       </c>
       <c r="P21" s="7"/>
     </row>
@@ -9260,7 +5814,7 @@
       </c>
       <c r="C22">
         <f ca="1"/>
-        <v>-0.16162022515137464</v>
+        <v>0.31939169557978364</v>
       </c>
       <c r="D22">
         <f ca="1"/>
@@ -9268,7 +5822,7 @@
       </c>
       <c r="E22" s="12">
         <f ca="1"/>
-        <v>96.726377409715553</v>
+        <v>106.4939871749053</v>
       </c>
       <c r="F22" s="11">
         <f ca="1"/>
@@ -9280,15 +5834,15 @@
       </c>
       <c r="H22" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I22" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="8">
         <f ca="1"/>
-        <v>2.41823068041505</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K22">
         <f ca="1"/>
@@ -9296,7 +5850,7 @@
       </c>
       <c r="L22">
         <f ca="1"/>
-        <v>3.2736225902844467</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -9305,7 +5859,7 @@
       </c>
       <c r="C23">
         <f ca="1"/>
-        <v>-0.11431820583864011</v>
+        <v>0.24833381140025479</v>
       </c>
       <c r="D23">
         <f ca="1"/>
@@ -9313,7 +5867,7 @@
       </c>
       <c r="E23" s="12">
         <f ca="1"/>
-        <v>97.637978804142932</v>
+        <v>104.98284420329796</v>
       </c>
       <c r="F23" s="11">
         <f ca="1"/>
@@ -9325,15 +5879,15 @@
       </c>
       <c r="H23" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I23" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="8">
         <f ca="1"/>
-        <v>3.3298320748424288</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K23">
         <f ca="1"/>
@@ -9341,7 +5895,7 @@
       </c>
       <c r="L23">
         <f ca="1"/>
-        <v>2.3620211958570678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -9350,7 +5904,7 @@
       </c>
       <c r="C24">
         <f ca="1"/>
-        <v>-7.5210096106383517E-2</v>
+        <v>0.1633192532085081</v>
       </c>
       <c r="D24">
         <f ca="1"/>
@@ -9358,7 +5912,7 @@
       </c>
       <c r="E24" s="12">
         <f ca="1"/>
-        <v>98.396788542933834</v>
+        <v>103.20466305104242</v>
       </c>
       <c r="F24" s="11">
         <f ca="1"/>
@@ -9370,15 +5924,15 @@
       </c>
       <c r="H24" s="11">
         <f ca="1"/>
-        <v>-94.308146729300503</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I24" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="8">
         <f ca="1"/>
-        <v>4.0886418136333305</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K24">
         <f ca="1"/>
@@ -9386,7 +5940,7 @@
       </c>
       <c r="L24">
         <f ca="1"/>
-        <v>1.6032114570661662</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -9395,7 +5949,7 @@
       </c>
       <c r="C25">
         <f ca="1"/>
-        <v>7.7832522407885935E-2</v>
+        <v>0.17079689730935149</v>
       </c>
       <c r="D25">
         <f ca="1"/>
@@ -9403,19 +5957,19 @@
       </c>
       <c r="E25" s="12">
         <f ca="1"/>
-        <v>101.44701986864344</v>
+        <v>103.35085567148994</v>
       </c>
       <c r="F25" s="11">
         <f ca="1"/>
-        <v>101.44701986864344</v>
+        <v>0</v>
       </c>
       <c r="G25" s="8">
         <f ca="1"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="11">
         <f ca="1"/>
-        <v>7.1388731393429339</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I25" s="8">
         <f ca="1"/>
@@ -9423,7 +5977,7 @@
       </c>
       <c r="J25" s="8">
         <f ca="1"/>
-        <v>7.1388731393429339</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K25">
         <f ca="1"/>
@@ -9440,7 +5994,7 @@
       </c>
       <c r="C26">
         <f ca="1"/>
-        <v>9.8509275712634334E-2</v>
+        <v>0.19966931204600219</v>
       </c>
       <c r="D26">
         <f ca="1"/>
@@ -9448,7 +6002,7 @@
       </c>
       <c r="E26" s="12">
         <f ca="1"/>
-        <v>101.85925842870935</v>
+        <v>103.94106422808677</v>
       </c>
       <c r="F26" s="11">
         <f ca="1"/>
@@ -9460,7 +6014,7 @@
       </c>
       <c r="H26" s="11">
         <f ca="1"/>
-        <v>7.1388731393429339</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I26" s="8">
         <f ca="1"/>
@@ -9468,7 +6022,7 @@
       </c>
       <c r="J26" s="8">
         <f ca="1"/>
-        <v>7.1388731393429339</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K26">
         <f ca="1"/>
@@ -9485,7 +6039,7 @@
       </c>
       <c r="C27">
         <f ca="1"/>
-        <v>9.3279914683090076E-2</v>
+        <v>0.17633628352928335</v>
       </c>
       <c r="D27">
         <f ca="1"/>
@@ -9493,7 +6047,7 @@
       </c>
       <c r="E27" s="12">
         <f ca="1"/>
-        <v>101.7446424543071</v>
+        <v>103.44886603928782</v>
       </c>
       <c r="F27" s="11">
         <f ca="1"/>
@@ -9505,7 +6059,7 @@
       </c>
       <c r="H27" s="11">
         <f ca="1"/>
-        <v>7.1388731393429339</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I27" s="8">
         <f ca="1"/>
@@ -9513,7 +6067,7 @@
       </c>
       <c r="J27" s="8">
         <f ca="1"/>
-        <v>7.1388731393429339</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K27">
         <f ca="1"/>
@@ -9530,7 +6084,7 @@
       </c>
       <c r="C28">
         <f ca="1"/>
-        <v>7.938094075644711E-2</v>
+        <v>0.20482052907356457</v>
       </c>
       <c r="D28">
         <f ca="1"/>
@@ -9538,7 +6092,7 @@
       </c>
       <c r="E28" s="12">
         <f ca="1"/>
-        <v>101.45408931557891</v>
+        <v>104.03155762372253</v>
       </c>
       <c r="F28" s="11">
         <f ca="1"/>
@@ -9550,7 +6104,7 @@
       </c>
       <c r="H28" s="11">
         <f ca="1"/>
-        <v>7.1388731393429339</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I28" s="8">
         <f ca="1"/>
@@ -9558,7 +6112,7 @@
       </c>
       <c r="J28" s="8">
         <f ca="1"/>
-        <v>7.1388731393429339</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K28">
         <f ca="1"/>
@@ -9575,7 +6129,7 @@
       </c>
       <c r="C29">
         <f ca="1"/>
-        <v>-2.7020655389477746E-2</v>
+        <v>0.15213940321442412</v>
       </c>
       <c r="D29">
         <f ca="1"/>
@@ -9583,27 +6137,27 @@
       </c>
       <c r="E29" s="12">
         <f ca="1"/>
-        <v>99.30997854853868</v>
+        <v>102.93297689109913</v>
       </c>
       <c r="F29" s="11">
         <f ca="1"/>
-        <v>-99.30997854853868</v>
+        <v>0</v>
       </c>
       <c r="G29" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I29" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="8">
         <f ca="1"/>
-        <v>7.1388731393429339</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K29">
         <f ca="1"/>
@@ -9611,7 +6165,7 @@
       </c>
       <c r="L29">
         <f ca="1"/>
-        <v>0.69002145146131966</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -9620,7 +6174,7 @@
       </c>
       <c r="C30">
         <f ca="1"/>
-        <v>-1.6955708830669429E-3</v>
+        <v>0.14955341561953156</v>
       </c>
       <c r="D30">
         <f ca="1"/>
@@ -9628,7 +6182,7 @@
       </c>
       <c r="E30" s="12">
         <f ca="1"/>
-        <v>99.806276469063931</v>
+        <v>102.87152392428476</v>
       </c>
       <c r="F30" s="11">
         <f ca="1"/>
@@ -9640,15 +6194,15 @@
       </c>
       <c r="H30" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I30" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="8">
         <f ca="1"/>
-        <v>7.6351710598681848</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K30">
         <f ca="1"/>
@@ -9656,7 +6210,7 @@
       </c>
       <c r="L30">
         <f ca="1"/>
-        <v>0.19372353093606876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -9665,7 +6219,7 @@
       </c>
       <c r="C31">
         <f ca="1"/>
-        <v>-2.9127633388265534E-2</v>
+        <v>0.14792380643240402</v>
       </c>
       <c r="D31">
         <f ca="1"/>
@@ -9673,7 +6227,7 @@
       </c>
       <c r="E31" s="12">
         <f ca="1"/>
-        <v>99.252256945167574</v>
+        <v>102.82977460032905</v>
       </c>
       <c r="F31" s="11">
         <f ca="1"/>
@@ -9685,15 +6239,15 @@
       </c>
       <c r="H31" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I31" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="8">
         <f ca="1"/>
-        <v>7.0811515359718271</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K31">
         <f ca="1"/>
@@ -9701,7 +6255,7 @@
       </c>
       <c r="L31">
         <f ca="1"/>
-        <v>0.74774305483242642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -9710,7 +6264,7 @@
       </c>
       <c r="C32">
         <f ca="1"/>
-        <v>-0.102864745044508</v>
+        <v>0.23587896561726085</v>
       </c>
       <c r="D32">
         <f ca="1"/>
@@ -9718,7 +6272,7 @@
       </c>
       <c r="E32" s="12">
         <f ca="1"/>
-        <v>97.791458514989642</v>
+        <v>104.6462881533039</v>
       </c>
       <c r="F32" s="11">
         <f ca="1"/>
@@ -9730,15 +6284,15 @@
       </c>
       <c r="H32" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I32" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="8">
         <f ca="1"/>
-        <v>5.620353105793896</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K32">
         <f ca="1"/>
@@ -9746,7 +6300,7 @@
       </c>
       <c r="L32">
         <f ca="1"/>
-        <v>2.2085414850103575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -9755,7 +6309,7 @@
       </c>
       <c r="C33">
         <f ca="1"/>
-        <v>-9.4050731937078524E-2</v>
+        <v>0.21864670000475542</v>
       </c>
       <c r="D33">
         <f ca="1"/>
@@ -9763,7 +6317,7 @@
       </c>
       <c r="E33" s="12">
         <f ca="1"/>
-        <v>97.956160779571562</v>
+        <v>104.27790784339538</v>
       </c>
       <c r="F33" s="11">
         <f ca="1"/>
@@ -9775,15 +6329,15 @@
       </c>
       <c r="H33" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I33" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="8">
         <f ca="1"/>
-        <v>5.7850553703758152</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K33">
         <f ca="1"/>
@@ -9791,7 +6345,7 @@
       </c>
       <c r="L33">
         <f ca="1"/>
-        <v>2.0438392204284384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -9800,7 +6354,7 @@
       </c>
       <c r="C34">
         <f ca="1"/>
-        <v>-0.14710162446511685</v>
+        <v>0.21723566555142379</v>
       </c>
       <c r="D34">
         <f ca="1"/>
@@ -9808,7 +6362,7 @@
       </c>
       <c r="E34" s="12">
         <f ca="1"/>
-        <v>96.91456925417927</v>
+        <v>104.24014450611358</v>
       </c>
       <c r="F34" s="11">
         <f ca="1"/>
@@ -9820,15 +6374,15 @@
       </c>
       <c r="H34" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I34" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="8">
         <f ca="1"/>
-        <v>4.7434638449835234</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K34">
         <f ca="1"/>
@@ -9836,7 +6390,7 @@
       </c>
       <c r="L34">
         <f ca="1"/>
-        <v>3.0854307458207302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -9845,7 +6399,7 @@
       </c>
       <c r="C35">
         <f ca="1"/>
-        <v>-0.3503704902179523</v>
+        <v>0.2549313932470042</v>
       </c>
       <c r="D35">
         <f ca="1"/>
@@ -9853,7 +6407,7 @@
       </c>
       <c r="E35" s="12">
         <f ca="1"/>
-        <v>93.046194784681177</v>
+        <v>105.02059403972541</v>
       </c>
       <c r="F35" s="11">
         <f ca="1"/>
@@ -9865,15 +6419,15 @@
       </c>
       <c r="H35" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I35" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="8">
         <f ca="1"/>
-        <v>0.87508937548543031</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K35">
         <f ca="1"/>
@@ -9881,7 +6435,7 @@
       </c>
       <c r="L35">
         <f ca="1"/>
-        <v>6.9538052153188232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -9890,7 +6444,7 @@
       </c>
       <c r="C36">
         <f ca="1"/>
-        <v>-0.34516381720880795</v>
+        <v>0.1230264568340973</v>
       </c>
       <c r="D36">
         <f ca="1"/>
@@ -9898,7 +6452,7 @@
       </c>
       <c r="E36" s="12">
         <f ca="1"/>
-        <v>93.135686320058895</v>
+        <v>102.27809013642886</v>
       </c>
       <c r="F36" s="11">
         <f ca="1"/>
@@ -9910,15 +6464,15 @@
       </c>
       <c r="H36" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I36" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="8">
         <f ca="1"/>
-        <v>0.96458091086314823</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K36">
         <f ca="1"/>
@@ -9926,7 +6480,7 @@
       </c>
       <c r="L36">
         <f ca="1"/>
-        <v>6.8643136799411053</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -9935,7 +6489,7 @@
       </c>
       <c r="C37">
         <f ca="1"/>
-        <v>-0.39966176938465636</v>
+        <v>0.12098446580345813</v>
       </c>
       <c r="D37">
         <f ca="1"/>
@@ -9943,7 +6497,7 @@
       </c>
       <c r="E37" s="12">
         <f ca="1"/>
-        <v>92.11868795880082</v>
+        <v>102.2281498970344</v>
       </c>
       <c r="F37" s="11">
         <f ca="1"/>
@@ -9955,15 +6509,15 @@
       </c>
       <c r="H37" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I37" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8">
         <f ca="1"/>
-        <v>-5.2417450394926846E-2</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K37">
         <f ca="1"/>
@@ -9971,7 +6525,7 @@
       </c>
       <c r="L37">
         <f ca="1"/>
-        <v>7.8813120411991804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -9980,7 +6534,7 @@
       </c>
       <c r="C38">
         <f ca="1"/>
-        <v>-0.36457265340772821</v>
+        <v>0.11790312710001981</v>
       </c>
       <c r="D38">
         <f ca="1"/>
@@ -9988,7 +6542,7 @@
       </c>
       <c r="E38" s="12">
         <f ca="1"/>
-        <v>92.76001325718731</v>
+        <v>102.15699650785022</v>
       </c>
       <c r="F38" s="11">
         <f ca="1"/>
@@ -10000,15 +6554,15 @@
       </c>
       <c r="H38" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I38" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="8">
         <f ca="1"/>
-        <v>0.58890784799156393</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K38">
         <f ca="1"/>
@@ -10016,7 +6570,7 @@
       </c>
       <c r="L38">
         <f ca="1"/>
-        <v>7.2399867428126896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10025,7 +6579,7 @@
       </c>
       <c r="C39">
         <f ca="1"/>
-        <v>-0.3140097179624004</v>
+        <v>0.13916324799665292</v>
       </c>
       <c r="D39">
         <f ca="1"/>
@@ -10033,7 +6587,7 @@
       </c>
       <c r="E39" s="12">
         <f ca="1"/>
-        <v>93.695320097144872</v>
+        <v>102.5840882664514</v>
       </c>
       <c r="F39" s="11">
         <f ca="1"/>
@@ -10045,15 +6599,15 @@
       </c>
       <c r="H39" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I39" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="8">
         <f ca="1"/>
-        <v>1.5242146879491258</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K39">
         <f ca="1"/>
@@ -10061,7 +6615,7 @@
       </c>
       <c r="L39">
         <f ca="1"/>
-        <v>6.3046799028551277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10070,7 +6624,7 @@
       </c>
       <c r="C40">
         <f ca="1"/>
-        <v>-0.36754663685648409</v>
+        <v>0.21697575992611967</v>
       </c>
       <c r="D40">
         <f ca="1"/>
@@ -10078,7 +6632,7 @@
       </c>
       <c r="E40" s="12">
         <f ca="1"/>
-        <v>92.690024723119251</v>
+        <v>104.18470546433207</v>
       </c>
       <c r="F40" s="11">
         <f ca="1"/>
@@ -10090,15 +6644,15 @@
       </c>
       <c r="H40" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I40" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="8">
         <f ca="1"/>
-        <v>0.51891931392350443</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K40">
         <f ca="1"/>
@@ -10106,7 +6660,7 @@
       </c>
       <c r="L40">
         <f ca="1"/>
-        <v>7.3099752768807491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10115,7 +6669,7 @@
       </c>
       <c r="C41">
         <f ca="1"/>
-        <v>-0.39995765482032092</v>
+        <v>0.30421457154033521</v>
       </c>
       <c r="D41">
         <f ca="1"/>
@@ -10123,7 +6677,7 @@
       </c>
       <c r="E41" s="12">
         <f ca="1"/>
-        <v>92.083765284387496</v>
+        <v>106.00996512389797</v>
       </c>
       <c r="F41" s="11">
         <f ca="1"/>
@@ -10135,15 +6689,15 @@
       </c>
       <c r="H41" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I41" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="8">
         <f ca="1"/>
-        <v>-8.7340124808250152E-2</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K41">
         <f ca="1"/>
@@ -10151,7 +6705,7 @@
       </c>
       <c r="L41">
         <f ca="1"/>
-        <v>7.9162347156125037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10160,7 +6714,7 @@
       </c>
       <c r="C42">
         <f ca="1"/>
-        <v>-0.3779165166407405</v>
+        <v>0.39421747521135259</v>
       </c>
       <c r="D42">
         <f ca="1"/>
@@ -10168,7 +6722,7 @@
       </c>
       <c r="E42" s="12">
         <f ca="1"/>
-        <v>92.48318855598059</v>
+        <v>107.92684980597589</v>
       </c>
       <c r="F42" s="11">
         <f ca="1"/>
@@ -10180,15 +6734,15 @@
       </c>
       <c r="H42" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I42" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="8">
         <f ca="1"/>
-        <v>0.31208314678484328</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K42">
         <f ca="1"/>
@@ -10196,7 +6750,7 @@
       </c>
       <c r="L42">
         <f ca="1"/>
-        <v>7.5168114440194103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10205,7 +6759,7 @@
       </c>
       <c r="C43">
         <f ca="1"/>
-        <v>-0.37101986038157347</v>
+        <v>0.30765812661465836</v>
       </c>
       <c r="D43">
         <f ca="1"/>
@@ -10213,7 +6767,7 @@
       </c>
       <c r="E43" s="12">
         <f ca="1"/>
-        <v>92.60343295487624</v>
+        <v>106.06602857952167</v>
       </c>
       <c r="F43" s="11">
         <f ca="1"/>
@@ -10225,15 +6779,15 @@
       </c>
       <c r="H43" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I43" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" s="8">
         <f ca="1"/>
-        <v>0.43232754568049359</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K43">
         <f ca="1"/>
@@ -10241,7 +6795,7 @@
       </c>
       <c r="L43">
         <f ca="1"/>
-        <v>7.39656704512376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10250,7 +6804,7 @@
       </c>
       <c r="C44">
         <f ca="1"/>
-        <v>-0.42740931419957728</v>
+        <v>0.32410100611106268</v>
       </c>
       <c r="D44">
         <f ca="1"/>
@@ -10258,7 +6812,7 @@
       </c>
       <c r="E44" s="12">
         <f ca="1"/>
-        <v>91.557603728880096</v>
+        <v>106.40689603967846</v>
       </c>
       <c r="F44" s="11">
         <f ca="1"/>
@@ -10270,15 +6824,15 @@
       </c>
       <c r="H44" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I44" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="8">
         <f ca="1"/>
-        <v>-0.61350168031565033</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K44">
         <f ca="1"/>
@@ -10286,7 +6840,7 @@
       </c>
       <c r="L44">
         <f ca="1"/>
-        <v>8.4423962711199039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10295,7 +6849,7 @@
       </c>
       <c r="C45">
         <f ca="1"/>
-        <v>-0.46785062473625533</v>
+        <v>0.34537631475524883</v>
       </c>
       <c r="D45">
         <f ca="1"/>
@@ -10303,7 +6857,7 @@
       </c>
       <c r="E45" s="12">
         <f ca="1"/>
-        <v>90.812783309137046</v>
+        <v>106.8520800877869</v>
       </c>
       <c r="F45" s="11">
         <f ca="1"/>
@@ -10315,15 +6869,15 @@
       </c>
       <c r="H45" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I45" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="8">
         <f ca="1"/>
-        <v>-1.3583221000587002</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K45">
         <f ca="1"/>
@@ -10331,7 +6885,7 @@
       </c>
       <c r="L45">
         <f ca="1"/>
-        <v>9.1872166908629538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10340,7 +6894,7 @@
       </c>
       <c r="C46">
         <f ca="1"/>
-        <v>-0.62390302034793121</v>
+        <v>0.38375420257235293</v>
       </c>
       <c r="D46">
         <f ca="1"/>
@@ -10348,7 +6902,7 @@
       </c>
       <c r="E46" s="12">
         <f ca="1"/>
-        <v>88.015204848159811</v>
+        <v>107.66677346645592</v>
       </c>
       <c r="F46" s="11">
         <f ca="1"/>
@@ -10360,15 +6914,15 @@
       </c>
       <c r="H46" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I46" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="8">
         <f ca="1"/>
-        <v>-4.155900561035935</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K46">
         <f ca="1"/>
@@ -10376,7 +6930,7 @@
       </c>
       <c r="L46">
         <f ca="1"/>
-        <v>11.984795151840189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10385,7 +6939,7 @@
       </c>
       <c r="C47">
         <f ca="1"/>
-        <v>-0.72276746565514227</v>
+        <v>0.44860021734087913</v>
       </c>
       <c r="D47">
         <f ca="1"/>
@@ -10393,7 +6947,7 @@
       </c>
       <c r="E47" s="12">
         <f ca="1"/>
-        <v>86.285079568398359</v>
+        <v>109.06349433383669</v>
       </c>
       <c r="F47" s="11">
         <f ca="1"/>
@@ -10405,15 +6959,15 @@
       </c>
       <c r="H47" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I47" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="8">
         <f ca="1"/>
-        <v>-5.8860258407973873</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K47">
         <f ca="1"/>
@@ -10421,7 +6975,7 @@
       </c>
       <c r="L47">
         <f ca="1"/>
-        <v>13.714920431601641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10430,7 +6984,7 @@
       </c>
       <c r="C48">
         <f ca="1"/>
-        <v>-0.78945231275215721</v>
+        <v>0.33928639992452264</v>
       </c>
       <c r="D48">
         <f ca="1"/>
@@ -10438,7 +6992,7 @@
       </c>
       <c r="E48" s="12">
         <f ca="1"/>
-        <v>85.135126984485467</v>
+        <v>106.69640508844707</v>
       </c>
       <c r="F48" s="11">
         <f ca="1"/>
@@ -10450,15 +7004,15 @@
       </c>
       <c r="H48" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I48" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="8">
         <f ca="1"/>
-        <v>-7.0359784247102795</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K48">
         <f ca="1"/>
@@ -10466,7 +7020,7 @@
       </c>
       <c r="L48">
         <f ca="1"/>
-        <v>14.864873015514533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10475,7 +7029,7 @@
       </c>
       <c r="C49">
         <f ca="1"/>
-        <v>-0.81063227590324538</v>
+        <v>0.37500345704311722</v>
       </c>
       <c r="D49">
         <f ca="1"/>
@@ -10483,7 +7037,7 @@
       </c>
       <c r="E49" s="12">
         <f ca="1"/>
-        <v>84.76847620403862</v>
+        <v>107.4527136096806</v>
       </c>
       <c r="F49" s="11">
         <f ca="1"/>
@@ -10495,15 +7049,15 @@
       </c>
       <c r="H49" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I49" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="8">
         <f ca="1"/>
-        <v>-7.4026292051571261</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K49">
         <f ca="1"/>
@@ -10511,7 +7065,7 @@
       </c>
       <c r="L49">
         <f ca="1"/>
-        <v>15.23152379596138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10520,7 +7074,7 @@
       </c>
       <c r="C50">
         <f ca="1"/>
-        <v>-0.89978183579052617</v>
+        <v>0.41818096487772299</v>
       </c>
       <c r="D50">
         <f ca="1"/>
@@ -10528,7 +7082,7 @@
       </c>
       <c r="E50" s="12">
         <f ca="1"/>
-        <v>83.263794832756432</v>
+        <v>108.37596929547966</v>
       </c>
       <c r="F50" s="11">
         <f ca="1"/>
@@ -10540,15 +7094,15 @@
       </c>
       <c r="H50" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I50" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="8">
         <f ca="1"/>
-        <v>-8.9073105764393148</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K50">
         <f ca="1"/>
@@ -10556,7 +7110,7 @@
       </c>
       <c r="L50">
         <f ca="1"/>
-        <v>16.736205167243568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10565,7 +7119,7 @@
       </c>
       <c r="C51">
         <f ca="1"/>
-        <v>-0.95212029034014989</v>
+        <v>0.38724464115920715</v>
       </c>
       <c r="D51">
         <f ca="1"/>
@@ -10573,7 +7127,7 @@
       </c>
       <c r="E51" s="12">
         <f ca="1"/>
-        <v>82.390169525225659</v>
+        <v>107.69887239310543</v>
       </c>
       <c r="F51" s="11">
         <f ca="1"/>
@@ -10585,15 +7139,15 @@
       </c>
       <c r="H51" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I51" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" s="8">
         <f ca="1"/>
-        <v>-9.7809358839700877</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K51">
         <f ca="1"/>
@@ -10601,7 +7155,7 @@
       </c>
       <c r="L51">
         <f ca="1"/>
-        <v>17.609830474774341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10610,7 +7164,7 @@
       </c>
       <c r="C52">
         <f ca="1"/>
-        <v>-0.91008517638769437</v>
+        <v>0.36730221402028818</v>
       </c>
       <c r="D52">
         <f ca="1"/>
@@ -10618,7 +7172,7 @@
       </c>
       <c r="E52" s="12">
         <f ca="1"/>
-        <v>83.07909872834405</v>
+        <v>107.26159123936347</v>
       </c>
       <c r="F52" s="11">
         <f ca="1"/>
@@ -10630,15 +7184,15 @@
       </c>
       <c r="H52" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I52" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" s="8">
         <f ca="1"/>
-        <v>-9.0920066808516964</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K52">
         <f ca="1"/>
@@ -10646,7 +7200,7 @@
       </c>
       <c r="L52">
         <f ca="1"/>
-        <v>16.92090127165595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10655,7 +7209,7 @@
       </c>
       <c r="C53">
         <f ca="1"/>
-        <v>-0.84514979155801528</v>
+        <v>0.34140320688626569</v>
       </c>
       <c r="D53">
         <f ca="1"/>
@@ -10663,7 +7217,7 @@
       </c>
       <c r="E53" s="12">
         <f ca="1"/>
-        <v>84.158357102341185</v>
+        <v>106.69889769414378</v>
       </c>
       <c r="F53" s="11">
         <f ca="1"/>
@@ -10675,15 +7229,15 @@
       </c>
       <c r="H53" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I53" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" s="8">
         <f ca="1"/>
-        <v>-8.0127483068545615</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K53">
         <f ca="1"/>
@@ -10691,7 +7245,7 @@
       </c>
       <c r="L53">
         <f ca="1"/>
-        <v>15.841642897658815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10700,7 +7254,7 @@
       </c>
       <c r="C54">
         <f ca="1"/>
-        <v>-0.80954165596010585</v>
+        <v>0.28605391734911245</v>
       </c>
       <c r="D54">
         <f ca="1"/>
@@ -10708,7 +7262,7 @@
       </c>
       <c r="E54" s="12">
         <f ca="1"/>
-        <v>84.753060253634828</v>
+        <v>105.51582793235528</v>
       </c>
       <c r="F54" s="11">
         <f ca="1"/>
@@ -10720,15 +7274,15 @@
       </c>
       <c r="H54" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I54" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="8">
         <f ca="1"/>
-        <v>-7.4180451555609181</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K54">
         <f ca="1"/>
@@ -10736,7 +7290,7 @@
       </c>
       <c r="L54">
         <f ca="1"/>
-        <v>15.246939746365172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10745,7 +7299,7 @@
       </c>
       <c r="C55">
         <f ca="1"/>
-        <v>-0.74799252226096102</v>
+        <v>0.22542463770193133</v>
       </c>
       <c r="D55">
         <f ca="1"/>
@@ -10753,7 +7307,7 @@
       </c>
       <c r="E55" s="12">
         <f ca="1"/>
-        <v>85.795939614681643</v>
+        <v>104.2357450842491</v>
       </c>
       <c r="F55" s="11">
         <f ca="1"/>
@@ -10765,15 +7319,15 @@
       </c>
       <c r="H55" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I55" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="8">
         <f ca="1"/>
-        <v>-6.3751657945141034</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K55">
         <f ca="1"/>
@@ -10781,7 +7335,7 @@
       </c>
       <c r="L55">
         <f ca="1"/>
-        <v>14.204060385318357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10790,7 +7344,7 @@
       </c>
       <c r="C56">
         <f ca="1"/>
-        <v>-0.76586651111633319</v>
+        <v>0.17492220313866663</v>
       </c>
       <c r="D56">
         <f ca="1"/>
@@ -10798,7 +7352,7 @@
       </c>
       <c r="E56" s="12">
         <f ca="1"/>
-        <v>85.482945120004558</v>
+        <v>103.17995777868256</v>
       </c>
       <c r="F56" s="11">
         <f ca="1"/>
@@ -10810,15 +7364,15 @@
       </c>
       <c r="H56" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I56" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="8">
         <f ca="1"/>
-        <v>-6.6881602891911882</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K56">
         <f ca="1"/>
@@ -10826,7 +7380,7 @@
       </c>
       <c r="L56">
         <f ca="1"/>
-        <v>14.517054879995442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10835,7 +7389,7 @@
       </c>
       <c r="C57">
         <f ca="1"/>
-        <v>-0.80649184836630228</v>
+        <v>0.14083864773621957</v>
       </c>
       <c r="D57">
         <f ca="1"/>
@@ -10843,7 +7397,7 @@
       </c>
       <c r="E57" s="12">
         <f ca="1"/>
-        <v>84.784421425381538</v>
+        <v>102.47080364704982</v>
       </c>
       <c r="F57" s="11">
         <f ca="1"/>
@@ -10855,15 +7409,15 @@
       </c>
       <c r="H57" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I57" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="8">
         <f ca="1"/>
-        <v>-7.3866839838142084</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K57">
         <f ca="1"/>
@@ -10871,7 +7425,7 @@
       </c>
       <c r="L57">
         <f ca="1"/>
-        <v>15.215578574618462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10880,7 +7434,7 @@
       </c>
       <c r="C58">
         <f ca="1"/>
-        <v>-0.84726701994796227</v>
+        <v>0.14094959634013782</v>
       </c>
       <c r="D58">
         <f ca="1"/>
@@ -10888,7 +7442,7 @@
       </c>
       <c r="E58" s="12">
         <f ca="1"/>
-        <v>84.089085791413567</v>
+        <v>102.46487995250632</v>
       </c>
       <c r="F58" s="11">
         <f ca="1"/>
@@ -10900,15 +7454,15 @@
       </c>
       <c r="H58" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I58" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" s="8">
         <f ca="1"/>
-        <v>-8.0820196177821799</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K58">
         <f ca="1"/>
@@ -10916,7 +7470,7 @@
       </c>
       <c r="L58">
         <f ca="1"/>
-        <v>15.910914208586433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10925,7 +7479,7 @@
       </c>
       <c r="C59">
         <f ca="1"/>
-        <v>-0.8293024760448684</v>
+        <v>0.15822015688068936</v>
       </c>
       <c r="D59">
         <f ca="1"/>
@@ -10933,7 +7487,7 @@
       </c>
       <c r="E59" s="12">
         <f ca="1"/>
-        <v>84.385002539201224</v>
+        <v>102.81119186366369</v>
       </c>
       <c r="F59" s="11">
         <f ca="1"/>
@@ -10945,15 +7499,15 @@
       </c>
       <c r="H59" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I59" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="8">
         <f ca="1"/>
-        <v>-7.7861028699945223</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K59">
         <f ca="1"/>
@@ -10961,7 +7515,7 @@
       </c>
       <c r="L59">
         <f ca="1"/>
-        <v>15.614997460798776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -10970,7 +7524,7 @@
       </c>
       <c r="C60">
         <f ca="1"/>
-        <v>-0.8216375465603204</v>
+        <v>0.17753898129986634</v>
       </c>
       <c r="D60">
         <f ca="1"/>
@@ -10978,7 +7532,7 @@
       </c>
       <c r="E60" s="12">
         <f ca="1"/>
-        <v>84.507701876418068</v>
+        <v>103.20094213780263</v>
       </c>
       <c r="F60" s="11">
         <f ca="1"/>
@@ -10990,15 +7544,15 @@
       </c>
       <c r="H60" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I60" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="8">
         <f ca="1"/>
-        <v>-7.6634035327776786</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K60">
         <f ca="1"/>
@@ -11006,7 +7560,7 @@
       </c>
       <c r="L60">
         <f ca="1"/>
-        <v>15.492298123581932</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -11015,7 +7569,7 @@
       </c>
       <c r="C61">
         <f ca="1"/>
-        <v>-0.79045181188115421</v>
+        <v>0.20509444177838801</v>
       </c>
       <c r="D61">
         <f ca="1"/>
@@ -11023,7 +7577,7 @@
       </c>
       <c r="E61" s="12">
         <f ca="1"/>
-        <v>85.029633369640393</v>
+        <v>103.76296076490136</v>
       </c>
       <c r="F61" s="11">
         <f ca="1"/>
@@ -11035,15 +7589,15 @@
       </c>
       <c r="H61" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I61" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="8">
         <f ca="1"/>
-        <v>-7.141472039555353</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K61">
         <f ca="1"/>
@@ -11051,7 +7605,7 @@
       </c>
       <c r="L61">
         <f ca="1"/>
-        <v>14.970366630359607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -11060,7 +7614,7 @@
       </c>
       <c r="C62">
         <f ca="1"/>
-        <v>-0.80137628390333304</v>
+        <v>0.16046727161621677</v>
       </c>
       <c r="D62">
         <f ca="1"/>
@@ -11068,7 +7622,7 @@
       </c>
       <c r="E62" s="12">
         <f ca="1"/>
-        <v>84.837268154492023</v>
+        <v>102.83272514116173</v>
       </c>
       <c r="F62" s="11">
         <f ca="1"/>
@@ -11080,15 +7634,15 @@
       </c>
       <c r="H62" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I62" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="8">
         <f ca="1"/>
-        <v>-7.3338372547037238</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K62">
         <f ca="1"/>
@@ -11096,7 +7650,7 @@
       </c>
       <c r="L62">
         <f ca="1"/>
-        <v>15.162731845507977</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -11105,7 +7659,7 @@
       </c>
       <c r="C63">
         <f ca="1"/>
-        <v>-0.77940126708588631</v>
+        <v>0.15576425952150941</v>
       </c>
       <c r="D63">
         <f ca="1"/>
@@ -11113,7 +7667,7 @@
       </c>
       <c r="E63" s="12">
         <f ca="1"/>
-        <v>85.204132192479122</v>
+        <v>102.72782735171053</v>
       </c>
       <c r="F63" s="11">
         <f ca="1"/>
@@ -11125,15 +7679,15 @@
       </c>
       <c r="H63" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I63" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="8">
         <f ca="1"/>
-        <v>-6.9669732167166245</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K63">
         <f ca="1"/>
@@ -11141,7 +7695,7 @@
       </c>
       <c r="L63">
         <f ca="1"/>
-        <v>14.795867807520878</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -11150,7 +7704,7 @@
       </c>
       <c r="C64">
         <f ca="1"/>
-        <v>-0.81887375484513392</v>
+        <v>0.21271792266006012</v>
       </c>
       <c r="D64">
         <f ca="1"/>
@@ -11158,7 +7712,7 @@
       </c>
       <c r="E64" s="12">
         <f ca="1"/>
-        <v>84.527374038421812</v>
+        <v>103.89635030801317</v>
       </c>
       <c r="F64" s="11">
         <f ca="1"/>
@@ -11170,15 +7724,15 @@
       </c>
       <c r="H64" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I64" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" s="8">
         <f ca="1"/>
-        <v>-7.6437313707739349</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K64">
         <f ca="1"/>
@@ -11186,7 +7740,7 @@
       </c>
       <c r="L64">
         <f ca="1"/>
-        <v>15.472625961578188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -11195,7 +7749,7 @@
       </c>
       <c r="C65">
         <f ca="1"/>
-        <v>-0.82332327054491361</v>
+        <v>0.21948759519689068</v>
       </c>
       <c r="D65">
         <f ca="1"/>
@@ -11203,7 +7757,7 @@
       </c>
       <c r="E65" s="12">
         <f ca="1"/>
-        <v>84.445430418040843</v>
+        <v>104.02879179683966</v>
       </c>
       <c r="F65" s="11">
         <f ca="1"/>
@@ -11215,15 +7769,15 @@
       </c>
       <c r="H65" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I65" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" s="8">
         <f ca="1"/>
-        <v>-7.7256749911549036</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K65">
         <f ca="1"/>
@@ -11231,7 +7785,7 @@
       </c>
       <c r="L65">
         <f ca="1"/>
-        <v>15.554569581959157</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -11240,7 +7794,7 @@
       </c>
       <c r="C66">
         <f ca="1"/>
-        <v>-0.83985350407621118</v>
+        <v>9.8376306402575539E-2</v>
       </c>
       <c r="D66">
         <f ca="1"/>
@@ -11248,7 +7802,7 @@
       </c>
       <c r="E66" s="12">
         <f ca="1"/>
-        <v>84.159977797202032</v>
+        <v>101.53112962454345</v>
       </c>
       <c r="F66" s="11">
         <f ca="1"/>
@@ -11260,15 +7814,15 @@
       </c>
       <c r="H66" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="I66" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" s="8">
         <f ca="1"/>
-        <v>-8.0111276119937145</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K66">
         <f ca="1"/>
@@ -11276,7 +7830,7 @@
       </c>
       <c r="L66">
         <f ca="1"/>
-        <v>15.840022202797968</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -11285,7 +7839,7 @@
       </c>
       <c r="C67">
         <f ca="1"/>
-        <v>-0.90193665904756049</v>
+        <v>1.1881647246253332E-2</v>
       </c>
       <c r="D67">
         <f ca="1"/>
@@ -11293,19 +7847,19 @@
       </c>
       <c r="E67" s="12">
         <f ca="1"/>
-        <v>83.114805776359916</v>
+        <v>99.781871192329277</v>
       </c>
       <c r="F67" s="11">
         <f ca="1"/>
-        <v>0</v>
+        <v>-99.781871192329277</v>
       </c>
       <c r="G67" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>-95.242315587752614</v>
       </c>
       <c r="I67" s="8">
         <f ca="1"/>
@@ -11313,7 +7867,7 @@
       </c>
       <c r="J67" s="8">
         <f ca="1"/>
-        <v>-9.0562996328358309</v>
+        <v>4.5395556045766625</v>
       </c>
       <c r="K67">
         <f ca="1"/>
@@ -11321,7 +7875,7 @@
       </c>
       <c r="L67">
         <f ca="1"/>
-        <v>16.885194223640084</v>
+        <v>0.21812880767072329</v>
       </c>
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -11330,7 +7884,7 @@
       </c>
       <c r="C68">
         <f ca="1"/>
-        <v>-0.9316501452512238</v>
+        <v>-5.271700813535192E-2</v>
       </c>
       <c r="D68">
         <f ca="1"/>
@@ -11338,7 +7892,7 @@
       </c>
       <c r="E68" s="12">
         <f ca="1"/>
-        <v>82.615734850052831</v>
+        <v>98.493128503717003</v>
       </c>
       <c r="F68" s="11">
         <f ca="1"/>
@@ -11350,7 +7904,7 @@
       </c>
       <c r="H68" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>-95.242315587752614</v>
       </c>
       <c r="I68" s="8">
         <f ca="1"/>
@@ -11358,7 +7912,7 @@
       </c>
       <c r="J68" s="8">
         <f ca="1"/>
-        <v>-9.555370559142915</v>
+        <v>3.2508129159643886</v>
       </c>
       <c r="K68">
         <f ca="1"/>
@@ -11366,7 +7920,7 @@
       </c>
       <c r="L68">
         <f ca="1"/>
-        <v>17.384265149947169</v>
+        <v>1.5068714962829972</v>
       </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -11375,7 +7929,7 @@
       </c>
       <c r="C69">
         <f ca="1"/>
-        <v>-0.84352188841466036</v>
+        <v>-9.2505313785698262E-2</v>
       </c>
       <c r="D69">
         <f ca="1"/>
@@ -11383,7 +7937,7 @@
       </c>
       <c r="E69" s="12">
         <f ca="1"/>
-        <v>84.07807305448307</v>
+        <v>97.704647131119998</v>
       </c>
       <c r="F69" s="11">
         <f ca="1"/>
@@ -11395,7 +7949,7 @@
       </c>
       <c r="H69" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>-95.242315587752614</v>
       </c>
       <c r="I69" s="8">
         <f ca="1"/>
@@ -11403,7 +7957,7 @@
       </c>
       <c r="J69" s="8">
         <f ca="1"/>
-        <v>-8.0930323547126761</v>
+        <v>2.4623315433673838</v>
       </c>
       <c r="K69">
         <f ca="1"/>
@@ -11411,7 +7965,7 @@
       </c>
       <c r="L69">
         <f ca="1"/>
-        <v>15.92192694551693</v>
+        <v>2.295352868880002</v>
       </c>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -11420,7 +7974,7 @@
       </c>
       <c r="C70">
         <f ca="1"/>
-        <v>-0.8089561678558167</v>
+        <v>-9.130821155286814E-2</v>
       </c>
       <c r="D70">
         <f ca="1"/>
@@ -11428,7 +7982,7 @@
       </c>
       <c r="E70" s="12">
         <f ca="1"/>
-        <v>84.654558003577492</v>
+        <v>97.720224491239065</v>
       </c>
       <c r="F70" s="11">
         <f ca="1"/>
@@ -11440,7 +7994,7 @@
       </c>
       <c r="H70" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>-95.242315587752614</v>
       </c>
       <c r="I70" s="8">
         <f ca="1"/>
@@ -11448,7 +8002,7 @@
       </c>
       <c r="J70" s="8">
         <f ca="1"/>
-        <v>-7.5165474056182546</v>
+        <v>2.4779089034864512</v>
       </c>
       <c r="K70">
         <f ca="1"/>
@@ -11456,7 +8010,7 @@
       </c>
       <c r="L70">
         <f ca="1"/>
-        <v>15.345441996422508</v>
+        <v>2.2797755087609346</v>
       </c>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -11465,7 +8019,7 @@
       </c>
       <c r="C71">
         <f ca="1"/>
-        <v>-0.75460445017154276</v>
+        <v>-8.6092587061043668E-2</v>
       </c>
       <c r="D71">
         <f ca="1"/>
@@ -11473,7 +8027,7 @@
       </c>
       <c r="E71" s="12">
         <f ca="1"/>
-        <v>85.572955769241318</v>
+        <v>97.814386610182197</v>
       </c>
       <c r="F71" s="11">
         <f ca="1"/>
@@ -11485,7 +8039,7 @@
       </c>
       <c r="H71" s="11">
         <f ca="1"/>
-        <v>-92.171105409195746</v>
+        <v>-95.242315587752614</v>
       </c>
       <c r="I71" s="8">
         <f ca="1"/>
@@ -11493,7 +8047,7 @@
       </c>
       <c r="J71" s="8">
         <f ca="1"/>
-        <v>-6.5981496399544284</v>
+        <v>2.5720710224295829</v>
       </c>
       <c r="K71">
         <f ca="1"/>
@@ -11501,7 +8055,7 @@
       </c>
       <c r="L71">
         <f ca="1"/>
-        <v>14.427044230758682</v>
+        <v>2.185613389817803</v>
       </c>
     </row>
     <row r="72" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -11510,7 +8064,7 @@
       </c>
       <c r="C72">
         <f ca="1"/>
-        <v>-0.72373313246710369</v>
+        <v>-0.12658255211244224</v>
       </c>
       <c r="D72">
         <f ca="1"/>
@@ -11518,11 +8072,11 @@
       </c>
       <c r="E72" s="12">
         <f ca="1"/>
-        <v>86.096052238557803</v>
+        <v>97.017723233977435</v>
       </c>
       <c r="F72" s="11">
         <f ca="1"/>
-        <v>92.171105409195746</v>
+        <v>95.242315587752614</v>
       </c>
       <c r="G72" s="8">
         <f ca="1"/>
@@ -11538,15 +8092,15 @@
       </c>
       <c r="J72" s="8">
         <f ca="1"/>
-        <v>86.096052238557803</v>
+        <v>97.017723233977435</v>
       </c>
       <c r="K72">
         <f ca="1"/>
-        <v>-6.0750531706379434</v>
+        <v>1.7754076462248207</v>
       </c>
       <c r="L72">
         <f ca="1"/>
-        <v>13.903947761442197</v>
+        <v>2.9822767660225651</v>
       </c>
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.55000000000000004">

--- a/xlsx/hw5.xlsx
+++ b/xlsx/hw5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keith\source\repos\xlladdins\xll_ml\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCAE566-A9F2-441B-86DB-F04CCA4FE5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF780FA-2010-4334-A52C-7AFA12419DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13996" activeTab="2" xr2:uid="{5E38A752-04D7-4C78-952F-E31FCF3159F7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13996" activeTab="1" xr2:uid="{5E38A752-04D7-4C78-952F-E31FCF3159F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Elementary" sheetId="1" r:id="rId1"/>
@@ -991,18 +991,18 @@
       </c>
       <c r="D4">
         <f ca="1">RAND()</f>
-        <v>0.50705860915592771</v>
+        <v>0.38624765189640453</v>
       </c>
       <c r="E4">
         <f ca="1">-F4*D4</f>
-        <v>-1.5211758274677831</v>
+        <v>-1.1587429556892137</v>
       </c>
       <c r="F4" s="20">
         <v>3</v>
       </c>
       <c r="G4">
         <f ca="1">E4</f>
-        <v>-1.5211758274677831</v>
+        <v>-1.1587429556892137</v>
       </c>
       <c r="H4">
         <f>F4</f>
@@ -1026,11 +1026,11 @@
       </c>
       <c r="D5">
         <f ca="1">RAND()</f>
-        <v>0.18183783962827582</v>
+        <v>0.60002550215153139</v>
       </c>
       <c r="E5">
         <f ca="1">-E4</f>
-        <v>1.5211758274677831</v>
+        <v>1.1587429556892137</v>
       </c>
       <c r="F5" s="21">
         <f>-F4</f>
@@ -1050,11 +1050,11 @@
       </c>
       <c r="J5">
         <f ca="1">-SUMPRODUCT(E5:F5,C5:D5)</f>
-        <v>-0.97566230858295566</v>
+        <v>0.64133355076538034</v>
       </c>
       <c r="K5">
         <f ca="1">F4*(D5-D4)</f>
-        <v>-0.97566230858295566</v>
+        <v>0.64133355076538057</v>
       </c>
       <c r="L5" s="6">
         <f ca="1">J5-K5</f>
@@ -1087,7 +1087,7 @@
     <row r="1" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="18" cm="1">
         <f t="array" aca="1" ref="B1" ca="1">_xll.MONTE.COUNT()</f>
-        <v>10441</v>
+        <v>17749</v>
       </c>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G3" s="8" cm="1">
         <f t="array" aca="1" ref="G3" ca="1">_xlfn.TAKE(S_,-1)</f>
-        <v>106.19284045436892</v>
+        <v>91.578275485005179</v>
       </c>
       <c r="N3" s="7">
         <v>1</v>
@@ -1163,15 +1163,15 @@
       </c>
       <c r="G4" s="11">
         <f ca="1">MAX(k - last,0)</f>
-        <v>0</v>
+        <v>8.4217245149948212</v>
       </c>
       <c r="H4" s="11">
         <f t="array" aca="1" ref="H4:I4" ca="1">_xll.MONTE.STDEV(G4)</f>
-        <v>3.940636698271593</v>
+        <v>4.0089949031248189</v>
       </c>
       <c r="I4" s="11">
         <f ca="1"/>
-        <v>5.4540603594786763</v>
+        <v>5.4770512639207718</v>
       </c>
       <c r="M4">
         <v>1E-3</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G5" s="11" cm="1">
         <f t="array" aca="1" ref="G5" ca="1">_xlfn.TAKE(A,-1)</f>
-        <v>5.9557150775633221E-2</v>
+        <v>7.8662963197909761</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
@@ -1228,19 +1228,19 @@
       </c>
       <c r="G6" s="11">
         <f ca="1">payoff-hedge</f>
-        <v>-5.9557150775633221E-2</v>
+        <v>0.55542819520384512</v>
       </c>
       <c r="H6" s="8">
         <f t="array" aca="1" ref="H6:I6" ca="1">_xll.MONTE.STDEV(error)</f>
-        <v>-1.4968078938005986E-2</v>
+        <v>-4.8258026454621246E-2</v>
       </c>
       <c r="I6" s="13">
         <f ca="1"/>
-        <v>0.43658700690594882</v>
+        <v>0.71854050053657714</v>
       </c>
       <c r="J6" s="17">
         <f ca="1">I6/put</f>
-        <v>0.10948173387237969</v>
+        <v>0.18018644305009926</v>
       </c>
       <c r="K6" s="16" t="s">
         <v>30</v>
@@ -1256,6 +1256,10 @@
       <c r="C7">
         <v>100</v>
       </c>
+      <c r="O7" cm="1">
+        <f t="array" ref="O7:O16">_xll.ARRAY.SEQUENCE(0.001,0.1,0.01)</f>
+        <v>1E-3</v>
+      </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="D8" s="26" t="s">
@@ -1276,6 +1280,12 @@
       <c r="K8" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="O8">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="P8">
+        <v>0.18018644305009926</v>
+      </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="5" t="s">
@@ -1311,6 +1321,9 @@
       <c r="L9" s="19" t="s">
         <v>31</v>
       </c>
+      <c r="O9">
+        <v>2.1000000000000001E-2</v>
+      </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" cm="1">
@@ -1365,6 +1378,9 @@
         <f ca="1">F10-M10</f>
         <v>0</v>
       </c>
+      <c r="O10">
+        <v>3.1E-2</v>
+      </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B11">
@@ -1372,7 +1388,7 @@
       </c>
       <c r="C11">
         <f ca="1"/>
-        <v>1.0570239487426679E-2</v>
+        <v>-3.3140554378005324E-2</v>
       </c>
       <c r="D11">
         <f ca="1"/>
@@ -1380,27 +1396,27 @@
       </c>
       <c r="E11" s="12">
         <f ca="1"/>
-        <v>100.20361179762185</v>
+        <v>99.331433827498017</v>
       </c>
       <c r="F11" s="11">
         <f ca="1"/>
-        <v>-0.80218814356188028</v>
+        <v>2.6948328977212959</v>
       </c>
       <c r="G11" s="8">
         <f ca="1"/>
-        <v>8.0055811279740596E-3</v>
+        <v>-2.7129709034515948E-2</v>
       </c>
       <c r="H11" s="11">
         <f ca="1"/>
-        <v>51.191692440275368</v>
+        <v>54.688713481558544</v>
       </c>
       <c r="I11" s="8">
         <f ca="1"/>
-        <v>-0.47205561303365345</v>
+        <v>-0.50719090319614346</v>
       </c>
       <c r="J11" s="8">
         <f ca="1"/>
-        <v>3.8900150449627589</v>
+        <v>4.3087138428218665</v>
       </c>
       <c r="K11">
         <f ca="1"/>
@@ -1408,15 +1424,18 @@
       </c>
       <c r="L11">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.66856617250198269</v>
       </c>
       <c r="M11" s="22">
         <f ca="1" xml:space="preserve"> - G11*E11</f>
-        <v>-0.80218814356188028</v>
+        <v>2.6948328977212959</v>
       </c>
       <c r="N11" s="22">
         <f ca="1">F11-M11</f>
         <v>0</v>
+      </c>
+      <c r="O11">
+        <v>4.1000000000000002E-2</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1425,7 +1444,7 @@
       </c>
       <c r="C12">
         <f ca="1"/>
-        <v>9.6500231423624037E-3</v>
+        <v>-3.1412987258112444E-2</v>
       </c>
       <c r="D12">
         <f ca="1"/>
@@ -1433,27 +1452,27 @@
       </c>
       <c r="E12" s="12">
         <f ca="1"/>
-        <v>100.17715720112868</v>
+        <v>99.357811158214986</v>
       </c>
       <c r="F12" s="11">
         <f ca="1"/>
-        <v>0.11641661046079653</v>
+        <v>-6.8848431632998128E-2</v>
       </c>
       <c r="G12" s="8">
         <f ca="1"/>
-        <v>-1.1621073477565691E-3</v>
+        <v>6.929342628468893E-4</v>
       </c>
       <c r="H12" s="11">
         <f ca="1"/>
-        <v>51.308109050736164</v>
+        <v>54.619865049925544</v>
       </c>
       <c r="I12" s="8">
         <f ca="1"/>
-        <v>-0.47321772038141002</v>
+        <v>-0.50649796893329657</v>
       </c>
       <c r="J12" s="8">
         <f ca="1"/>
-        <v>3.9025030857278935</v>
+        <v>4.2953355006316229</v>
       </c>
       <c r="K12">
         <f ca="1"/>
@@ -1461,7 +1480,13 @@
       </c>
       <c r="L12">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.64218884178501412</v>
+      </c>
+      <c r="O12">
+        <v>5.1000000000000004E-2</v>
+      </c>
+      <c r="P12">
+        <v>0.37259544053208832</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1470,7 +1495,7 @@
       </c>
       <c r="C13">
         <f ca="1"/>
-        <v>-1.9103651635405554E-2</v>
+        <v>-5.446733374204403E-2</v>
       </c>
       <c r="D13">
         <f ca="1"/>
@@ -1478,27 +1503,27 @@
       </c>
       <c r="E13" s="12">
         <f ca="1"/>
-        <v>99.594750328971074</v>
+        <v>98.892828092483811</v>
       </c>
       <c r="F13" s="11">
         <f ca="1"/>
-        <v>2.3826209887818721</v>
+        <v>1.9326709265880835</v>
       </c>
       <c r="G13" s="8">
         <f ca="1"/>
-        <v>-2.3923158408569178E-2</v>
+        <v>-1.9543084810767719E-2</v>
       </c>
       <c r="H13" s="11">
         <f ca="1"/>
-        <v>53.690730039518037</v>
+        <v>56.552535976513624</v>
       </c>
       <c r="I13" s="8">
         <f ca="1"/>
-        <v>-0.4971408787899792</v>
+        <v>-0.52604105374406429</v>
       </c>
       <c r="J13" s="8">
         <f ca="1"/>
-        <v>4.178108338104785</v>
+        <v>4.5308484790128389</v>
       </c>
       <c r="K13">
         <f ca="1"/>
@@ -1506,7 +1531,10 @@
       </c>
       <c r="L13">
         <f ca="1"/>
-        <v>0.40524967102892617</v>
+        <v>1.1071719075161894</v>
+      </c>
+      <c r="O13">
+        <v>6.0999999999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1515,7 +1543,7 @@
       </c>
       <c r="C14">
         <f ca="1"/>
-        <v>-1.1890813914420324E-2</v>
+        <v>3.6057119161237772E-2</v>
       </c>
       <c r="D14">
         <f ca="1"/>
@@ -1523,27 +1551,27 @@
       </c>
       <c r="E14" s="12">
         <f ca="1"/>
-        <v>99.730547398671661</v>
+        <v>100.69152243351706</v>
       </c>
       <c r="F14" s="11">
         <f ca="1"/>
-        <v>-0.52982138860798333</v>
+        <v>-7.4152232019922559</v>
       </c>
       <c r="G14" s="8">
         <f ca="1"/>
-        <v>5.3125286326768939E-3</v>
+        <v>7.3642974331709576E-2</v>
       </c>
       <c r="H14" s="11">
         <f ca="1"/>
-        <v>53.160908650910052</v>
+        <v>49.137312774521369</v>
       </c>
       <c r="I14" s="8">
         <f ca="1"/>
-        <v>-0.49182835015730231</v>
+        <v>-0.45239807941235471</v>
       </c>
       <c r="J14" s="8">
         <f ca="1"/>
-        <v>4.1105980635367345</v>
+        <v>3.5846614124922169</v>
       </c>
       <c r="K14">
         <f ca="1"/>
@@ -1551,15 +1579,18 @@
       </c>
       <c r="L14">
         <f ca="1"/>
-        <v>0.26945260132833937</v>
+        <v>0</v>
       </c>
       <c r="M14" s="22">
         <f ca="1">f*EXP(sigma*C14-sigma^2*B14/2)</f>
-        <v>99.730547398671661</v>
+        <v>100.69152243351706</v>
       </c>
       <c r="N14" s="23">
         <f ca="1">E14-M14</f>
         <v>0</v>
+      </c>
+      <c r="O14">
+        <v>7.1000000000000008E-2</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1568,7 +1599,7 @@
       </c>
       <c r="C15">
         <f ca="1"/>
-        <v>0.11384089833221395</v>
+        <v>9.9403393980482563E-2</v>
       </c>
       <c r="D15">
         <f ca="1"/>
@@ -1576,27 +1607,27 @@
       </c>
       <c r="E15" s="12">
         <f ca="1"/>
-        <v>102.26202231403074</v>
+        <v>101.96716653861692</v>
       </c>
       <c r="F15" s="11">
         <f ca="1"/>
-        <v>-10.48549244961926</v>
+        <v>-5.2526971126830357</v>
       </c>
       <c r="G15" s="8">
         <f ca="1"/>
-        <v>0.10253554753122274</v>
+        <v>5.1513612577375467E-2</v>
       </c>
       <c r="H15" s="11">
         <f ca="1"/>
-        <v>42.675416201290794</v>
+        <v>43.884615661838332</v>
       </c>
       <c r="I15" s="8">
         <f ca="1"/>
-        <v>-0.38929280262607957</v>
+        <v>-0.40088446683497925</v>
       </c>
       <c r="J15" s="8">
         <f ca="1"/>
-        <v>2.8655469324510818</v>
+        <v>3.0075624693313472</v>
       </c>
       <c r="K15">
         <f ca="1"/>
@@ -1605,6 +1636,9 @@
       <c r="L15">
         <f ca="1"/>
         <v>0</v>
+      </c>
+      <c r="O15">
+        <v>8.1000000000000003E-2</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1613,7 +1647,7 @@
       </c>
       <c r="C16">
         <f ca="1"/>
-        <v>0.14798176549826633</v>
+        <v>7.3321818500526881E-2</v>
       </c>
       <c r="D16">
         <f ca="1"/>
@@ -1621,27 +1655,27 @@
       </c>
       <c r="E16" s="12">
         <f ca="1"/>
-        <v>102.95443781860251</v>
+        <v>101.42854391183027</v>
       </c>
       <c r="F16" s="11">
         <f ca="1"/>
-        <v>-2.8351900773136824</v>
+        <v>2.143900507487591</v>
       </c>
       <c r="G16" s="8">
         <f ca="1"/>
-        <v>2.7538298857102794E-2</v>
+        <v>-2.1137052991229366E-2</v>
       </c>
       <c r="H16" s="11">
         <f ca="1"/>
-        <v>39.840226123977111</v>
+        <v>46.028516169325925</v>
       </c>
       <c r="I16" s="8">
         <f ca="1"/>
-        <v>-0.36175450376897678</v>
+        <v>-0.42202151982620861</v>
       </c>
       <c r="J16" s="8">
         <f ca="1"/>
-        <v>2.5959945600945815</v>
+        <v>3.2234879138959727</v>
       </c>
       <c r="K16">
         <f ca="1"/>
@@ -1653,11 +1687,17 @@
       </c>
       <c r="M16" s="22" cm="1">
         <f t="array" aca="1" ref="M16" ca="1">_xll.OPTION.BLACK.PUT_DELTA(E16,sigma*SQRT(t - B16),k)</f>
-        <v>-0.36175450376897678</v>
+        <v>-0.42202151982620861</v>
       </c>
       <c r="N16" s="23">
         <f ca="1">I16-M16</f>
         <v>0</v>
+      </c>
+      <c r="O16">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="P16">
+        <v>0.47559219130158181</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -1666,7 +1706,7 @@
       </c>
       <c r="C17">
         <f ca="1"/>
-        <v>0.2439146914254427</v>
+        <v>0.1875409047907303</v>
       </c>
       <c r="D17">
         <f ca="1"/>
@@ -1674,27 +1714,27 @@
       </c>
       <c r="E17" s="12">
         <f ca="1"/>
-        <v>104.94045817057381</v>
+        <v>103.76392499732681</v>
       </c>
       <c r="F17" s="11">
         <f ca="1"/>
-        <v>-7.726128573934532</v>
+        <v>-9.5219966162000986</v>
       </c>
       <c r="G17" s="8">
         <f ca="1"/>
-        <v>7.3623926449570276E-2</v>
+        <v>9.1765964100195774E-2</v>
       </c>
       <c r="H17" s="11">
         <f ca="1"/>
-        <v>32.11409755004258</v>
+        <v>36.506519553125827</v>
       </c>
       <c r="I17" s="8">
         <f ca="1"/>
-        <v>-0.2881305773194065</v>
+        <v>-0.33025555572601284</v>
       </c>
       <c r="J17" s="8">
         <f ca="1"/>
-        <v>1.8775427531921203</v>
+        <v>2.2379068388213454</v>
       </c>
       <c r="K17">
         <f ca="1"/>
@@ -1711,7 +1751,7 @@
       </c>
       <c r="C18">
         <f ca="1"/>
-        <v>0.23450021060815388</v>
+        <v>0.14490230064553586</v>
       </c>
       <c r="D18">
         <f ca="1"/>
@@ -1719,27 +1759,27 @@
       </c>
       <c r="E18" s="12">
         <f ca="1"/>
-        <v>104.73467298139198</v>
+        <v>102.87458717579467</v>
       </c>
       <c r="F18" s="11">
         <f ca="1"/>
-        <v>0.60230231891726416</v>
+        <v>3.378911311331287</v>
       </c>
       <c r="G18" s="8">
         <f ca="1"/>
-        <v>-5.7507442547156673E-3</v>
+        <v>-3.284495621408734E-2</v>
       </c>
       <c r="H18" s="11">
         <f ca="1"/>
-        <v>32.716399868959847</v>
+        <v>39.885430864457113</v>
       </c>
       <c r="I18" s="8">
         <f ca="1"/>
-        <v>-0.29388132157412217</v>
+        <v>-0.36310051194010018</v>
       </c>
       <c r="J18" s="8">
         <f ca="1"/>
-        <v>1.9368357585548672</v>
+        <v>2.5316155952996056</v>
       </c>
       <c r="K18">
         <f ca="1"/>
@@ -1756,7 +1796,7 @@
       </c>
       <c r="C19">
         <f ca="1"/>
-        <v>0.13155959211507812</v>
+        <v>0.15501284852962721</v>
       </c>
       <c r="D19">
         <f ca="1"/>
@@ -1764,27 +1804,27 @@
       </c>
       <c r="E19" s="12">
         <f ca="1"/>
-        <v>102.59222030876154</v>
+        <v>103.07457503306709</v>
       </c>
       <c r="F19" s="11">
         <f ca="1"/>
-        <v>8.1577166694131105</v>
+        <v>-0.90061113623286881</v>
       </c>
       <c r="G19" s="8">
         <f ca="1"/>
-        <v>-7.9515938390470997E-2</v>
+        <v>8.7374712526726017E-3</v>
       </c>
       <c r="H19" s="11">
         <f ca="1"/>
-        <v>40.874116538372959</v>
+        <v>38.984819728224245</v>
       </c>
       <c r="I19" s="8">
         <f ca="1"/>
-        <v>-0.37339725996459316</v>
+        <v>-0.35436304068742758</v>
       </c>
       <c r="J19" s="8">
         <f ca="1"/>
-        <v>2.5664625813975093</v>
+        <v>2.4589999019421853</v>
       </c>
       <c r="K19">
         <f ca="1"/>
@@ -1801,7 +1841,7 @@
       </c>
       <c r="C20">
         <f ca="1"/>
-        <v>0.19752777212954131</v>
+        <v>9.0962539212198504E-2</v>
       </c>
       <c r="D20">
         <f ca="1"/>
@@ -1809,27 +1849,27 @@
       </c>
       <c r="E20" s="12">
         <f ca="1"/>
-        <v>103.94643729018649</v>
+        <v>101.75446382033344</v>
       </c>
       <c r="F20" s="11">
         <f ca="1"/>
-        <v>-5.5667785951393727</v>
+        <v>5.3432275268879934</v>
       </c>
       <c r="G20" s="8">
         <f ca="1"/>
-        <v>5.3554299120407933E-2</v>
+        <v>-5.2510988965776106E-2</v>
       </c>
       <c r="H20" s="11">
         <f ca="1"/>
-        <v>35.307337943233584</v>
+        <v>44.328047255112239</v>
       </c>
       <c r="I20" s="8">
         <f ca="1"/>
-        <v>-0.31984296084418523</v>
+        <v>-0.40687402965320368</v>
       </c>
       <c r="J20" s="8">
         <f ca="1"/>
-        <v>2.0608016711359127</v>
+        <v>2.9267985253320461</v>
       </c>
       <c r="K20">
         <f ca="1"/>
@@ -1841,14 +1881,14 @@
       </c>
       <c r="M20" s="7">
         <f t="array" aca="1" ref="M20:M21" ca="1">_xll.MONTE.STDEV(C20)</f>
-        <v>-3.682849923316224E-3</v>
+        <v>-3.1843942103343902E-4</v>
       </c>
       <c r="N20" s="7">
         <v>0</v>
       </c>
       <c r="O20" s="7">
         <f t="array" aca="1" ref="O20:O21" ca="1">_xll.MONTE.STDEV(E20)</f>
-        <v>99.928175749452592</v>
+        <v>99.991262829712568</v>
       </c>
       <c r="P20" s="7">
         <f>f*EXP(mu*B20)</f>
@@ -1861,7 +1901,7 @@
       </c>
       <c r="C21">
         <f ca="1"/>
-        <v>0.15712315267085941</v>
+        <v>0.17497657189107368</v>
       </c>
       <c r="D21">
         <f ca="1"/>
@@ -1869,27 +1909,27 @@
       </c>
       <c r="E21" s="12">
         <f ca="1"/>
-        <v>103.10159038124907</v>
+        <v>103.47039160876635</v>
       </c>
       <c r="F21" s="11">
         <f ca="1"/>
-        <v>3.240845210041265</v>
+        <v>-7.2505845498642172</v>
       </c>
       <c r="G21" s="8">
         <f ca="1"/>
-        <v>-3.1433513276150904E-2</v>
+        <v>7.0074003172613142E-2</v>
       </c>
       <c r="H21" s="11">
         <f ca="1"/>
-        <v>38.548183153274849</v>
+        <v>37.077462705248024</v>
       </c>
       <c r="I21" s="8">
         <f ca="1"/>
-        <v>-0.35127647412033614</v>
+        <v>-0.33680002648059054</v>
       </c>
       <c r="J21" s="8">
         <f ca="1"/>
-        <v>2.3310200079505137</v>
+        <v>2.228632071458442</v>
       </c>
       <c r="K21">
         <f ca="1"/>
@@ -1901,7 +1941,7 @@
       </c>
       <c r="M21" s="7">
         <f ca="1"/>
-        <v>0.20232311453400736</v>
+        <v>0.32967459134372368</v>
       </c>
       <c r="N21" s="7">
         <f>SQRT(B20)</f>
@@ -1909,7 +1949,7 @@
       </c>
       <c r="O21" s="7">
         <f ca="1"/>
-        <v>4.0412704612687227</v>
+        <v>6.6135540268305384</v>
       </c>
       <c r="P21" s="7"/>
     </row>
@@ -1919,7 +1959,7 @@
       </c>
       <c r="C22">
         <f ca="1"/>
-        <v>0.27658291732044243</v>
+        <v>0.16905236248228836</v>
       </c>
       <c r="D22">
         <f ca="1"/>
@@ -1927,27 +1967,27 @@
       </c>
       <c r="E22" s="12">
         <f ca="1"/>
-        <v>105.58610376221513</v>
+        <v>103.33960065631187</v>
       </c>
       <c r="F22" s="11">
         <f ca="1"/>
-        <v>-9.8531293577049386</v>
+        <v>0.40879450386675326</v>
       </c>
       <c r="G22" s="8">
         <f ca="1"/>
-        <v>9.3318429287765459E-2</v>
+        <v>-3.9558359164394985E-3</v>
       </c>
       <c r="H22" s="11">
         <f ca="1"/>
-        <v>28.695053795569912</v>
+        <v>37.486257209114775</v>
       </c>
       <c r="I22" s="8">
         <f ca="1"/>
-        <v>-0.25795804483257068</v>
+        <v>-0.34075586239703004</v>
       </c>
       <c r="J22" s="8">
         <f ca="1"/>
-        <v>1.45826890757996</v>
+        <v>2.2726824677085347</v>
       </c>
       <c r="K22">
         <f ca="1"/>
@@ -1964,7 +2004,7 @@
       </c>
       <c r="C23">
         <f ca="1"/>
-        <v>0.30080512919534746</v>
+        <v>5.5825695089188596E-2</v>
       </c>
       <c r="D23">
         <f ca="1"/>
@@ -1972,27 +2012,27 @@
       </c>
       <c r="E23" s="12">
         <f ca="1"/>
-        <v>106.09036297227692</v>
+        <v>101.01765716789524</v>
       </c>
       <c r="F23" s="11">
         <f ca="1"/>
-        <v>-1.9881387455944044</v>
+        <v>9.7346846130147338</v>
       </c>
       <c r="G23" s="8">
         <f ca="1"/>
-        <v>1.874005036738291E-2</v>
+        <v>-9.6366168904860994E-2</v>
       </c>
       <c r="H23" s="11">
         <f ca="1"/>
-        <v>26.706915049975507</v>
+        <v>47.220941822129511</v>
       </c>
       <c r="I23" s="8">
         <f ca="1"/>
-        <v>-0.23921799446518777</v>
+        <v>-0.43712203130189103</v>
       </c>
       <c r="J23" s="8">
         <f ca="1"/>
-        <v>1.3281911876636059</v>
+        <v>3.0638983235411104</v>
       </c>
       <c r="K23">
         <f ca="1"/>
@@ -2009,7 +2049,7 @@
       </c>
       <c r="C24">
         <f ca="1"/>
-        <v>0.21880316989657339</v>
+        <v>9.6038008267417485E-2</v>
       </c>
       <c r="D24">
         <f ca="1"/>
@@ -2017,27 +2057,27 @@
       </c>
       <c r="E24" s="12">
         <f ca="1"/>
-        <v>104.35628064445481</v>
+        <v>101.82521730568719</v>
       </c>
       <c r="F24" s="11">
         <f ca="1"/>
-        <v>6.2089444014754882</v>
+        <v>-3.6235949350723127</v>
       </c>
       <c r="G24" s="8">
         <f ca="1"/>
-        <v>-5.9497563185770874E-2</v>
+        <v>3.5586419857018325E-2</v>
       </c>
       <c r="H24" s="11">
         <f ca="1"/>
-        <v>32.915859451450999</v>
+        <v>43.597346887057199</v>
       </c>
       <c r="I24" s="8">
         <f ca="1"/>
-        <v>-0.29871555765095864</v>
+        <v>-0.40153561144487271</v>
       </c>
       <c r="J24" s="8">
         <f ca="1"/>
-        <v>1.7430148843627364</v>
+        <v>2.7108959957110628</v>
       </c>
       <c r="K24">
         <f ca="1"/>
@@ -2054,7 +2094,7 @@
       </c>
       <c r="C25">
         <f ca="1"/>
-        <v>4.4187135085260287E-2</v>
+        <v>0.12874126294007976</v>
       </c>
       <c r="D25">
         <f ca="1"/>
@@ -2062,27 +2102,27 @@
       </c>
       <c r="E25" s="12">
         <f ca="1"/>
-        <v>100.76666665536476</v>
+        <v>102.48520416774744</v>
       </c>
       <c r="F25" s="11">
         <f ca="1"/>
-        <v>15.023751695241897</v>
+        <v>-2.9732969129766111</v>
       </c>
       <c r="G25" s="8">
         <f ca="1"/>
-        <v>-0.14909445944684369</v>
+        <v>2.9011962625453025E-2</v>
       </c>
       <c r="H25" s="11">
         <f ca="1"/>
-        <v>47.939611146692897</v>
+        <v>40.624049974080592</v>
       </c>
       <c r="I25" s="8">
         <f ca="1"/>
-        <v>-0.44781001709780233</v>
+        <v>-0.37252364881941968</v>
       </c>
       <c r="J25" s="8">
         <f ca="1"/>
-        <v>2.8152884288654576</v>
+        <v>2.4458877675081183</v>
       </c>
       <c r="K25">
         <f ca="1"/>
@@ -2099,7 +2139,7 @@
       </c>
       <c r="C26">
         <f ca="1"/>
-        <v>9.2712700741800408E-2</v>
+        <v>0.11211030194572283</v>
       </c>
       <c r="D26">
         <f ca="1"/>
@@ -2107,27 +2147,27 @@
       </c>
       <c r="E26" s="12">
         <f ca="1"/>
-        <v>101.74123988666912</v>
+        <v>102.13671371447953</v>
       </c>
       <c r="F26" s="11">
         <f ca="1"/>
-        <v>-4.4672763536693134</v>
+        <v>1.4359177404104746</v>
       </c>
       <c r="G26" s="8">
         <f ca="1"/>
-        <v>4.3908216163332292E-2</v>
+        <v>-1.4058781491879058E-2</v>
       </c>
       <c r="H26" s="11">
         <f ca="1"/>
-        <v>43.472334793023585</v>
+        <v>42.059967714491066</v>
       </c>
       <c r="I26" s="8">
         <f ca="1"/>
-        <v>-0.40390180093447003</v>
+        <v>-0.38658243031129874</v>
       </c>
       <c r="J26" s="8">
         <f ca="1"/>
-        <v>2.3788647734919905</v>
+        <v>2.5757087027382113</v>
       </c>
       <c r="K26">
         <f ca="1"/>
@@ -2144,7 +2184,7 @@
       </c>
       <c r="C27">
         <f ca="1"/>
-        <v>0.14180755318005117</v>
+        <v>8.9196958816675206E-2</v>
       </c>
       <c r="D27">
         <f ca="1"/>
@@ -2152,27 +2192,27 @@
       </c>
       <c r="E27" s="12">
         <f ca="1"/>
-        <v>102.73693547434601</v>
+        <v>101.66159259085774</v>
       </c>
       <c r="F27" s="11">
         <f ca="1"/>
-        <v>-4.5359028134167731</v>
+        <v>2.0546189348192634</v>
       </c>
       <c r="G27" s="8">
         <f ca="1"/>
-        <v>4.4150653243393789E-2</v>
+        <v>-2.0210375250446666E-2</v>
       </c>
       <c r="H27" s="11">
         <f ca="1"/>
-        <v>38.936431979606809</v>
+        <v>44.114586649310326</v>
       </c>
       <c r="I27" s="8">
         <f ca="1"/>
-        <v>-0.35975114769107625</v>
+        <v>-0.40679280556174541</v>
       </c>
       <c r="J27" s="8">
         <f ca="1"/>
-        <v>1.9767015324467891</v>
+        <v>2.7593821814001558</v>
       </c>
       <c r="K27">
         <f ca="1"/>
@@ -2189,7 +2229,7 @@
       </c>
       <c r="C28">
         <f ca="1"/>
-        <v>0.1088449142298322</v>
+        <v>6.4549603857941174E-2</v>
       </c>
       <c r="D28">
         <f ca="1"/>
@@ -2197,27 +2237,27 @@
       </c>
       <c r="E28" s="12">
         <f ca="1"/>
-        <v>102.05370239811604</v>
+        <v>101.15359525310326</v>
       </c>
       <c r="F28" s="11">
         <f ca="1"/>
-        <v>2.9385851055174705</v>
+        <v>2.2780716922099802</v>
       </c>
       <c r="G28" s="8">
         <f ca="1"/>
-        <v>-2.8794497764068561E-2</v>
+        <v>-2.2520916696137816E-2</v>
       </c>
       <c r="H28" s="11">
         <f ca="1"/>
-        <v>41.875017085124277</v>
+        <v>46.392658341520303</v>
       </c>
       <c r="I28" s="8">
         <f ca="1"/>
-        <v>-0.38854564545514481</v>
+        <v>-0.42931372225788322</v>
       </c>
       <c r="J28" s="8">
         <f ca="1"/>
-        <v>2.2224954157610171</v>
+        <v>2.9660318436431936</v>
       </c>
       <c r="K28">
         <f ca="1"/>
@@ -2234,7 +2274,7 @@
       </c>
       <c r="C29">
         <f ca="1"/>
-        <v>0.12947690149019384</v>
+        <v>6.2188497152387646E-2</v>
       </c>
       <c r="D29">
         <f ca="1"/>
@@ -2242,27 +2282,27 @@
       </c>
       <c r="E29" s="12">
         <f ca="1"/>
-        <v>102.46748884710233</v>
+        <v>101.09775149954979</v>
       </c>
       <c r="F29" s="11">
         <f ca="1"/>
-        <v>-1.9791257291352438</v>
+        <v>0.22012762358362506</v>
       </c>
       <c r="G29" s="8">
         <f ca="1"/>
-        <v>1.9314669964132836E-2</v>
+        <v>-2.1773740792306873E-3</v>
       </c>
       <c r="H29" s="11">
         <f ca="1"/>
-        <v>39.895891355989036</v>
+        <v>46.612785965103924</v>
       </c>
       <c r="I29" s="8">
         <f ca="1"/>
-        <v>-0.36923097549101197</v>
+        <v>-0.43149109633711391</v>
       </c>
       <c r="J29" s="8">
         <f ca="1"/>
-        <v>2.0617204928590525</v>
+        <v>2.9900063333460878</v>
       </c>
       <c r="K29">
         <f ca="1"/>
@@ -2279,7 +2319,7 @@
       </c>
       <c r="C30">
         <f ca="1"/>
-        <v>0.1815435997714332</v>
+        <v>7.2600270186219881E-2</v>
       </c>
       <c r="D30">
         <f ca="1"/>
@@ -2287,27 +2327,27 @@
       </c>
       <c r="E30" s="12">
         <f ca="1"/>
-        <v>103.53180973723302</v>
+        <v>101.30038785521418</v>
       </c>
       <c r="F30" s="11">
         <f ca="1"/>
-        <v>-4.8907513265215385</v>
+        <v>-1.0062419614177343</v>
       </c>
       <c r="G30" s="8">
         <f ca="1"/>
-        <v>4.7239117513104611E-2</v>
+        <v>9.9332488524715989E-3</v>
       </c>
       <c r="H30" s="11">
         <f ca="1"/>
-        <v>35.005140029467498</v>
+        <v>45.606544003686189</v>
       </c>
       <c r="I30" s="8">
         <f ca="1"/>
-        <v>-0.32199185797790736</v>
+        <v>-0.42155784748464231</v>
       </c>
       <c r="J30" s="8">
         <f ca="1"/>
-        <v>1.6687402523606352</v>
+        <v>2.902570550082693</v>
       </c>
       <c r="K30">
         <f ca="1"/>
@@ -2324,7 +2364,7 @@
       </c>
       <c r="C31">
         <f ca="1"/>
-        <v>0.13129339866010115</v>
+        <v>0.14251084649889106</v>
       </c>
       <c r="D31">
         <f ca="1"/>
@@ -2332,27 +2372,27 @@
       </c>
       <c r="E31" s="12">
         <f ca="1"/>
-        <v>102.48832254725441</v>
+        <v>102.71851214713912</v>
       </c>
       <c r="F31" s="11">
         <f ca="1"/>
-        <v>4.5139151061057055</v>
+        <v>-6.7620924864904453</v>
       </c>
       <c r="G31" s="8">
         <f ca="1"/>
-        <v>-4.4043213840527728E-2</v>
+        <v>6.5831293163632343E-2</v>
       </c>
       <c r="H31" s="11">
         <f ca="1"/>
-        <v>39.519055135573204</v>
+        <v>38.844451517195743</v>
       </c>
       <c r="I31" s="8">
         <f ca="1"/>
-        <v>-0.36603507181843509</v>
+        <v>-0.35572655432100997</v>
       </c>
       <c r="J31" s="8">
         <f ca="1"/>
-        <v>2.0047346314379979</v>
+        <v>2.304749126113137</v>
       </c>
       <c r="K31">
         <f ca="1"/>
@@ -2369,7 +2409,7 @@
       </c>
       <c r="C32">
         <f ca="1"/>
-        <v>0.11767599000023436</v>
+        <v>7.5715597939813417E-2</v>
       </c>
       <c r="D32">
         <f ca="1"/>
@@ -2377,27 +2417,27 @@
       </c>
       <c r="E32" s="12">
         <f ca="1"/>
-        <v>102.20140078513391</v>
+        <v>101.34730743768709</v>
       </c>
       <c r="F32" s="11">
         <f ca="1"/>
-        <v>1.222208864793187</v>
+        <v>6.3314404515109484</v>
       </c>
       <c r="G32" s="8">
         <f ca="1"/>
-        <v>-1.1958826937829681E-2</v>
+        <v>-6.2472705112603055E-2</v>
       </c>
       <c r="H32" s="11">
         <f ca="1"/>
-        <v>40.741264000366392</v>
+        <v>45.175891968706694</v>
       </c>
       <c r="I32" s="8">
         <f ca="1"/>
-        <v>-0.37799389875626477</v>
+        <v>-0.41819925943361302</v>
       </c>
       <c r="J32" s="8">
         <f ca="1"/>
-        <v>2.1097580592420471</v>
+        <v>2.79252305267525</v>
       </c>
       <c r="K32">
         <f ca="1"/>
@@ -2414,7 +2454,7 @@
       </c>
       <c r="C33">
         <f ca="1"/>
-        <v>4.6145283947534838E-2</v>
+        <v>1.7974698379898804E-2</v>
       </c>
       <c r="D33">
         <f ca="1"/>
@@ -2422,27 +2462,27 @@
       </c>
       <c r="E33" s="12">
         <f ca="1"/>
-        <v>100.74164232321678</v>
+        <v>100.17564804838226</v>
       </c>
       <c r="F33" s="11">
         <f ca="1"/>
-        <v>6.9736725132514445</v>
+        <v>5.7252477830215556</v>
       </c>
       <c r="G33" s="8">
         <f ca="1"/>
-        <v>-6.922333557832322E-2</v>
+        <v>-5.7152091297242302E-2</v>
       </c>
       <c r="H33" s="11">
         <f ca="1"/>
-        <v>47.714936513617836</v>
+        <v>50.901139751728252</v>
       </c>
       <c r="I33" s="8">
         <f ca="1"/>
-        <v>-0.44721723433458799</v>
+        <v>-0.47535135073085533</v>
       </c>
       <c r="J33" s="8">
         <f ca="1"/>
-        <v>2.6615378515045478</v>
+        <v>3.2825101415909756</v>
       </c>
       <c r="K33">
         <f ca="1"/>
@@ -2459,7 +2499,7 @@
       </c>
       <c r="C34">
         <f ca="1"/>
-        <v>0.13106043341461404</v>
+        <v>-8.908321745576292E-3</v>
       </c>
       <c r="D34">
         <f ca="1"/>
@@ -2467,27 +2507,27 @@
       </c>
       <c r="E34" s="12">
         <f ca="1"/>
-        <v>102.45895431496534</v>
+        <v>99.630517836461451</v>
       </c>
       <c r="F34" s="11">
         <f ca="1"/>
-        <v>-8.5634925307338889</v>
+        <v>2.770578563455909</v>
       </c>
       <c r="G34" s="8">
         <f ca="1"/>
-        <v>8.3579737739750581E-2</v>
+        <v>-2.7808533204692121E-2</v>
       </c>
       <c r="H34" s="11">
         <f ca="1"/>
-        <v>39.151443982883947</v>
+        <v>53.671718315184158</v>
       </c>
       <c r="I34" s="8">
         <f ca="1"/>
-        <v>-0.36363749659483741</v>
+        <v>-0.50315988393554745</v>
       </c>
       <c r="J34" s="8">
         <f ca="1"/>
-        <v>1.8935263320651359</v>
+        <v>3.5416385241517219</v>
       </c>
       <c r="K34">
         <f ca="1"/>
@@ -2495,7 +2535,7 @@
       </c>
       <c r="L34">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.36948216353854946</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -2504,7 +2544,7 @@
       </c>
       <c r="C35">
         <f ca="1"/>
-        <v>0.18992040056174278</v>
+        <v>-9.0162032866715036E-2</v>
       </c>
       <c r="D35">
         <f ca="1"/>
@@ -2512,27 +2552,27 @@
       </c>
       <c r="E35" s="12">
         <f ca="1"/>
-        <v>103.66393431776801</v>
+        <v>98.016690894124793</v>
       </c>
       <c r="F35" s="11">
         <f ca="1"/>
-        <v>-5.83157270937724</v>
+        <v>8.2197483491183281</v>
       </c>
       <c r="G35" s="8">
         <f ca="1"/>
-        <v>5.6254595658132456E-2</v>
+        <v>-8.3860700398436183E-2</v>
       </c>
       <c r="H35" s="11">
         <f ca="1"/>
-        <v>33.319871273506706</v>
+        <v>61.891466664302484</v>
       </c>
       <c r="I35" s="8">
         <f ca="1"/>
-        <v>-0.30738290093670495</v>
+        <v>-0.58702058433398363</v>
       </c>
       <c r="J35" s="8">
         <f ca="1"/>
-        <v>1.4553504203991317</v>
+        <v>4.3536515011498977</v>
       </c>
       <c r="K35">
         <f ca="1"/>
@@ -2540,7 +2580,7 @@
       </c>
       <c r="L35">
         <f ca="1"/>
-        <v>0</v>
+        <v>1.9833091058752075</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -2549,7 +2589,7 @@
       </c>
       <c r="C36">
         <f ca="1"/>
-        <v>0.17059370153070766</v>
+        <v>-2.3751379940768785E-2</v>
       </c>
       <c r="D36">
         <f ca="1"/>
@@ -2557,27 +2597,27 @@
       </c>
       <c r="E36" s="12">
         <f ca="1"/>
-        <v>103.25575061241874</v>
+        <v>99.319299732901072</v>
       </c>
       <c r="F36" s="11">
         <f ca="1"/>
-        <v>1.6819071965339163</v>
+        <v>-6.6162832945702794</v>
       </c>
       <c r="G36" s="8">
         <f ca="1"/>
-        <v>-1.6288750859476397E-2</v>
+        <v>6.6616290211101159E-2</v>
       </c>
       <c r="H36" s="11">
         <f ca="1"/>
-        <v>35.00177847004062</v>
+        <v>55.275183369732204</v>
       </c>
       <c r="I36" s="8">
         <f ca="1"/>
-        <v>-0.32367165179618135</v>
+        <v>-0.52040429412288247</v>
       </c>
       <c r="J36" s="8">
         <f ca="1"/>
-        <v>1.5808191118644856</v>
+        <v>3.5889932994528309</v>
       </c>
       <c r="K36">
         <f ca="1"/>
@@ -2585,7 +2625,7 @@
       </c>
       <c r="L36">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.68070026709892772</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -2594,7 +2634,7 @@
       </c>
       <c r="C37">
         <f ca="1"/>
-        <v>0.19393707863599449</v>
+        <v>1.9560517712158415E-2</v>
       </c>
       <c r="D37">
         <f ca="1"/>
@@ -2602,27 +2642,27 @@
       </c>
       <c r="E37" s="12">
         <f ca="1"/>
-        <v>103.73064647554276</v>
+        <v>100.17536393726903</v>
       </c>
       <c r="F37" s="11">
         <f ca="1"/>
-        <v>-2.4294207933435925</v>
+        <v>-4.4775551609734618</v>
       </c>
       <c r="G37" s="8">
         <f ca="1"/>
-        <v>2.3420472887117239E-2</v>
+        <v>4.4697168894513417E-2</v>
       </c>
       <c r="H37" s="11">
         <f ca="1"/>
-        <v>32.572357676697024</v>
+        <v>50.797628208758745</v>
       </c>
       <c r="I37" s="8">
         <f ca="1"/>
-        <v>-0.30025117890906411</v>
+        <v>-0.47570712522836905</v>
       </c>
       <c r="J37" s="8">
         <f ca="1"/>
-        <v>1.4271087834159566</v>
+        <v>3.1434938114548601</v>
       </c>
       <c r="K37">
         <f ca="1"/>
@@ -2639,7 +2679,7 @@
       </c>
       <c r="C38">
         <f ca="1"/>
-        <v>0.17099699734336438</v>
+        <v>3.7013913685201127E-2</v>
       </c>
       <c r="D38">
         <f ca="1"/>
@@ -2647,27 +2687,27 @@
       </c>
       <c r="E38" s="12">
         <f ca="1"/>
-        <v>103.24755853967895</v>
+        <v>100.51761328645499</v>
       </c>
       <c r="F38" s="11">
         <f ca="1"/>
-        <v>2.0534700018870131</v>
+        <v>-1.8262714757265377</v>
       </c>
       <c r="G38" s="8">
         <f ca="1"/>
-        <v>-1.9888799608736962E-2</v>
+        <v>1.8168671300640926E-2</v>
       </c>
       <c r="H38" s="11">
         <f ca="1"/>
-        <v>34.625827678584038</v>
+        <v>48.971356733032209</v>
       </c>
       <c r="I38" s="8">
         <f ca="1"/>
-        <v>-0.32013997851780107</v>
+        <v>-0.45753845392772813</v>
       </c>
       <c r="J38" s="8">
         <f ca="1"/>
-        <v>1.5721565056758138</v>
+        <v>2.9806833574423308</v>
       </c>
       <c r="K38">
         <f ca="1"/>
@@ -2684,7 +2724,7 @@
       </c>
       <c r="C39">
         <f ca="1"/>
-        <v>0.1674825430027958</v>
+        <v>3.354537031581116E-2</v>
       </c>
       <c r="D39">
         <f ca="1"/>
@@ -2692,27 +2732,27 @@
       </c>
       <c r="E39" s="12">
         <f ca="1"/>
-        <v>103.16675860183693</v>
+        <v>100.4398720156037</v>
       </c>
       <c r="F39" s="11">
         <f ca="1"/>
-        <v>0.1796400001016174</v>
+        <v>0.40185683644352471</v>
       </c>
       <c r="G39" s="8">
         <f ca="1"/>
-        <v>-1.7412585462234231E-3</v>
+        <v>-4.0009692204814318E-3</v>
       </c>
       <c r="H39" s="11">
         <f ca="1"/>
-        <v>34.805467678685659</v>
+        <v>49.373213569475737</v>
       </c>
       <c r="I39" s="8">
         <f ca="1"/>
-        <v>-0.32188123706402449</v>
+        <v>-0.46153942314820956</v>
       </c>
       <c r="J39" s="8">
         <f ca="1"/>
-        <v>1.598023796040799</v>
+        <v>3.0162529783140073</v>
       </c>
       <c r="K39">
         <f ca="1"/>
@@ -2729,7 +2769,7 @@
       </c>
       <c r="C40">
         <f ca="1"/>
-        <v>0.23508076271824754</v>
+        <v>-2.1534713617973808E-3</v>
       </c>
       <c r="D40">
         <f ca="1"/>
@@ -2737,27 +2777,27 @@
       </c>
       <c r="E40" s="12">
         <f ca="1"/>
-        <v>104.56264218258417</v>
+        <v>99.717330836503407</v>
       </c>
       <c r="F40" s="11">
         <f ca="1"/>
-        <v>-6.8565264829055765</v>
+        <v>3.9624528619971753</v>
       </c>
       <c r="G40" s="8">
         <f ca="1"/>
-        <v>6.5573385865029254E-2</v>
+        <v>-3.9736852448387483E-2</v>
       </c>
       <c r="H40" s="11">
         <f ca="1"/>
-        <v>27.948941195780083</v>
+        <v>53.335666431472916</v>
       </c>
       <c r="I40" s="8">
         <f ca="1"/>
-        <v>-0.25630785119899524</v>
+        <v>-0.50127627559659704</v>
       </c>
       <c r="J40" s="8">
         <f ca="1"/>
-        <v>1.1487150622725153</v>
+        <v>3.3497342173167866</v>
       </c>
       <c r="K40">
         <f ca="1"/>
@@ -2765,7 +2805,7 @@
       </c>
       <c r="L40">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.28266916349659255</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -2774,7 +2814,7 @@
       </c>
       <c r="C41">
         <f ca="1"/>
-        <v>0.19423050513462889</v>
+        <v>-4.6633720756715291E-2</v>
       </c>
       <c r="D41">
         <f ca="1"/>
@@ -2782,27 +2822,27 @@
       </c>
       <c r="E41" s="12">
         <f ca="1"/>
-        <v>103.70354367408432</v>
+        <v>98.826268195168595</v>
       </c>
       <c r="F41" s="11">
         <f ca="1"/>
-        <v>3.6944745822141503</v>
+        <v>5.0165976931659406</v>
       </c>
       <c r="G41" s="8">
         <f ca="1"/>
-        <v>-3.562534558920194E-2</v>
+        <v>-5.076178413677257E-2</v>
       </c>
       <c r="H41" s="11">
         <f ca="1"/>
-        <v>31.643415777994235</v>
+        <v>58.352264124638857</v>
       </c>
       <c r="I41" s="8">
         <f ca="1"/>
-        <v>-0.29193319678819718</v>
+        <v>-0.55203805973336961</v>
       </c>
       <c r="J41" s="8">
         <f ca="1"/>
-        <v>1.3689087549543792</v>
+        <v>3.7964027794883677</v>
       </c>
       <c r="K41">
         <f ca="1"/>
@@ -2810,7 +2850,7 @@
       </c>
       <c r="L41">
         <f ca="1"/>
-        <v>0</v>
+        <v>1.1737318048314052</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -2819,7 +2859,7 @@
       </c>
       <c r="C42">
         <f ca="1"/>
-        <v>2.7090583458080186E-2</v>
+        <v>-1.8333759578466089E-2</v>
       </c>
       <c r="D42">
         <f ca="1"/>
@@ -2827,27 +2867,27 @@
       </c>
       <c r="E42" s="12">
         <f ca="1"/>
-        <v>100.28622050011549</v>
+        <v>99.379259412884934</v>
       </c>
       <c r="F42" s="11">
         <f ca="1"/>
-        <v>17.834808846545787</v>
+        <v>-3.0234254956731501</v>
       </c>
       <c r="G42" s="8">
         <f ca="1"/>
-        <v>-0.17783907657109532</v>
+        <v>3.0423103508066096E-2</v>
       </c>
       <c r="H42" s="11">
         <f ca="1"/>
-        <v>49.478224624540019</v>
+        <v>55.328838628965705</v>
       </c>
       <c r="I42" s="8">
         <f ca="1"/>
-        <v>-0.4697722733592925</v>
+        <v>-0.52161495622530352</v>
       </c>
       <c r="J42" s="8">
         <f ca="1"/>
-        <v>2.3665388335894804</v>
+        <v>3.4911305806106512</v>
       </c>
       <c r="K42">
         <f ca="1"/>
@@ -2855,7 +2895,7 @@
       </c>
       <c r="L42">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.62074058711506552</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -2864,7 +2904,7 @@
       </c>
       <c r="C43">
         <f ca="1"/>
-        <v>-4.5897536299875058E-2</v>
+        <v>3.0261062606854152E-2</v>
       </c>
       <c r="D43">
         <f ca="1"/>
@@ -2872,27 +2912,27 @@
       </c>
       <c r="E43" s="12">
         <f ca="1"/>
-        <v>98.825006872821149</v>
+        <v>100.34180407456776</v>
       </c>
       <c r="F43" s="11">
         <f ca="1"/>
-        <v>8.3985842306233618</v>
+        <v>-5.5282130016268844</v>
       </c>
       <c r="G43" s="8">
         <f ca="1"/>
-        <v>-8.4984403203043346E-2</v>
+        <v>5.5093817104570508E-2</v>
       </c>
       <c r="H43" s="11">
         <f ca="1"/>
-        <v>57.876808855163382</v>
+        <v>49.800625627338817</v>
       </c>
       <c r="I43" s="8">
         <f ca="1"/>
-        <v>-0.55475667656233585</v>
+        <v>-0.46652113912073301</v>
       </c>
       <c r="J43" s="8">
         <f ca="1"/>
-        <v>3.0529764811471196</v>
+        <v>2.9890528890420569</v>
       </c>
       <c r="K43">
         <f ca="1"/>
@@ -2900,7 +2940,7 @@
       </c>
       <c r="L43">
         <f ca="1"/>
-        <v>1.1749931271788512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -2909,7 +2949,7 @@
       </c>
       <c r="C44">
         <f ca="1"/>
-        <v>8.3831227005368464E-2</v>
+        <v>-2.2664748330877203E-2</v>
       </c>
       <c r="D44">
         <f ca="1"/>
@@ -2917,27 +2957,27 @@
       </c>
       <c r="E44" s="12">
         <f ca="1"/>
-        <v>101.41453574128651</v>
+        <v>99.277328949781904</v>
       </c>
       <c r="F44" s="11">
         <f ca="1"/>
-        <v>-15.240353788182336</v>
+        <v>6.237757876964201</v>
       </c>
       <c r="G44" s="8">
         <f ca="1"/>
-        <v>0.15027780462419343</v>
+        <v>-6.2831644877547888E-2</v>
       </c>
       <c r="H44" s="11">
         <f ca="1"/>
-        <v>42.636455066981043</v>
+        <v>56.03838350430302</v>
       </c>
       <c r="I44" s="8">
         <f ca="1"/>
-        <v>-0.40447887193814241</v>
+        <v>-0.5293527839982809</v>
       </c>
       <c r="J44" s="8">
         <f ca="1"/>
-        <v>1.616418052215046</v>
+        <v>3.4856530368228391</v>
       </c>
       <c r="K44">
         <f ca="1"/>
@@ -2945,7 +2985,7 @@
       </c>
       <c r="L44">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.72267105021809641</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -2954,7 +2994,7 @@
       </c>
       <c r="C45">
         <f ca="1"/>
-        <v>6.9209358111326905E-2</v>
+        <v>0.15845469058869105</v>
       </c>
       <c r="D45">
         <f ca="1"/>
@@ -2962,27 +3002,27 @@
       </c>
       <c r="E45" s="12">
         <f ca="1"/>
-        <v>101.1103058083702</v>
+        <v>102.93123296132308</v>
       </c>
       <c r="F45" s="11">
         <f ca="1"/>
-        <v>1.6588771564875977</v>
+        <v>-21.586282801758674</v>
       </c>
       <c r="G45" s="8">
         <f ca="1"/>
-        <v>-1.6406608042820015E-2</v>
+        <v>0.20971557593087248</v>
       </c>
       <c r="H45" s="11">
         <f ca="1"/>
-        <v>44.295332223468641</v>
+        <v>34.452100702544342</v>
       </c>
       <c r="I45" s="8">
         <f ca="1"/>
-        <v>-0.42088547998096243</v>
+        <v>-0.31963720806740842</v>
       </c>
       <c r="J45" s="8">
         <f ca="1"/>
-        <v>1.7394726322908554</v>
+        <v>1.5514487758510285</v>
       </c>
       <c r="K45">
         <f ca="1"/>
@@ -2999,7 +3039,7 @@
       </c>
       <c r="C46">
         <f ca="1"/>
-        <v>5.3076080761499701E-2</v>
+        <v>0.15510755560686768</v>
       </c>
       <c r="D46">
         <f ca="1"/>
@@ -3007,27 +3047,27 @@
       </c>
       <c r="E46" s="12">
         <f ca="1"/>
-        <v>100.77652102237596</v>
+        <v>102.85412241454451</v>
       </c>
       <c r="F46" s="11">
         <f ca="1"/>
-        <v>1.9111485806755801</v>
+        <v>0.14631311602975589</v>
       </c>
       <c r="G46" s="8">
         <f ca="1"/>
-        <v>-1.8964224615882874E-2</v>
+        <v>-1.4225304012614459E-3</v>
       </c>
       <c r="H46" s="11">
         <f ca="1"/>
-        <v>46.206480804144221</v>
+        <v>34.598413818574102</v>
       </c>
       <c r="I46" s="8">
         <f ca="1"/>
-        <v>-0.4398497045968453</v>
+        <v>-0.32105973846866986</v>
       </c>
       <c r="J46" s="8">
         <f ca="1"/>
-        <v>1.8799578021543866</v>
+        <v>1.5760961757358842</v>
       </c>
       <c r="K46">
         <f ca="1"/>
@@ -3044,7 +3084,7 @@
       </c>
       <c r="C47">
         <f ca="1"/>
-        <v>3.1431246078661962E-2</v>
+        <v>5.9858488567427787E-2</v>
       </c>
       <c r="D47">
         <f ca="1"/>
@@ -3052,27 +3092,27 @@
       </c>
       <c r="E47" s="12">
         <f ca="1"/>
-        <v>100.33317873213257</v>
+        <v>100.90524253109936</v>
       </c>
       <c r="F47" s="11">
         <f ca="1"/>
-        <v>2.6762655840504777</v>
+        <v>11.125580627417531</v>
       </c>
       <c r="G47" s="8">
         <f ca="1"/>
-        <v>-2.6673784463617123E-2</v>
+        <v>-0.11025770662003598</v>
       </c>
       <c r="H47" s="11">
         <f ca="1"/>
-        <v>48.882746388194697</v>
+        <v>45.723994445991636</v>
       </c>
       <c r="I47" s="8">
         <f ca="1"/>
-        <v>-0.46652348906046243</v>
+        <v>-0.43131744508870584</v>
       </c>
       <c r="J47" s="8">
         <f ca="1"/>
-        <v>2.0749617775532272</v>
+        <v>2.2018030414216412</v>
       </c>
       <c r="K47">
         <f ca="1"/>
@@ -3089,7 +3129,7 @@
       </c>
       <c r="C48">
         <f ca="1"/>
-        <v>6.7568945143510306E-2</v>
+        <v>0.13469089892384351</v>
       </c>
       <c r="D48">
         <f ca="1"/>
@@ -3097,27 +3137,27 @@
       </c>
       <c r="E48" s="12">
         <f ca="1"/>
-        <v>101.05288311557099</v>
+        <v>102.41860297394057</v>
       </c>
       <c r="F48" s="11">
         <f ca="1"/>
-        <v>-4.5708545774636047</v>
+        <v>-9.3729237868874655</v>
       </c>
       <c r="G48" s="8">
         <f ca="1"/>
-        <v>4.5232302498841748E-2</v>
+        <v>9.1515833205343733E-2</v>
       </c>
       <c r="H48" s="11">
         <f ca="1"/>
-        <v>44.31189181073109</v>
+        <v>36.351070659104167</v>
       </c>
       <c r="I48" s="8">
         <f ca="1"/>
-        <v>-0.42129118656162068</v>
+        <v>-0.33980161188336211</v>
       </c>
       <c r="J48" s="8">
         <f ca="1"/>
-        <v>1.7392027774994219</v>
+        <v>1.5490642817170581</v>
       </c>
       <c r="K48">
         <f ca="1"/>
@@ -3134,7 +3174,7 @@
       </c>
       <c r="C49">
         <f ca="1"/>
-        <v>6.4569380979022442E-2</v>
+        <v>0.10417310401581845</v>
       </c>
       <c r="D49">
         <f ca="1"/>
@@ -3142,27 +3182,27 @@
       </c>
       <c r="E49" s="12">
         <f ca="1"/>
-        <v>100.98419931568384</v>
+        <v>101.78724553136507</v>
       </c>
       <c r="F49" s="11">
         <f ca="1"/>
-        <v>0.32461629299261652</v>
+        <v>3.5474870950807262</v>
       </c>
       <c r="G49" s="8">
         <f ca="1"/>
-        <v>-3.2145255910565051E-3</v>
+        <v>-3.4851980486961809E-2</v>
       </c>
       <c r="H49" s="11">
         <f ca="1"/>
-        <v>44.636508103723706</v>
+        <v>39.898557754184893</v>
       </c>
       <c r="I49" s="8">
         <f ca="1"/>
-        <v>-0.42450571215267718</v>
+        <v>-0.37465359237032392</v>
       </c>
       <c r="J49" s="8">
         <f ca="1"/>
-        <v>1.7681386570514448</v>
+        <v>1.7636005583787693</v>
       </c>
       <c r="K49">
         <f ca="1"/>
@@ -3179,7 +3219,7 @@
       </c>
       <c r="C50">
         <f ca="1"/>
-        <v>7.2227660424275877E-2</v>
+        <v>0.25439758735494339</v>
       </c>
       <c r="D50">
         <f ca="1"/>
@@ -3187,27 +3227,27 @@
       </c>
       <c r="E50" s="12">
         <f ca="1"/>
-        <v>101.13090007707169</v>
+        <v>104.88344683333936</v>
       </c>
       <c r="F50" s="11">
         <f ca="1"/>
-        <v>-1.0686851626404281</v>
+        <v>-17.816643232268802</v>
       </c>
       <c r="G50" s="8">
         <f ca="1"/>
-        <v>1.0567345507910886E-2</v>
+        <v>0.16987087829578668</v>
       </c>
       <c r="H50" s="11">
         <f ca="1"/>
-        <v>43.567822941083278</v>
+        <v>22.08191452191609</v>
       </c>
       <c r="I50" s="8">
         <f ca="1"/>
-        <v>-0.4139383666447663</v>
+        <v>-0.20478271407453724</v>
       </c>
       <c r="J50" s="8">
         <f ca="1"/>
-        <v>1.7058633458651542</v>
+        <v>0.60359761789242583</v>
       </c>
       <c r="K50">
         <f ca="1"/>
@@ -3224,7 +3264,7 @@
       </c>
       <c r="C51">
         <f ca="1"/>
-        <v>0.11674648122295003</v>
+        <v>0.2729941107133993</v>
       </c>
       <c r="D51">
         <f ca="1"/>
@@ -3232,27 +3272,27 @@
       </c>
       <c r="E51" s="12">
         <f ca="1"/>
-        <v>102.02720385978898</v>
+        <v>105.26584506115424</v>
       </c>
       <c r="F51" s="11">
         <f ca="1"/>
-        <v>-5.99995800462872</v>
+        <v>-2.3017124467928629</v>
       </c>
       <c r="G51" s="8">
         <f ca="1"/>
-        <v>5.8807433484839688E-2</v>
+        <v>2.1865710054915555E-2</v>
       </c>
       <c r="H51" s="11">
         <f ca="1"/>
-        <v>37.567864936454555</v>
+        <v>19.780202075123228</v>
       </c>
       <c r="I51" s="8">
         <f ca="1"/>
-        <v>-0.35513093315992661</v>
+        <v>-0.18291700401962169</v>
       </c>
       <c r="J51" s="8">
         <f ca="1"/>
-        <v>1.3348488220296275</v>
+        <v>0.52528907094320587</v>
       </c>
       <c r="K51">
         <f ca="1"/>
@@ -3269,7 +3309,7 @@
       </c>
       <c r="C52">
         <f ca="1"/>
-        <v>0.15333688299694814</v>
+        <v>0.30363133677245852</v>
       </c>
       <c r="D52">
         <f ca="1"/>
@@ -3277,27 +3317,27 @@
       </c>
       <c r="E52" s="12">
         <f ca="1"/>
-        <v>102.76836401230453</v>
+        <v>105.90436324774393</v>
       </c>
       <c r="F52" s="11">
         <f ca="1"/>
-        <v>-4.9849966940534918</v>
+        <v>-3.3339778599980532</v>
       </c>
       <c r="G52" s="8">
         <f ca="1"/>
-        <v>4.8507113467882335E-2</v>
+        <v>3.1481024556078208E-2</v>
       </c>
       <c r="H52" s="11">
         <f ca="1"/>
-        <v>32.582868242401062</v>
+        <v>16.446224215125174</v>
       </c>
       <c r="I52" s="8">
         <f ca="1"/>
-        <v>-0.30662381969204427</v>
+        <v>-0.15143597946354348</v>
       </c>
       <c r="J52" s="8">
         <f ca="1"/>
-        <v>1.071639925445826</v>
+        <v>0.40849323724017594</v>
       </c>
       <c r="K52">
         <f ca="1"/>
@@ -3314,7 +3354,7 @@
       </c>
       <c r="C53">
         <f ca="1"/>
-        <v>0.17281910037395992</v>
+        <v>0.26351286560042125</v>
       </c>
       <c r="D53">
         <f ca="1"/>
@@ -3322,27 +3362,27 @@
       </c>
       <c r="E53" s="12">
         <f ca="1"/>
-        <v>103.16132304061512</v>
+        <v>105.04961465810005</v>
       </c>
       <c r="F53" s="11">
         <f ca="1"/>
-        <v>-2.826113909072475</v>
+        <v>3.1524920088344204</v>
       </c>
       <c r="G53" s="8">
         <f ca="1"/>
-        <v>2.739509174344168E-2</v>
+        <v>-3.0009553286746316E-2</v>
       </c>
       <c r="H53" s="11">
         <f ca="1"/>
-        <v>29.756754333328587</v>
+        <v>19.598716223959595</v>
       </c>
       <c r="I53" s="8">
         <f ca="1"/>
-        <v>-0.2792287279486026</v>
+        <v>-0.1814455327502898</v>
       </c>
       <c r="J53" s="8">
         <f ca="1"/>
-        <v>0.95114932720276002</v>
+        <v>0.53793292710797758</v>
       </c>
       <c r="K53">
         <f ca="1"/>
@@ -3359,7 +3399,7 @@
       </c>
       <c r="C54">
         <f ca="1"/>
-        <v>0.20236569666031617</v>
+        <v>0.32570305794946414</v>
       </c>
       <c r="D54">
         <f ca="1"/>
@@ -3367,27 +3407,27 @@
       </c>
       <c r="E54" s="12">
         <f ca="1"/>
-        <v>103.76443949894161</v>
+        <v>106.35587663069819</v>
       </c>
       <c r="F54" s="11">
         <f ca="1"/>
-        <v>-4.0741786210405477</v>
+        <v>-6.2093662897898154</v>
       </c>
       <c r="G54" s="8">
         <f ca="1"/>
-        <v>3.9263726963822743E-2</v>
+        <v>5.8382916736709645E-2</v>
       </c>
       <c r="H54" s="11">
         <f ca="1"/>
-        <v>25.682575712288038</v>
+        <v>13.389349934169779</v>
       </c>
       <c r="I54" s="8">
         <f ca="1"/>
-        <v>-0.23996500098477985</v>
+        <v>-0.12306261601358015</v>
       </c>
       <c r="J54" s="8">
         <f ca="1"/>
-        <v>0.78274188573938375</v>
+        <v>0.30091752757846457</v>
       </c>
       <c r="K54">
         <f ca="1"/>
@@ -3404,7 +3444,7 @@
       </c>
       <c r="C55">
         <f ca="1"/>
-        <v>0.24673109089851386</v>
+        <v>0.24414150733173162</v>
       </c>
       <c r="D55">
         <f ca="1"/>
@@ -3412,27 +3452,27 @@
       </c>
       <c r="E55" s="12">
         <f ca="1"/>
-        <v>104.68087162226105</v>
+        <v>104.62666968653495</v>
       </c>
       <c r="F55" s="11">
         <f ca="1"/>
-        <v>-5.5999022657134887</v>
+        <v>6.9099971952783257</v>
       </c>
       <c r="G55" s="8">
         <f ca="1"/>
-        <v>5.3494990812845256E-2</v>
+        <v>-6.6044319445327959E-2</v>
       </c>
       <c r="H55" s="11">
         <f ca="1"/>
-        <v>20.08267344657455</v>
+        <v>20.299347129448105</v>
       </c>
       <c r="I55" s="8">
         <f ca="1"/>
-        <v>-0.1864700101719346</v>
+        <v>-0.18910693545890811</v>
       </c>
       <c r="J55" s="8">
         <f ca="1"/>
-        <v>0.56283025036455214</v>
+        <v>0.51371825775604307</v>
       </c>
       <c r="K55">
         <f ca="1"/>
@@ -3449,7 +3489,7 @@
       </c>
       <c r="C56">
         <f ca="1"/>
-        <v>0.26682296351729523</v>
+        <v>0.12316257154747211</v>
       </c>
       <c r="D56">
         <f ca="1"/>
@@ -3457,27 +3497,27 @@
       </c>
       <c r="E56" s="12">
         <f ca="1"/>
-        <v>105.09395700872382</v>
+        <v>102.1173559354601</v>
       </c>
       <c r="F56" s="11">
         <f ca="1"/>
-        <v>-2.7362221257260768</v>
+        <v>14.625937690340049</v>
       </c>
       <c r="G56" s="8">
         <f ca="1"/>
-        <v>2.6035960616640819E-2</v>
+        <v>-0.14322675666988371</v>
       </c>
       <c r="H56" s="11">
         <f ca="1"/>
-        <v>17.346451320848473</v>
+        <v>34.925284819788153</v>
       </c>
       <c r="I56" s="8">
         <f ca="1"/>
-        <v>-0.16043404955529378</v>
+        <v>-0.33233369212879182</v>
       </c>
       <c r="J56" s="8">
         <f ca="1"/>
-        <v>0.4858022141489613</v>
+        <v>0.98824689132670329</v>
       </c>
       <c r="K56">
         <f ca="1"/>
@@ -3494,7 +3534,7 @@
       </c>
       <c r="C57">
         <f ca="1"/>
-        <v>0.25425282938647992</v>
+        <v>6.2677697925070192E-2</v>
       </c>
       <c r="D57">
         <f ca="1"/>
@@ -3502,27 +3542,27 @@
       </c>
       <c r="E57" s="12">
         <f ca="1"/>
-        <v>104.82169374674926</v>
+        <v>100.88141575142484</v>
       </c>
       <c r="F57" s="11">
         <f ca="1"/>
-        <v>0.5727808069488235</v>
+        <v>8.8745282214770302</v>
       </c>
       <c r="G57" s="8">
         <f ca="1"/>
-        <v>-5.4643345902487539E-3</v>
+        <v>-8.7969901645156945E-2</v>
       </c>
       <c r="H57" s="11">
         <f ca="1"/>
-        <v>17.919232127797297</v>
+        <v>43.799813041265182</v>
       </c>
       <c r="I57" s="8">
         <f ca="1"/>
-        <v>-0.16589838414554253</v>
+        <v>-0.42030359377394877</v>
       </c>
       <c r="J57" s="8">
         <f ca="1"/>
-        <v>0.52948251181267381</v>
+        <v>1.3989914559374768</v>
       </c>
       <c r="K57">
         <f ca="1"/>
@@ -3539,7 +3579,7 @@
       </c>
       <c r="C58">
         <f ca="1"/>
-        <v>0.25542284574852964</v>
+        <v>1.7151767407182071E-2</v>
       </c>
       <c r="D58">
         <f ca="1"/>
@@ -3547,27 +3587,27 @@
       </c>
       <c r="E58" s="12">
         <f ca="1"/>
-        <v>104.83783787369809</v>
+        <v>99.95904373751155</v>
       </c>
       <c r="F58" s="11">
         <f ca="1"/>
-        <v>-0.8844914107639823</v>
+        <v>7.3451693249783077</v>
       </c>
       <c r="G58" s="8">
         <f ca="1"/>
-        <v>8.4367574599312212E-3</v>
+        <v>-7.3481788644021329E-2</v>
       </c>
       <c r="H58" s="11">
         <f ca="1"/>
-        <v>17.034740717033316</v>
+        <v>51.144982366243489</v>
       </c>
       <c r="I58" s="8">
         <f ca="1"/>
-        <v>-0.15746162668561131</v>
+        <v>-0.4937853824179701</v>
       </c>
       <c r="J58" s="8">
         <f ca="1"/>
-        <v>0.52680422723842568</v>
+        <v>1.7866677281817473</v>
       </c>
       <c r="K58">
         <f ca="1"/>
@@ -3575,7 +3615,7 @@
       </c>
       <c r="L58">
         <f ca="1"/>
-        <v>0</v>
+        <v>4.0956262488450079E-2</v>
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -3584,7 +3624,7 @@
       </c>
       <c r="C59">
         <f ca="1"/>
-        <v>0.23903040396952602</v>
+        <v>0.1395904243472374</v>
       </c>
       <c r="D59">
         <f ca="1"/>
@@ -3592,27 +3632,27 @@
       </c>
       <c r="E59" s="12">
         <f ca="1"/>
-        <v>104.48633181086082</v>
+        <v>102.42883562428176</v>
       </c>
       <c r="F59" s="11">
         <f ca="1"/>
-        <v>0.95933538367490601</v>
+        <v>-20.388154259563823</v>
       </c>
       <c r="G59" s="8">
         <f ca="1"/>
-        <v>-9.1814438027308376E-3</v>
+        <v>0.19904701772018007</v>
       </c>
       <c r="H59" s="11">
         <f ca="1"/>
-        <v>17.99407610070822</v>
+        <v>30.756828106679666</v>
       </c>
       <c r="I59" s="8">
         <f ca="1"/>
-        <v>-0.16664307048834215</v>
+        <v>-0.29473836469779002</v>
       </c>
       <c r="J59" s="8">
         <f ca="1"/>
-        <v>0.58215294368263315</v>
+        <v>0.56712059688012317</v>
       </c>
       <c r="K59">
         <f ca="1"/>
@@ -3629,7 +3669,7 @@
       </c>
       <c r="C60">
         <f ca="1"/>
-        <v>0.25917663718609779</v>
+        <v>8.2180146848640723E-2</v>
       </c>
       <c r="D60">
         <f ca="1"/>
@@ -3637,27 +3677,27 @@
       </c>
       <c r="E60" s="12">
         <f ca="1"/>
-        <v>104.89978999282914</v>
+        <v>101.25136783307032</v>
       </c>
       <c r="F60" s="11">
         <f ca="1"/>
-        <v>-3.065651046076483</v>
+        <v>8.8273868799983291</v>
       </c>
       <c r="G60" s="8">
         <f ca="1"/>
-        <v>2.9224568002338691E-2</v>
+        <v>-8.7182890156622284E-2</v>
       </c>
       <c r="H60" s="11">
         <f ca="1"/>
-        <v>14.928425054631738</v>
+        <v>39.584214986677992</v>
       </c>
       <c r="I60" s="8">
         <f ca="1"/>
-        <v>-0.13741850248600346</v>
+        <v>-0.38192125485441231</v>
       </c>
       <c r="J60" s="8">
         <f ca="1"/>
-        <v>0.51325300272090679</v>
+        <v>0.91416552814609986</v>
       </c>
       <c r="K60">
         <f ca="1"/>
@@ -3674,7 +3714,7 @@
       </c>
       <c r="C61">
         <f ca="1"/>
-        <v>0.22153407632619898</v>
+        <v>-7.435032907348732E-4</v>
       </c>
       <c r="D61">
         <f ca="1"/>
@@ -3682,27 +3722,27 @@
       </c>
       <c r="E61" s="12">
         <f ca="1"/>
-        <v>104.10468727385663</v>
+        <v>99.578022770691973</v>
       </c>
       <c r="F61" s="11">
         <f ca="1"/>
-        <v>3.2585188807843708</v>
+        <v>14.819247558515539</v>
       </c>
       <c r="G61" s="8">
         <f ca="1"/>
-        <v>-3.1300405064495773E-2</v>
+        <v>-0.14882046405602234</v>
       </c>
       <c r="H61" s="11">
         <f ca="1"/>
-        <v>18.18694393541611</v>
+        <v>54.403462545193534</v>
       </c>
       <c r="I61" s="8">
         <f ca="1"/>
-        <v>-0.16871890755049923</v>
+        <v>-0.53074171891043465</v>
       </c>
       <c r="J61" s="8">
         <f ca="1"/>
-        <v>0.62251482768466104</v>
+        <v>1.5532515741740767</v>
       </c>
       <c r="K61">
         <f ca="1"/>
@@ -3710,7 +3750,7 @@
       </c>
       <c r="L61">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.42197722930802684</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -3719,7 +3759,7 @@
       </c>
       <c r="C62">
         <f ca="1"/>
-        <v>0.34986740327129229</v>
+        <v>-6.4071755409013345E-2</v>
       </c>
       <c r="D62">
         <f ca="1"/>
@@ -3727,27 +3767,27 @@
       </c>
       <c r="E62" s="12">
         <f ca="1"/>
-        <v>106.80274907979674</v>
+        <v>98.316890153024474</v>
       </c>
       <c r="F62" s="11">
         <f ca="1"/>
-        <v>-12.470615196331172</v>
+        <v>12.027505175935577</v>
       </c>
       <c r="G62" s="8">
         <f ca="1"/>
-        <v>0.11676305435746659</v>
+        <v>-0.12233406851269879</v>
       </c>
       <c r="H62" s="11">
         <f ca="1"/>
-        <v>5.716328739084938</v>
+        <v>66.430967721129107</v>
       </c>
       <c r="I62" s="8">
         <f ca="1"/>
-        <v>-5.1955853193032642E-2</v>
+        <v>-0.65307578742313344</v>
       </c>
       <c r="J62" s="8">
         <f ca="1"/>
-        <v>0.16730078728271636</v>
+        <v>2.2225872674489295</v>
       </c>
       <c r="K62">
         <f ca="1"/>
@@ -3755,7 +3795,7 @@
       </c>
       <c r="L62">
         <f ca="1"/>
-        <v>0</v>
+        <v>1.6831098469755261</v>
       </c>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -3764,7 +3804,7 @@
       </c>
       <c r="C63">
         <f ca="1"/>
-        <v>0.30804756201138606</v>
+        <v>-0.17014232484757599</v>
       </c>
       <c r="D63">
         <f ca="1"/>
@@ -3772,27 +3812,27 @@
       </c>
       <c r="E63" s="12">
         <f ca="1"/>
-        <v>105.90470691302096</v>
+        <v>96.245452088078352</v>
       </c>
       <c r="F63" s="11">
         <f ca="1"/>
-        <v>1.6972433372242102</v>
+        <v>17.219990874117357</v>
       </c>
       <c r="G63" s="8">
         <f ca="1"/>
-        <v>-1.6026136955538228E-2</v>
+        <v>-0.17891745012905758</v>
       </c>
       <c r="H63" s="11">
         <f ca="1"/>
-        <v>7.4135720763091477</v>
+        <v>83.650958595246465</v>
       </c>
       <c r="I63" s="8">
         <f ca="1"/>
-        <v>-6.798199014857087E-2</v>
+        <v>-0.83199323755219101</v>
       </c>
       <c r="J63" s="8">
         <f ca="1"/>
-        <v>0.21395933426087144</v>
+        <v>3.5753933128118689</v>
       </c>
       <c r="K63">
         <f ca="1"/>
@@ -3800,7 +3840,7 @@
       </c>
       <c r="L63">
         <f ca="1"/>
-        <v>0</v>
+        <v>3.7545479119216481</v>
       </c>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -3809,7 +3849,7 @@
       </c>
       <c r="C64">
         <f ca="1"/>
-        <v>0.35157195070483821</v>
+        <v>-0.17974057643266811</v>
       </c>
       <c r="D64">
         <f ca="1"/>
@@ -3817,27 +3857,27 @@
       </c>
       <c r="E64" s="12">
         <f ca="1"/>
-        <v>106.82207245815043</v>
+        <v>96.053187134702227</v>
       </c>
       <c r="F64" s="11">
         <f ca="1"/>
-        <v>-3.4905051893575996</v>
+        <v>2.5434540801210219</v>
       </c>
       <c r="G64" s="8">
         <f ca="1"/>
-        <v>3.2675879703841837E-2</v>
+        <v>-2.647964274786796E-2</v>
       </c>
       <c r="H64" s="11">
         <f ca="1"/>
-        <v>3.9230668869515481</v>
+        <v>86.194412675367488</v>
       </c>
       <c r="I64" s="8">
         <f ca="1"/>
-        <v>-3.5306110444729033E-2</v>
+        <v>-0.85847288030005897</v>
       </c>
       <c r="J64" s="8">
         <f ca="1"/>
-        <v>0.15159499880924177</v>
+        <v>3.7353564538391026</v>
       </c>
       <c r="K64">
         <f ca="1"/>
@@ -3845,7 +3885,7 @@
       </c>
       <c r="L64">
         <f ca="1"/>
-        <v>0</v>
+        <v>3.9468128652977725</v>
       </c>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -3854,7 +3894,7 @@
       </c>
       <c r="C65">
         <f ca="1"/>
-        <v>0.46611710373429643</v>
+        <v>-0.27793757405723818</v>
       </c>
       <c r="D65">
         <f ca="1"/>
@@ -3862,27 +3902,27 @@
       </c>
       <c r="E65" s="12">
         <f ca="1"/>
-        <v>109.28876580006653</v>
+        <v>94.177629176542382</v>
       </c>
       <c r="F65" s="11">
         <f ca="1"/>
-        <v>-3.3209073419850448</v>
+        <v>9.2573512619484291</v>
       </c>
       <c r="G65" s="8">
         <f ca="1"/>
-        <v>3.0386538979315869E-2</v>
+        <v>-9.8296711680805782E-2</v>
       </c>
       <c r="H65" s="11">
         <f ca="1"/>
-        <v>0.60215954496650337</v>
+        <v>95.451763937315917</v>
       </c>
       <c r="I65" s="8">
         <f ca="1"/>
-        <v>-4.9195714654131639E-3</v>
+        <v>-0.95676959198086475</v>
       </c>
       <c r="J65" s="8">
         <f ca="1"/>
-        <v>6.4505651246274054E-2</v>
+        <v>5.345472096350278</v>
       </c>
       <c r="K65">
         <f ca="1"/>
@@ -3890,7 +3930,7 @@
       </c>
       <c r="L65">
         <f ca="1"/>
-        <v>0</v>
+        <v>5.8223708234576179</v>
       </c>
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -3899,7 +3939,7 @@
       </c>
       <c r="C66">
         <f ca="1"/>
-        <v>0.49721089244020522</v>
+        <v>-0.31607686244446576</v>
       </c>
       <c r="D66">
         <f ca="1"/>
@@ -3907,27 +3947,27 @@
       </c>
       <c r="E66" s="12">
         <f ca="1"/>
-        <v>109.96172651520659</v>
+        <v>93.454511837312154</v>
       </c>
       <c r="F66" s="11">
         <f ca="1"/>
-        <v>-0.37224789265676761</v>
+        <v>2.2995138695749424</v>
       </c>
       <c r="G66" s="8">
         <f ca="1"/>
-        <v>3.3852496177866898E-3</v>
+        <v>-2.460570200803136E-2</v>
       </c>
       <c r="H66" s="11">
         <f ca="1"/>
-        <v>0.22991165230973576</v>
+        <v>97.751277806890855</v>
       </c>
       <c r="I66" s="8">
         <f ca="1"/>
-        <v>-1.5343218476264742E-3</v>
+        <v>-0.98137529398889611</v>
       </c>
       <c r="J66" s="8">
         <f ca="1"/>
-        <v>6.1194972914726919E-2</v>
+        <v>6.0373287779598712</v>
       </c>
       <c r="K66">
         <f ca="1"/>
@@ -3935,7 +3975,7 @@
       </c>
       <c r="L66">
         <f ca="1"/>
-        <v>0</v>
+        <v>6.5454881626878461</v>
       </c>
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -3944,7 +3984,7 @@
       </c>
       <c r="C67">
         <f ca="1"/>
-        <v>0.52923357277271632</v>
+        <v>-0.45201200208590486</v>
       </c>
       <c r="D67">
         <f ca="1"/>
@@ -3952,27 +3992,27 @@
       </c>
       <c r="E67" s="12">
         <f ca="1"/>
-        <v>110.65938728531806</v>
+        <v>90.940712715400565</v>
       </c>
       <c r="F67" s="11">
         <f ca="1"/>
-        <v>-0.13629339697629025</v>
+        <v>1.6282301474829415</v>
       </c>
       <c r="G67" s="8">
         <f ca="1"/>
-        <v>1.2316478549160847E-3</v>
+        <v>-1.7904303791619669E-2</v>
       </c>
       <c r="H67" s="11">
         <f ca="1"/>
-        <v>9.3618255333445505E-2</v>
+        <v>99.379507954373793</v>
       </c>
       <c r="I67" s="8">
         <f ca="1"/>
-        <v>-3.0267399271038942E-4</v>
+        <v>-0.99927959778051578</v>
       </c>
       <c r="J67" s="8">
         <f ca="1"/>
-        <v>6.0124536752912988E-2</v>
+        <v>8.5043091302548817</v>
       </c>
       <c r="K67">
         <f ca="1"/>
@@ -3980,7 +4020,7 @@
       </c>
       <c r="L67">
         <f ca="1"/>
-        <v>0</v>
+        <v>9.059287284599435</v>
       </c>
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -3989,7 +4029,7 @@
       </c>
       <c r="C68">
         <f ca="1"/>
-        <v>0.4937014162954958</v>
+        <v>-0.4910217058211539</v>
       </c>
       <c r="D68">
         <f ca="1"/>
@@ -3997,27 +4037,27 @@
       </c>
       <c r="E68" s="12">
         <f ca="1"/>
-        <v>109.86699185929547</v>
+        <v>90.226740844561263</v>
       </c>
       <c r="F68" s="11">
         <f ca="1"/>
-        <v>-9.5767088279430455E-3</v>
+        <v>5.8963592978762289E-2</v>
       </c>
       <c r="G68" s="8">
         <f ca="1"/>
-        <v>8.7166387882975371E-5</v>
+        <v>-6.5350463096458533E-4</v>
       </c>
       <c r="H68" s="11">
         <f ca="1"/>
-        <v>8.4041546505502454E-2</v>
+        <v>99.438471547352549</v>
       </c>
       <c r="I68" s="8">
         <f ca="1"/>
-        <v>-2.1550760482741405E-4</v>
+        <v>-0.99993310241148037</v>
       </c>
       <c r="J68" s="8">
         <f ca="1"/>
-        <v>6.0364374240312692E-2</v>
+        <v>9.2177666541737722</v>
       </c>
       <c r="K68">
         <f ca="1"/>
@@ -4025,7 +4065,7 @@
       </c>
       <c r="L68">
         <f ca="1"/>
-        <v>0</v>
+        <v>9.7732591554387369</v>
       </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -4034,7 +4074,7 @@
       </c>
       <c r="C69">
         <f ca="1"/>
-        <v>0.44571247597793906</v>
+        <v>-0.43895432168021919</v>
       </c>
       <c r="D69">
         <f ca="1"/>
@@ -4042,27 +4082,27 @@
       </c>
       <c r="E69" s="12">
         <f ca="1"/>
-        <v>108.80885088767852</v>
+        <v>91.16393065548823</v>
       </c>
       <c r="F69" s="11">
         <f ca="1"/>
-        <v>-4.7083683763562796E-3</v>
+        <v>1.6678650939920753E-3</v>
       </c>
       <c r="G69" s="8">
         <f ca="1"/>
-        <v>4.3271924461518729E-5</v>
+        <v>-1.8295230163944964E-5</v>
       </c>
       <c r="H69" s="11">
         <f ca="1"/>
-        <v>7.933317812914617E-2</v>
+        <v>99.440139412446541</v>
       </c>
       <c r="I69" s="8">
         <f ca="1"/>
-        <v>-1.7223568036589532E-4</v>
+        <v>-0.99995139764164431</v>
       </c>
       <c r="J69" s="8">
         <f ca="1"/>
-        <v>6.0592411666675609E-2</v>
+        <v>8.2806395389851417</v>
       </c>
       <c r="K69">
         <f ca="1"/>
@@ -4070,7 +4110,7 @@
       </c>
       <c r="L69">
         <f ca="1"/>
-        <v>0</v>
+        <v>8.8360693445117704</v>
       </c>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -4079,7 +4119,7 @@
       </c>
       <c r="C70">
         <f ca="1"/>
-        <v>0.31190112515968615</v>
+        <v>-0.4374470538728088</v>
       </c>
       <c r="D70">
         <f ca="1"/>
@@ -4087,27 +4127,27 @@
       </c>
       <c r="E70" s="12">
         <f ca="1"/>
-        <v>105.92702472354769</v>
+        <v>91.184121468191762</v>
       </c>
       <c r="F70" s="11">
         <f ca="1"/>
-        <v>0.18643585876324351</v>
+        <v>4.2432326316572426E-3</v>
       </c>
       <c r="G70" s="8">
         <f ca="1"/>
-        <v>-1.7600405491404181E-3</v>
+        <v>-4.6534775609341494E-5</v>
       </c>
       <c r="H70" s="11">
         <f ca="1"/>
-        <v>0.26576903689238968</v>
+        <v>99.444382645078193</v>
       </c>
       <c r="I70" s="8">
         <f ca="1"/>
-        <v>-1.9322762295063134E-3</v>
+        <v>-0.99999793241725365</v>
       </c>
       <c r="J70" s="8">
         <f ca="1"/>
-        <v>6.1088764956750918E-2</v>
+        <v>8.2604497076027172</v>
       </c>
       <c r="K70">
         <f ca="1"/>
@@ -4115,7 +4155,7 @@
       </c>
       <c r="L70">
         <f ca="1"/>
-        <v>0</v>
+        <v>8.815878531808238</v>
       </c>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -4124,7 +4164,7 @@
       </c>
       <c r="C71">
         <f ca="1"/>
-        <v>0.34974236315913937</v>
+        <v>-0.42040478461385189</v>
       </c>
       <c r="D71">
         <f ca="1"/>
@@ -4132,27 +4172,27 @@
       </c>
       <c r="E71" s="12">
         <f ca="1"/>
-        <v>106.72320980729164</v>
+        <v>91.48812926581212</v>
       </c>
       <c r="F71" s="11">
         <f ca="1"/>
-        <v>-0.20484328675106836</v>
+        <v>1.8871231842413887E-4</v>
       </c>
       <c r="G71" s="8">
         <f ca="1"/>
-        <v>1.9193883609849305E-3</v>
+        <v>-2.0626973131765425E-6</v>
       </c>
       <c r="H71" s="11">
         <f ca="1"/>
-        <v>6.0925750141321316E-2</v>
+        <v>99.444571357396612</v>
       </c>
       <c r="I71" s="8">
         <f ca="1"/>
-        <v>-1.2887868521382906E-5</v>
+        <v>-0.99999999511456683</v>
       </c>
       <c r="J71" s="8">
         <f ca="1"/>
-        <v>5.9550315445144976E-2</v>
+        <v>7.9564425385436266</v>
       </c>
       <c r="K71">
         <f ca="1"/>
@@ -4160,7 +4200,7 @@
       </c>
       <c r="L71">
         <f ca="1"/>
-        <v>0</v>
+        <v>8.5118707341878803</v>
       </c>
     </row>
     <row r="72" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -4169,7 +4209,7 @@
       </c>
       <c r="C72">
         <f ca="1"/>
-        <v>0.32523252431649596</v>
+        <v>-0.41508054815429979</v>
       </c>
       <c r="D72">
         <f ca="1"/>
@@ -4177,15 +4217,15 @@
       </c>
       <c r="E72" s="12">
         <f ca="1"/>
-        <v>106.19284045436892</v>
+        <v>91.578275485005179</v>
       </c>
       <c r="F72" s="11">
         <f ca="1"/>
-        <v>-6.0925750141321316E-2</v>
+        <v>-99.444571357396612</v>
       </c>
       <c r="G72" s="8">
         <f ca="1"/>
-        <v>1.2887868521382906E-5</v>
+        <v>0.99999999511456683</v>
       </c>
       <c r="H72" s="11">
         <f ca="1"/>
@@ -4201,11 +4241,11 @@
       </c>
       <c r="K72">
         <f ca="1"/>
-        <v>5.9557150775633221E-2</v>
+        <v>7.8662963197909761</v>
       </c>
       <c r="L72">
         <f ca="1"/>
-        <v>0</v>
+        <v>8.4217245149948212</v>
       </c>
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -4982,7 +5022,7 @@
     <row r="1" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="18" cm="1">
         <f t="array" aca="1" ref="B1" ca="1">_xll.MONTE.COUNT()</f>
-        <v>10441</v>
+        <v>17749</v>
       </c>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -5032,7 +5072,7 @@
       </c>
       <c r="G3" s="8" cm="1">
         <f t="array" aca="1" ref="G3" ca="1">_xlfn.TAKE(S_,-1)</f>
-        <v>97.017723233977435</v>
+        <v>101.48219873345587</v>
       </c>
       <c r="N3" s="7">
         <v>1</v>
@@ -5058,15 +5098,15 @@
       </c>
       <c r="G4" s="11">
         <f ca="1">MAX(k - last,0)</f>
-        <v>2.9822767660225651</v>
+        <v>0</v>
       </c>
       <c r="H4" s="11">
         <f t="array" aca="1" ref="H4:I4" ca="1">_xll.MONTE.STDEV(G4)</f>
-        <v>3.9698955412770243</v>
+        <v>3.9366394375921883</v>
       </c>
       <c r="I4" s="11">
         <f ca="1"/>
-        <v>5.4744558475318081</v>
+        <v>5.465712572665498</v>
       </c>
       <c r="M4">
         <v>1E-3</v>
@@ -5093,7 +5133,7 @@
       </c>
       <c r="G5" s="11" cm="1">
         <f t="array" aca="1" ref="G5" ca="1">_xlfn.TAKE(A,-1)</f>
-        <v>1.7754076462248207</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
@@ -5123,19 +5163,19 @@
       </c>
       <c r="G6" s="11">
         <f ca="1">payoff-hedge</f>
-        <v>1.2068691197977444</v>
+        <v>-8.6508240375046483</v>
       </c>
       <c r="H6" s="8">
         <f t="array" aca="1" ref="H6:I6" ca="1">_xll.MONTE.STDEV(error)</f>
-        <v>-4.9406313496674494E-2</v>
+        <v>-9.3383454035984567E-2</v>
       </c>
       <c r="I6" s="13">
         <f ca="1"/>
-        <v>11.9850450694938</v>
+        <v>11.967738579190495</v>
       </c>
       <c r="J6" s="17">
         <f ca="1">I6/put</f>
-        <v>3.0054570887160263</v>
+        <v>3.0011171873087918</v>
       </c>
       <c r="K6" s="16" t="s">
         <v>30</v>
@@ -5267,7 +5307,7 @@
       </c>
       <c r="C11">
         <f ca="1"/>
-        <v>-3.6216919301546975E-2</v>
+        <v>3.2518242925888306E-2</v>
       </c>
       <c r="D11">
         <f ca="1"/>
@@ -5275,27 +5315,27 @@
       </c>
       <c r="E11" s="12">
         <f ca="1"/>
-        <v>99.270336677371986</v>
+        <v>100.64443244635675</v>
       </c>
       <c r="F11" s="11">
         <f ca="1"/>
-        <v>0</v>
+        <v>100.64443244635675</v>
       </c>
       <c r="G11" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H11" s="11">
         <f ca="1"/>
-        <v>-96.012238832325508</v>
+        <v>4.6321936140312374</v>
       </c>
       <c r="I11" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="8">
         <f ca="1"/>
-        <v>3.2580978450464784</v>
+        <v>4.6321936140312374</v>
       </c>
       <c r="K11">
         <f ca="1"/>
@@ -5303,11 +5343,11 @@
       </c>
       <c r="L11">
         <f ca="1"/>
-        <v>0.72966332262801359</v>
+        <v>0</v>
       </c>
       <c r="M11" s="22">
         <f ca="1" xml:space="preserve"> - G11*E11</f>
-        <v>0</v>
+        <v>100.64443244635675</v>
       </c>
       <c r="N11" s="22">
         <f ca="1">F11-M11</f>
@@ -5320,7 +5360,7 @@
       </c>
       <c r="C12">
         <f ca="1"/>
-        <v>-4.9262360379045494E-2</v>
+        <v>-2.2042040483143233E-2</v>
       </c>
       <c r="D12">
         <f ca="1"/>
@@ -5328,19 +5368,19 @@
       </c>
       <c r="E12" s="12">
         <f ca="1"/>
-        <v>99.003748584958885</v>
+        <v>99.544201120705765</v>
       </c>
       <c r="F12" s="11">
         <f ca="1"/>
-        <v>0</v>
+        <v>-99.544201120705765</v>
       </c>
       <c r="G12" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="11">
         <f ca="1"/>
-        <v>-96.012238832325508</v>
+        <v>-94.912007506674527</v>
       </c>
       <c r="I12" s="8">
         <f ca="1"/>
@@ -5348,7 +5388,7 @@
       </c>
       <c r="J12" s="8">
         <f ca="1"/>
-        <v>2.9915097526333767</v>
+        <v>4.6321936140312374</v>
       </c>
       <c r="K12">
         <f ca="1"/>
@@ -5356,7 +5396,7 @@
       </c>
       <c r="L12">
         <f ca="1"/>
-        <v>0.99625141504111525</v>
+        <v>0.45579887929423535</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -5365,7 +5405,7 @@
       </c>
       <c r="C13">
         <f ca="1"/>
-        <v>-0.12832838464763496</v>
+        <v>-9.2413879581635994E-2</v>
       </c>
       <c r="D13">
         <f ca="1"/>
@@ -5373,7 +5413,7 @@
       </c>
       <c r="E13" s="12">
         <f ca="1"/>
-        <v>97.442699622045964</v>
+        <v>98.14514064992899</v>
       </c>
       <c r="F13" s="11">
         <f ca="1"/>
@@ -5385,7 +5425,7 @@
       </c>
       <c r="H13" s="11">
         <f ca="1"/>
-        <v>-96.012238832325508</v>
+        <v>-94.912007506674527</v>
       </c>
       <c r="I13" s="8">
         <f ca="1"/>
@@ -5393,7 +5433,7 @@
       </c>
       <c r="J13" s="8">
         <f ca="1"/>
-        <v>1.4304607897204562</v>
+        <v>3.233133143254463</v>
       </c>
       <c r="K13">
         <f ca="1"/>
@@ -5401,7 +5441,7 @@
       </c>
       <c r="L13">
         <f ca="1"/>
-        <v>2.5573003779540358</v>
+        <v>1.8548593500710098</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -5410,7 +5450,7 @@
       </c>
       <c r="C14">
         <f ca="1"/>
-        <v>-8.0617468857331481E-2</v>
+        <v>-6.2110939198036924E-3</v>
       </c>
       <c r="D14">
         <f ca="1"/>
@@ -5418,7 +5458,7 @@
       </c>
       <c r="E14" s="12">
         <f ca="1"/>
-        <v>98.369096248659488</v>
+        <v>99.843900084461225</v>
       </c>
       <c r="F14" s="11">
         <f ca="1"/>
@@ -5430,7 +5470,7 @@
       </c>
       <c r="H14" s="11">
         <f ca="1"/>
-        <v>-96.012238832325508</v>
+        <v>-94.912007506674527</v>
       </c>
       <c r="I14" s="8">
         <f ca="1"/>
@@ -5438,7 +5478,7 @@
       </c>
       <c r="J14" s="8">
         <f ca="1"/>
-        <v>2.3568574163339804</v>
+        <v>4.931892577786698</v>
       </c>
       <c r="K14">
         <f ca="1"/>
@@ -5446,11 +5486,11 @@
       </c>
       <c r="L14">
         <f ca="1"/>
-        <v>1.6309037513405116</v>
+        <v>0.15609991553877478</v>
       </c>
       <c r="M14" s="22">
         <f ca="1">f*EXP(sigma*C14-sigma^2*B14/2)</f>
-        <v>98.369096248659488</v>
+        <v>99.843900084461225</v>
       </c>
       <c r="N14" s="23">
         <f ca="1">E14-M14</f>
@@ -5463,7 +5503,7 @@
       </c>
       <c r="C15">
         <f ca="1"/>
-        <v>-3.3911359535823374E-2</v>
+        <v>4.0955929637588012E-2</v>
       </c>
       <c r="D15">
         <f ca="1"/>
@@ -5471,27 +5511,27 @@
       </c>
       <c r="E15" s="12">
         <f ca="1"/>
-        <v>99.284345896880779</v>
+        <v>100.7821616194548</v>
       </c>
       <c r="F15" s="11">
         <f ca="1"/>
-        <v>0</v>
+        <v>100.7821616194548</v>
       </c>
       <c r="G15" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H15" s="11">
         <f ca="1"/>
-        <v>-96.012238832325508</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I15" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="8">
         <f ca="1"/>
-        <v>3.2721070645552714</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K15">
         <f ca="1"/>
@@ -5499,7 +5539,7 @@
       </c>
       <c r="L15">
         <f ca="1"/>
-        <v>0.71565410311922051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -5508,7 +5548,7 @@
       </c>
       <c r="C16">
         <f ca="1"/>
-        <v>-2.5490900654778791E-2</v>
+        <v>0.13234814668334655</v>
       </c>
       <c r="D16">
         <f ca="1"/>
@@ -5516,7 +5556,7 @@
       </c>
       <c r="E16" s="12">
         <f ca="1"/>
-        <v>99.4437349027599</v>
+        <v>102.63303046921945</v>
       </c>
       <c r="F16" s="11">
         <f ca="1"/>
@@ -5528,15 +5568,15 @@
       </c>
       <c r="H16" s="11">
         <f ca="1"/>
-        <v>-96.012238832325508</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I16" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="8">
         <f ca="1"/>
-        <v>3.4314960704343918</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K16">
         <f ca="1"/>
@@ -5544,15 +5584,15 @@
       </c>
       <c r="L16">
         <f ca="1"/>
-        <v>0.5562650972401002</v>
+        <v>0</v>
       </c>
       <c r="M16" s="22" cm="1">
         <f t="array" aca="1" ref="M16" ca="1">_xll.OPTION.BLACK.PUT_DELTA(E16,sigma*SQRT(t - B16),k)</f>
-        <v>-0.50443993372722107</v>
+        <v>-0.37414784688361569</v>
       </c>
       <c r="N16" s="23">
         <f ca="1">I16-M16</f>
-        <v>1.504439933727221</v>
+        <v>0.37414784688361569</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.55000000000000004">
@@ -5561,7 +5601,7 @@
       </c>
       <c r="C17">
         <f ca="1"/>
-        <v>3.031388143083983E-2</v>
+        <v>0.21034067430672881</v>
       </c>
       <c r="D17">
         <f ca="1"/>
@@ -5569,19 +5609,19 @@
       </c>
       <c r="E17" s="12">
         <f ca="1"/>
-        <v>100.55179443690217</v>
+        <v>104.23816414471059</v>
       </c>
       <c r="F17" s="11">
         <f ca="1"/>
-        <v>100.55179443690217</v>
+        <v>0</v>
       </c>
       <c r="G17" s="8">
         <f ca="1"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I17" s="8">
         <f ca="1"/>
@@ -5589,7 +5629,7 @@
       </c>
       <c r="J17" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K17">
         <f ca="1"/>
@@ -5606,7 +5646,7 @@
       </c>
       <c r="C18">
         <f ca="1"/>
-        <v>4.3245171878774545E-2</v>
+        <v>0.20507564818206209</v>
       </c>
       <c r="D18">
         <f ca="1"/>
@@ -5614,7 +5654,7 @@
       </c>
       <c r="E18" s="12">
         <f ca="1"/>
-        <v>100.80411924860448</v>
+        <v>104.12012864014572</v>
       </c>
       <c r="F18" s="11">
         <f ca="1"/>
@@ -5626,7 +5666,7 @@
       </c>
       <c r="H18" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I18" s="8">
         <f ca="1"/>
@@ -5634,7 +5674,7 @@
       </c>
       <c r="J18" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K18">
         <f ca="1"/>
@@ -5651,7 +5691,7 @@
       </c>
       <c r="C19">
         <f ca="1"/>
-        <v>0.1356757314912205</v>
+        <v>9.9586424852735791E-2</v>
       </c>
       <c r="D19">
         <f ca="1"/>
@@ -5659,7 +5699,7 @@
       </c>
       <c r="E19" s="12">
         <f ca="1"/>
-        <v>102.67671185742864</v>
+        <v>101.93827376742097</v>
       </c>
       <c r="F19" s="11">
         <f ca="1"/>
@@ -5671,7 +5711,7 @@
       </c>
       <c r="H19" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I19" s="8">
         <f ca="1"/>
@@ -5679,7 +5719,7 @@
       </c>
       <c r="J19" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K19">
         <f ca="1"/>
@@ -5696,7 +5736,7 @@
       </c>
       <c r="C20">
         <f ca="1"/>
-        <v>0.14965677803554564</v>
+        <v>8.0207966797765207E-2</v>
       </c>
       <c r="D20">
         <f ca="1"/>
@@ -5704,7 +5744,7 @@
       </c>
       <c r="E20" s="12">
         <f ca="1"/>
-        <v>102.95598240490982</v>
+        <v>101.5358338818442</v>
       </c>
       <c r="F20" s="11">
         <f ca="1"/>
@@ -5716,7 +5756,7 @@
       </c>
       <c r="H20" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I20" s="8">
         <f ca="1"/>
@@ -5724,7 +5764,7 @@
       </c>
       <c r="J20" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K20">
         <f ca="1"/>
@@ -5736,14 +5776,14 @@
       </c>
       <c r="M20" s="7">
         <f t="array" aca="1" ref="M20:M21" ca="1">_xll.MONTE.STDEV(C20)</f>
-        <v>2.9585807742571026E-3</v>
+        <v>1.9389343090459451E-3</v>
       </c>
       <c r="N20" s="7">
         <v>0</v>
       </c>
       <c r="O20" s="7">
         <f t="array" aca="1" ref="O20:O21" ca="1">_xll.MONTE.STDEV(E20)</f>
-        <v>100.05839124834462</v>
+        <v>100.03731273708843</v>
       </c>
       <c r="P20" s="7">
         <f>f*EXP(mu*B20)</f>
@@ -5756,7 +5796,7 @@
       </c>
       <c r="C21">
         <f ca="1"/>
-        <v>0.31472117443703507</v>
+        <v>7.2477689338990292E-2</v>
       </c>
       <c r="D21">
         <f ca="1"/>
@@ -5764,7 +5804,7 @@
       </c>
       <c r="E21" s="12">
         <f ca="1"/>
-        <v>106.4030690424518</v>
+        <v>101.37086514206224</v>
       </c>
       <c r="F21" s="11">
         <f ca="1"/>
@@ -5776,7 +5816,7 @@
       </c>
       <c r="H21" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I21" s="8">
         <f ca="1"/>
@@ -5784,7 +5824,7 @@
       </c>
       <c r="J21" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K21">
         <f ca="1"/>
@@ -5796,7 +5836,7 @@
       </c>
       <c r="M21" s="7">
         <f ca="1"/>
-        <v>0.19902845775862468</v>
+        <v>0.19821599857598771</v>
       </c>
       <c r="N21" s="7">
         <f>SQRT(B20)</f>
@@ -5804,7 +5844,7 @@
       </c>
       <c r="O21" s="7">
         <f ca="1"/>
-        <v>3.983453566034624</v>
+        <v>3.9638153276009618</v>
       </c>
       <c r="P21" s="7"/>
     </row>
@@ -5814,7 +5854,7 @@
       </c>
       <c r="C22">
         <f ca="1"/>
-        <v>0.31939169557978364</v>
+        <v>6.2097692930649567E-2</v>
       </c>
       <c r="D22">
         <f ca="1"/>
@@ -5822,7 +5862,7 @@
       </c>
       <c r="E22" s="12">
         <f ca="1"/>
-        <v>106.4939871749053</v>
+        <v>101.1525450631692</v>
       </c>
       <c r="F22" s="11">
         <f ca="1"/>
@@ -5834,7 +5874,7 @@
       </c>
       <c r="H22" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I22" s="8">
         <f ca="1"/>
@@ -5842,7 +5882,7 @@
       </c>
       <c r="J22" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K22">
         <f ca="1"/>
@@ -5859,7 +5899,7 @@
       </c>
       <c r="C23">
         <f ca="1"/>
-        <v>0.24833381140025479</v>
+        <v>0.21662142806465678</v>
       </c>
       <c r="D23">
         <f ca="1"/>
@@ -5867,7 +5907,7 @@
       </c>
       <c r="E23" s="12">
         <f ca="1"/>
-        <v>104.98284420329796</v>
+        <v>104.31910007933558</v>
       </c>
       <c r="F23" s="11">
         <f ca="1"/>
@@ -5879,7 +5919,7 @@
       </c>
       <c r="H23" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I23" s="8">
         <f ca="1"/>
@@ -5887,7 +5927,7 @@
       </c>
       <c r="J23" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K23">
         <f ca="1"/>
@@ -5904,7 +5944,7 @@
       </c>
       <c r="C24">
         <f ca="1"/>
-        <v>0.1633192532085081</v>
+        <v>0.25330017796982374</v>
       </c>
       <c r="D24">
         <f ca="1"/>
@@ -5912,7 +5952,7 @@
       </c>
       <c r="E24" s="12">
         <f ca="1"/>
-        <v>103.20466305104242</v>
+        <v>105.07876602808189</v>
       </c>
       <c r="F24" s="11">
         <f ca="1"/>
@@ -5924,7 +5964,7 @@
       </c>
       <c r="H24" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I24" s="8">
         <f ca="1"/>
@@ -5932,7 +5972,7 @@
       </c>
       <c r="J24" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K24">
         <f ca="1"/>
@@ -5949,7 +5989,7 @@
       </c>
       <c r="C25">
         <f ca="1"/>
-        <v>0.17079689730935149</v>
+        <v>0.16143654216505043</v>
       </c>
       <c r="D25">
         <f ca="1"/>
@@ -5957,7 +5997,7 @@
       </c>
       <c r="E25" s="12">
         <f ca="1"/>
-        <v>103.35085567148994</v>
+        <v>103.15755652010385</v>
       </c>
       <c r="F25" s="11">
         <f ca="1"/>
@@ -5969,7 +6009,7 @@
       </c>
       <c r="H25" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I25" s="8">
         <f ca="1"/>
@@ -5977,7 +6017,7 @@
       </c>
       <c r="J25" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K25">
         <f ca="1"/>
@@ -5994,7 +6034,7 @@
       </c>
       <c r="C26">
         <f ca="1"/>
-        <v>0.19966931204600219</v>
+        <v>0.10985648666976952</v>
       </c>
       <c r="D26">
         <f ca="1"/>
@@ -6002,7 +6042,7 @@
       </c>
       <c r="E26" s="12">
         <f ca="1"/>
-        <v>103.94106422808677</v>
+        <v>102.09068463224268</v>
       </c>
       <c r="F26" s="11">
         <f ca="1"/>
@@ -6014,7 +6054,7 @@
       </c>
       <c r="H26" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I26" s="8">
         <f ca="1"/>
@@ -6022,7 +6062,7 @@
       </c>
       <c r="J26" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K26">
         <f ca="1"/>
@@ -6039,7 +6079,7 @@
       </c>
       <c r="C27">
         <f ca="1"/>
-        <v>0.17633628352928335</v>
+        <v>0.1687043632760177</v>
       </c>
       <c r="D27">
         <f ca="1"/>
@@ -6047,7 +6087,7 @@
       </c>
       <c r="E27" s="12">
         <f ca="1"/>
-        <v>103.44886603928782</v>
+        <v>103.2910837888966</v>
       </c>
       <c r="F27" s="11">
         <f ca="1"/>
@@ -6059,7 +6099,7 @@
       </c>
       <c r="H27" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I27" s="8">
         <f ca="1"/>
@@ -6067,7 +6107,7 @@
       </c>
       <c r="J27" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K27">
         <f ca="1"/>
@@ -6084,7 +6124,7 @@
       </c>
       <c r="C28">
         <f ca="1"/>
-        <v>0.20482052907356457</v>
+        <v>0.15983844543554215</v>
       </c>
       <c r="D28">
         <f ca="1"/>
@@ -6092,7 +6132,7 @@
       </c>
       <c r="E28" s="12">
         <f ca="1"/>
-        <v>104.03155762372253</v>
+        <v>103.09984370590909</v>
       </c>
       <c r="F28" s="11">
         <f ca="1"/>
@@ -6104,7 +6144,7 @@
       </c>
       <c r="H28" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I28" s="8">
         <f ca="1"/>
@@ -6112,7 +6152,7 @@
       </c>
       <c r="J28" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K28">
         <f ca="1"/>
@@ -6129,7 +6169,7 @@
       </c>
       <c r="C29">
         <f ca="1"/>
-        <v>0.15213940321442412</v>
+        <v>0.23248236010962478</v>
       </c>
       <c r="D29">
         <f ca="1"/>
@@ -6137,7 +6177,7 @@
       </c>
       <c r="E29" s="12">
         <f ca="1"/>
-        <v>102.93297689109913</v>
+        <v>104.60032492776834</v>
       </c>
       <c r="F29" s="11">
         <f ca="1"/>
@@ -6149,7 +6189,7 @@
       </c>
       <c r="H29" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I29" s="8">
         <f ca="1"/>
@@ -6157,7 +6197,7 @@
       </c>
       <c r="J29" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K29">
         <f ca="1"/>
@@ -6174,7 +6214,7 @@
       </c>
       <c r="C30">
         <f ca="1"/>
-        <v>0.14955341561953156</v>
+        <v>0.12802356138371518</v>
       </c>
       <c r="D30">
         <f ca="1"/>
@@ -6182,7 +6222,7 @@
       </c>
       <c r="E30" s="12">
         <f ca="1"/>
-        <v>102.87152392428476</v>
+        <v>102.42951446414372</v>
       </c>
       <c r="F30" s="11">
         <f ca="1"/>
@@ -6194,7 +6234,7 @@
       </c>
       <c r="H30" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I30" s="8">
         <f ca="1"/>
@@ -6202,7 +6242,7 @@
       </c>
       <c r="J30" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K30">
         <f ca="1"/>
@@ -6219,7 +6259,7 @@
       </c>
       <c r="C31">
         <f ca="1"/>
-        <v>0.14792380643240402</v>
+        <v>0.15015733378178253</v>
       </c>
       <c r="D31">
         <f ca="1"/>
@@ -6227,7 +6267,7 @@
       </c>
       <c r="E31" s="12">
         <f ca="1"/>
-        <v>102.82977460032905</v>
+        <v>102.87571948426057</v>
       </c>
       <c r="F31" s="11">
         <f ca="1"/>
@@ -6239,7 +6279,7 @@
       </c>
       <c r="H31" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I31" s="8">
         <f ca="1"/>
@@ -6247,7 +6287,7 @@
       </c>
       <c r="J31" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K31">
         <f ca="1"/>
@@ -6264,7 +6304,7 @@
       </c>
       <c r="C32">
         <f ca="1"/>
-        <v>0.23587896561726085</v>
+        <v>0.12445086837877289</v>
       </c>
       <c r="D32">
         <f ca="1"/>
@@ -6272,7 +6312,7 @@
       </c>
       <c r="E32" s="12">
         <f ca="1"/>
-        <v>104.6462881533039</v>
+        <v>102.33997505840439</v>
       </c>
       <c r="F32" s="11">
         <f ca="1"/>
@@ -6284,7 +6324,7 @@
       </c>
       <c r="H32" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I32" s="8">
         <f ca="1"/>
@@ -6292,7 +6332,7 @@
       </c>
       <c r="J32" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K32">
         <f ca="1"/>
@@ -6309,7 +6349,7 @@
       </c>
       <c r="C33">
         <f ca="1"/>
-        <v>0.21864670000475542</v>
+        <v>0.14767561184554251</v>
       </c>
       <c r="D33">
         <f ca="1"/>
@@ -6317,7 +6357,7 @@
       </c>
       <c r="E33" s="12">
         <f ca="1"/>
-        <v>104.27790784339538</v>
+        <v>102.80821973715624</v>
       </c>
       <c r="F33" s="11">
         <f ca="1"/>
@@ -6329,7 +6369,7 @@
       </c>
       <c r="H33" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I33" s="8">
         <f ca="1"/>
@@ -6337,7 +6377,7 @@
       </c>
       <c r="J33" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K33">
         <f ca="1"/>
@@ -6354,7 +6394,7 @@
       </c>
       <c r="C34">
         <f ca="1"/>
-        <v>0.21723566555142379</v>
+        <v>0.20287491904196173</v>
       </c>
       <c r="D34">
         <f ca="1"/>
@@ -6362,7 +6402,7 @@
       </c>
       <c r="E34" s="12">
         <f ca="1"/>
-        <v>104.24014450611358</v>
+        <v>103.94118078757757</v>
       </c>
       <c r="F34" s="11">
         <f ca="1"/>
@@ -6374,7 +6414,7 @@
       </c>
       <c r="H34" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I34" s="8">
         <f ca="1"/>
@@ -6382,7 +6422,7 @@
       </c>
       <c r="J34" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K34">
         <f ca="1"/>
@@ -6399,7 +6439,7 @@
       </c>
       <c r="C35">
         <f ca="1"/>
-        <v>0.2549313932470042</v>
+        <v>0.13176620748212106</v>
       </c>
       <c r="D35">
         <f ca="1"/>
@@ -6407,7 +6447,7 @@
       </c>
       <c r="E35" s="12">
         <f ca="1"/>
-        <v>105.02059403972541</v>
+        <v>102.46522036480563</v>
       </c>
       <c r="F35" s="11">
         <f ca="1"/>
@@ -6419,7 +6459,7 @@
       </c>
       <c r="H35" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I35" s="8">
         <f ca="1"/>
@@ -6427,7 +6467,7 @@
       </c>
       <c r="J35" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K35">
         <f ca="1"/>
@@ -6444,7 +6484,7 @@
       </c>
       <c r="C36">
         <f ca="1"/>
-        <v>0.1230264568340973</v>
+        <v>7.1822630686902311E-2</v>
       </c>
       <c r="D36">
         <f ca="1"/>
@@ -6452,7 +6492,7 @@
       </c>
       <c r="E36" s="12">
         <f ca="1"/>
-        <v>102.27809013642886</v>
+        <v>101.23602908552824</v>
       </c>
       <c r="F36" s="11">
         <f ca="1"/>
@@ -6464,7 +6504,7 @@
       </c>
       <c r="H36" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I36" s="8">
         <f ca="1"/>
@@ -6472,7 +6512,7 @@
       </c>
       <c r="J36" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K36">
         <f ca="1"/>
@@ -6489,7 +6529,7 @@
       </c>
       <c r="C37">
         <f ca="1"/>
-        <v>0.12098446580345813</v>
+        <v>9.1363430433877957E-2</v>
       </c>
       <c r="D37">
         <f ca="1"/>
@@ -6497,7 +6537,7 @@
       </c>
       <c r="E37" s="12">
         <f ca="1"/>
-        <v>102.2281498970344</v>
+        <v>101.62431954230354</v>
       </c>
       <c r="F37" s="11">
         <f ca="1"/>
@@ -6509,7 +6549,7 @@
       </c>
       <c r="H37" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I37" s="8">
         <f ca="1"/>
@@ -6517,7 +6557,7 @@
       </c>
       <c r="J37" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K37">
         <f ca="1"/>
@@ -6534,7 +6574,7 @@
       </c>
       <c r="C38">
         <f ca="1"/>
-        <v>0.11790312710001981</v>
+        <v>2.4491713613285448E-2</v>
       </c>
       <c r="D38">
         <f ca="1"/>
@@ -6542,7 +6582,7 @@
       </c>
       <c r="E38" s="12">
         <f ca="1"/>
-        <v>102.15699650785022</v>
+        <v>100.26618792487444</v>
       </c>
       <c r="F38" s="11">
         <f ca="1"/>
@@ -6554,7 +6594,7 @@
       </c>
       <c r="H38" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="I38" s="8">
         <f ca="1"/>
@@ -6562,7 +6602,7 @@
       </c>
       <c r="J38" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K38">
         <f ca="1"/>
@@ -6579,7 +6619,7 @@
       </c>
       <c r="C39">
         <f ca="1"/>
-        <v>0.13916324799665292</v>
+        <v>-3.054440338621827E-2</v>
       </c>
       <c r="D39">
         <f ca="1"/>
@@ -6587,27 +6627,27 @@
       </c>
       <c r="E39" s="12">
         <f ca="1"/>
-        <v>102.5840882664514</v>
+        <v>99.16065427410345</v>
       </c>
       <c r="F39" s="11">
         <f ca="1"/>
-        <v>0</v>
+        <v>-99.16065427410345</v>
       </c>
       <c r="G39" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-93.29050016132318</v>
       </c>
       <c r="I39" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.8701541127802699</v>
       </c>
       <c r="K39">
         <f ca="1"/>
@@ -6615,7 +6655,7 @@
       </c>
       <c r="L39">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.83934572589654977</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -6624,7 +6664,7 @@
       </c>
       <c r="C40">
         <f ca="1"/>
-        <v>0.21697575992611967</v>
+        <v>-3.6673598899559963E-2</v>
       </c>
       <c r="D40">
         <f ca="1"/>
@@ -6632,7 +6672,7 @@
       </c>
       <c r="E40" s="12">
         <f ca="1"/>
-        <v>104.18470546433207</v>
+        <v>99.031250922672697</v>
       </c>
       <c r="F40" s="11">
         <f ca="1"/>
@@ -6644,15 +6684,15 @@
       </c>
       <c r="H40" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-93.29050016132318</v>
       </c>
       <c r="I40" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.740750761349517</v>
       </c>
       <c r="K40">
         <f ca="1"/>
@@ -6660,7 +6700,7 @@
       </c>
       <c r="L40">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.96874907732730264</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -6669,7 +6709,7 @@
       </c>
       <c r="C41">
         <f ca="1"/>
-        <v>0.30421457154033521</v>
+        <v>-9.1477426333507236E-2</v>
       </c>
       <c r="D41">
         <f ca="1"/>
@@ -6677,7 +6717,7 @@
       </c>
       <c r="E41" s="12">
         <f ca="1"/>
-        <v>106.00996512389797</v>
+        <v>97.943883833565721</v>
       </c>
       <c r="F41" s="11">
         <f ca="1"/>
@@ -6689,15 +6729,15 @@
       </c>
       <c r="H41" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-93.29050016132318</v>
       </c>
       <c r="I41" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>4.6533836722425406</v>
       </c>
       <c r="K41">
         <f ca="1"/>
@@ -6705,7 +6745,7 @@
       </c>
       <c r="L41">
         <f ca="1"/>
-        <v>0</v>
+        <v>2.0561161664342791</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -6714,7 +6754,7 @@
       </c>
       <c r="C42">
         <f ca="1"/>
-        <v>0.39421747521135259</v>
+        <v>-0.19021953568326422</v>
       </c>
       <c r="D42">
         <f ca="1"/>
@@ -6722,7 +6762,7 @@
       </c>
       <c r="E42" s="12">
         <f ca="1"/>
-        <v>107.92684980597589</v>
+        <v>96.020938671972928</v>
       </c>
       <c r="F42" s="11">
         <f ca="1"/>
@@ -6734,15 +6774,15 @@
       </c>
       <c r="H42" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-93.29050016132318</v>
       </c>
       <c r="I42" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>2.7304385106497477</v>
       </c>
       <c r="K42">
         <f ca="1"/>
@@ -6750,7 +6790,7 @@
       </c>
       <c r="L42">
         <f ca="1"/>
-        <v>0</v>
+        <v>3.9790613280270719</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -6759,7 +6799,7 @@
       </c>
       <c r="C43">
         <f ca="1"/>
-        <v>0.30765812661465836</v>
+        <v>-0.15759944121038483</v>
       </c>
       <c r="D43">
         <f ca="1"/>
@@ -6767,7 +6807,7 @@
       </c>
       <c r="E43" s="12">
         <f ca="1"/>
-        <v>106.06602857952167</v>
+        <v>96.641697357296792</v>
       </c>
       <c r="F43" s="11">
         <f ca="1"/>
@@ -6779,15 +6819,15 @@
       </c>
       <c r="H43" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-93.29050016132318</v>
       </c>
       <c r="I43" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>3.3511971959736115</v>
       </c>
       <c r="K43">
         <f ca="1"/>
@@ -6795,7 +6835,7 @@
       </c>
       <c r="L43">
         <f ca="1"/>
-        <v>0</v>
+        <v>3.3583026427032081</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -6804,7 +6844,7 @@
       </c>
       <c r="C44">
         <f ca="1"/>
-        <v>0.32410100611106268</v>
+        <v>-0.1302733743440192</v>
       </c>
       <c r="D44">
         <f ca="1"/>
@@ -6812,7 +6852,7 @@
       </c>
       <c r="E44" s="12">
         <f ca="1"/>
-        <v>106.40689603967846</v>
+        <v>97.163537367085326</v>
       </c>
       <c r="F44" s="11">
         <f ca="1"/>
@@ -6824,15 +6864,15 @@
       </c>
       <c r="H44" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-93.29050016132318</v>
       </c>
       <c r="I44" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>3.8730372057621452</v>
       </c>
       <c r="K44">
         <f ca="1"/>
@@ -6840,7 +6880,7 @@
       </c>
       <c r="L44">
         <f ca="1"/>
-        <v>0</v>
+        <v>2.8364626329146745</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -6849,7 +6889,7 @@
       </c>
       <c r="C45">
         <f ca="1"/>
-        <v>0.34537631475524883</v>
+        <v>-0.21585296423640066</v>
       </c>
       <c r="D45">
         <f ca="1"/>
@@ -6857,7 +6897,7 @@
       </c>
       <c r="E45" s="12">
         <f ca="1"/>
-        <v>106.8520800877869</v>
+        <v>95.507004766850557</v>
       </c>
       <c r="F45" s="11">
         <f ca="1"/>
@@ -6869,15 +6909,15 @@
       </c>
       <c r="H45" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-93.29050016132318</v>
       </c>
       <c r="I45" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>2.2165046055273763</v>
       </c>
       <c r="K45">
         <f ca="1"/>
@@ -6885,7 +6925,7 @@
       </c>
       <c r="L45">
         <f ca="1"/>
-        <v>0</v>
+        <v>4.4929952331494434</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -6894,7 +6934,7 @@
       </c>
       <c r="C46">
         <f ca="1"/>
-        <v>0.38375420257235293</v>
+        <v>-0.12086859433805185</v>
       </c>
       <c r="D46">
         <f ca="1"/>
@@ -6902,7 +6942,7 @@
       </c>
       <c r="E46" s="12">
         <f ca="1"/>
-        <v>107.66677346645592</v>
+        <v>97.330895506506351</v>
       </c>
       <c r="F46" s="11">
         <f ca="1"/>
@@ -6914,15 +6954,15 @@
       </c>
       <c r="H46" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-93.29050016132318</v>
       </c>
       <c r="I46" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>4.0403953451831711</v>
       </c>
       <c r="K46">
         <f ca="1"/>
@@ -6930,7 +6970,7 @@
       </c>
       <c r="L46">
         <f ca="1"/>
-        <v>0</v>
+        <v>2.6691044934936485</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -6939,7 +6979,7 @@
       </c>
       <c r="C47">
         <f ca="1"/>
-        <v>0.44860021734087913</v>
+        <v>-7.2553302713611101E-2</v>
       </c>
       <c r="D47">
         <f ca="1"/>
@@ -6947,7 +6987,7 @@
       </c>
       <c r="E47" s="12">
         <f ca="1"/>
-        <v>109.06349433383669</v>
+        <v>98.268106657129977</v>
       </c>
       <c r="F47" s="11">
         <f ca="1"/>
@@ -6959,15 +6999,15 @@
       </c>
       <c r="H47" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-93.29050016132318</v>
       </c>
       <c r="I47" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>4.9776064958067963</v>
       </c>
       <c r="K47">
         <f ca="1"/>
@@ -6975,7 +7015,7 @@
       </c>
       <c r="L47">
         <f ca="1"/>
-        <v>0</v>
+        <v>1.7318933428700234</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -6984,7 +7024,7 @@
       </c>
       <c r="C48">
         <f ca="1"/>
-        <v>0.33928639992452264</v>
+        <v>-9.6422965597099369E-2</v>
       </c>
       <c r="D48">
         <f ca="1"/>
@@ -6992,7 +7032,7 @@
       </c>
       <c r="E48" s="12">
         <f ca="1"/>
-        <v>106.69640508844707</v>
+        <v>97.792275653023196</v>
       </c>
       <c r="F48" s="11">
         <f ca="1"/>
@@ -7004,15 +7044,15 @@
       </c>
       <c r="H48" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-93.29050016132318</v>
       </c>
       <c r="I48" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>4.5017754917000161</v>
       </c>
       <c r="K48">
         <f ca="1"/>
@@ -7020,7 +7060,7 @@
       </c>
       <c r="L48">
         <f ca="1"/>
-        <v>0</v>
+        <v>2.2077243469768035</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7029,7 +7069,7 @@
       </c>
       <c r="C49">
         <f ca="1"/>
-        <v>0.37500345704311722</v>
+        <v>-6.9347287145729533E-2</v>
       </c>
       <c r="D49">
         <f ca="1"/>
@@ -7037,7 +7077,7 @@
       </c>
       <c r="E49" s="12">
         <f ca="1"/>
-        <v>107.4527136096806</v>
+        <v>98.3154049551501</v>
       </c>
       <c r="F49" s="11">
         <f ca="1"/>
@@ -7049,15 +7089,15 @@
       </c>
       <c r="H49" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-93.29050016132318</v>
       </c>
       <c r="I49" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>5.02490479382692</v>
       </c>
       <c r="K49">
         <f ca="1"/>
@@ -7065,7 +7105,7 @@
       </c>
       <c r="L49">
         <f ca="1"/>
-        <v>0</v>
+        <v>1.6845950448498996</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7074,7 +7114,7 @@
       </c>
       <c r="C50">
         <f ca="1"/>
-        <v>0.41818096487772299</v>
+        <v>4.121498891038583E-2</v>
       </c>
       <c r="D50">
         <f ca="1"/>
@@ -7082,19 +7122,19 @@
       </c>
       <c r="E50" s="12">
         <f ca="1"/>
-        <v>108.37596929547966</v>
+        <v>100.50557350978093</v>
       </c>
       <c r="F50" s="11">
         <f ca="1"/>
-        <v>0</v>
+        <v>100.50557350978093</v>
       </c>
       <c r="G50" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H50" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.2150733484577501</v>
       </c>
       <c r="I50" s="8">
         <f ca="1"/>
@@ -7102,7 +7142,7 @@
       </c>
       <c r="J50" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.2150733484577501</v>
       </c>
       <c r="K50">
         <f ca="1"/>
@@ -7119,7 +7159,7 @@
       </c>
       <c r="C51">
         <f ca="1"/>
-        <v>0.38724464115920715</v>
+        <v>0.12796983697902717</v>
       </c>
       <c r="D51">
         <f ca="1"/>
@@ -7127,7 +7167,7 @@
       </c>
       <c r="E51" s="12">
         <f ca="1"/>
-        <v>107.69887239310543</v>
+        <v>102.25647860787093</v>
       </c>
       <c r="F51" s="11">
         <f ca="1"/>
@@ -7139,7 +7179,7 @@
       </c>
       <c r="H51" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.2150733484577501</v>
       </c>
       <c r="I51" s="8">
         <f ca="1"/>
@@ -7147,7 +7187,7 @@
       </c>
       <c r="J51" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.2150733484577501</v>
       </c>
       <c r="K51">
         <f ca="1"/>
@@ -7164,7 +7204,7 @@
       </c>
       <c r="C52">
         <f ca="1"/>
-        <v>0.36730221402028818</v>
+        <v>6.5663609574996645E-2</v>
       </c>
       <c r="D52">
         <f ca="1"/>
@@ -7172,7 +7212,7 @@
       </c>
       <c r="E52" s="12">
         <f ca="1"/>
-        <v>107.26159123936347</v>
+        <v>100.98206309016986</v>
       </c>
       <c r="F52" s="11">
         <f ca="1"/>
@@ -7184,7 +7224,7 @@
       </c>
       <c r="H52" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.2150733484577501</v>
       </c>
       <c r="I52" s="8">
         <f ca="1"/>
@@ -7192,7 +7232,7 @@
       </c>
       <c r="J52" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.2150733484577501</v>
       </c>
       <c r="K52">
         <f ca="1"/>
@@ -7209,7 +7249,7 @@
       </c>
       <c r="C53">
         <f ca="1"/>
-        <v>0.34140320688626569</v>
+        <v>0.1171464984688062</v>
       </c>
       <c r="D53">
         <f ca="1"/>
@@ -7217,7 +7257,7 @@
       </c>
       <c r="E53" s="12">
         <f ca="1"/>
-        <v>106.69889769414378</v>
+        <v>102.01904236183969</v>
       </c>
       <c r="F53" s="11">
         <f ca="1"/>
@@ -7229,7 +7269,7 @@
       </c>
       <c r="H53" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.2150733484577501</v>
       </c>
       <c r="I53" s="8">
         <f ca="1"/>
@@ -7237,7 +7277,7 @@
       </c>
       <c r="J53" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.2150733484577501</v>
       </c>
       <c r="K53">
         <f ca="1"/>
@@ -7254,7 +7294,7 @@
       </c>
       <c r="C54">
         <f ca="1"/>
-        <v>0.28605391734911245</v>
+        <v>-4.885857944763855E-2</v>
       </c>
       <c r="D54">
         <f ca="1"/>
@@ -7262,27 +7302,27 @@
       </c>
       <c r="E54" s="12">
         <f ca="1"/>
-        <v>105.51582793235528</v>
+        <v>98.679622888923973</v>
       </c>
       <c r="F54" s="11">
         <f ca="1"/>
-        <v>0</v>
+        <v>-98.679622888923973</v>
       </c>
       <c r="G54" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-91.464549540466223</v>
       </c>
       <c r="I54" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.2150733484577501</v>
       </c>
       <c r="K54">
         <f ca="1"/>
@@ -7290,7 +7330,7 @@
       </c>
       <c r="L54">
         <f ca="1"/>
-        <v>0</v>
+        <v>1.3203771110760272</v>
       </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7299,7 +7339,7 @@
       </c>
       <c r="C55">
         <f ca="1"/>
-        <v>0.22542463770193133</v>
+        <v>8.959739189271218E-3</v>
       </c>
       <c r="D55">
         <f ca="1"/>
@@ -7307,7 +7347,7 @@
       </c>
       <c r="E55" s="12">
         <f ca="1"/>
-        <v>104.2357450842491</v>
+        <v>99.819358137950701</v>
       </c>
       <c r="F55" s="11">
         <f ca="1"/>
@@ -7319,15 +7359,15 @@
       </c>
       <c r="H55" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-91.464549540466223</v>
       </c>
       <c r="I55" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>8.3548085974844781</v>
       </c>
       <c r="K55">
         <f ca="1"/>
@@ -7335,7 +7375,7 @@
       </c>
       <c r="L55">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.18064186204929911</v>
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7344,7 +7384,7 @@
       </c>
       <c r="C56">
         <f ca="1"/>
-        <v>0.17492220313866663</v>
+        <v>-4.9825697337377378E-2</v>
       </c>
       <c r="D56">
         <f ca="1"/>
@@ -7352,7 +7392,7 @@
       </c>
       <c r="E56" s="12">
         <f ca="1"/>
-        <v>103.17995777868256</v>
+        <v>98.644753345754339</v>
       </c>
       <c r="F56" s="11">
         <f ca="1"/>
@@ -7364,15 +7404,15 @@
       </c>
       <c r="H56" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-91.464549540466223</v>
       </c>
       <c r="I56" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.1802038052881159</v>
       </c>
       <c r="K56">
         <f ca="1"/>
@@ -7380,7 +7420,7 @@
       </c>
       <c r="L56">
         <f ca="1"/>
-        <v>0</v>
+        <v>1.3552466542456614</v>
       </c>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7389,7 +7429,7 @@
       </c>
       <c r="C57">
         <f ca="1"/>
-        <v>0.14083864773621957</v>
+        <v>-1.0993803322098213E-2</v>
       </c>
       <c r="D57">
         <f ca="1"/>
@@ -7397,7 +7437,7 @@
       </c>
       <c r="E57" s="12">
         <f ca="1"/>
-        <v>102.47080364704982</v>
+        <v>99.405895753959399</v>
       </c>
       <c r="F57" s="11">
         <f ca="1"/>
@@ -7409,15 +7449,15 @@
       </c>
       <c r="H57" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-91.464549540466223</v>
       </c>
       <c r="I57" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.9413462134931763</v>
       </c>
       <c r="K57">
         <f ca="1"/>
@@ -7425,7 +7465,7 @@
       </c>
       <c r="L57">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.59410424604060097</v>
       </c>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7434,7 +7474,7 @@
       </c>
       <c r="C58">
         <f ca="1"/>
-        <v>0.14094959634013782</v>
+        <v>1.8869697026822521E-2</v>
       </c>
       <c r="D58">
         <f ca="1"/>
@@ -7442,7 +7482,7 @@
       </c>
       <c r="E58" s="12">
         <f ca="1"/>
-        <v>102.46487995250632</v>
+        <v>99.993394158731746</v>
       </c>
       <c r="F58" s="11">
         <f ca="1"/>
@@ -7454,15 +7494,15 @@
       </c>
       <c r="H58" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-91.464549540466223</v>
       </c>
       <c r="I58" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>8.5288446182655235</v>
       </c>
       <c r="K58">
         <f ca="1"/>
@@ -7470,7 +7510,7 @@
       </c>
       <c r="L58">
         <f ca="1"/>
-        <v>0</v>
+        <v>6.6058412682536982E-3</v>
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7479,7 +7519,7 @@
       </c>
       <c r="C59">
         <f ca="1"/>
-        <v>0.15822015688068936</v>
+        <v>-4.9589768933637132E-4</v>
       </c>
       <c r="D59">
         <f ca="1"/>
@@ -7487,7 +7527,7 @@
       </c>
       <c r="E59" s="12">
         <f ca="1"/>
-        <v>102.81119186366369</v>
+        <v>99.598888655423565</v>
       </c>
       <c r="F59" s="11">
         <f ca="1"/>
@@ -7499,15 +7539,15 @@
       </c>
       <c r="H59" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-91.464549540466223</v>
       </c>
       <c r="I59" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>8.1343391149573421</v>
       </c>
       <c r="K59">
         <f ca="1"/>
@@ -7515,7 +7555,7 @@
       </c>
       <c r="L59">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.40111134457643516</v>
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7524,7 +7564,7 @@
       </c>
       <c r="C60">
         <f ca="1"/>
-        <v>0.17753898129986634</v>
+        <v>-4.5326133302656529E-2</v>
       </c>
       <c r="D60">
         <f ca="1"/>
@@ -7532,7 +7572,7 @@
       </c>
       <c r="E60" s="12">
         <f ca="1"/>
-        <v>103.20094213780263</v>
+        <v>98.701975291823445</v>
       </c>
       <c r="F60" s="11">
         <f ca="1"/>
@@ -7544,15 +7584,15 @@
       </c>
       <c r="H60" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-91.464549540466223</v>
       </c>
       <c r="I60" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.2374257513572218</v>
       </c>
       <c r="K60">
         <f ca="1"/>
@@ -7560,7 +7600,7 @@
       </c>
       <c r="L60">
         <f ca="1"/>
-        <v>0</v>
+        <v>1.2980247081765555</v>
       </c>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7569,7 +7609,7 @@
       </c>
       <c r="C61">
         <f ca="1"/>
-        <v>0.20509444177838801</v>
+        <v>-2.5773780941742978E-2</v>
       </c>
       <c r="D61">
         <f ca="1"/>
@@ -7577,7 +7617,7 @@
       </c>
       <c r="E61" s="12">
         <f ca="1"/>
-        <v>103.76296076490136</v>
+        <v>99.080775321727614</v>
       </c>
       <c r="F61" s="11">
         <f ca="1"/>
@@ -7589,15 +7629,15 @@
       </c>
       <c r="H61" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-91.464549540466223</v>
       </c>
       <c r="I61" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>7.6162257812613916</v>
       </c>
       <c r="K61">
         <f ca="1"/>
@@ -7605,7 +7645,7 @@
       </c>
       <c r="L61">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.91922467827238563</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7614,7 +7654,7 @@
       </c>
       <c r="C62">
         <f ca="1"/>
-        <v>0.16046727161621677</v>
+        <v>5.6072244425358075E-3</v>
       </c>
       <c r="D62">
         <f ca="1"/>
@@ -7622,7 +7662,7 @@
       </c>
       <c r="E62" s="12">
         <f ca="1"/>
-        <v>102.83272514116173</v>
+        <v>99.696605662490228</v>
       </c>
       <c r="F62" s="11">
         <f ca="1"/>
@@ -7634,15 +7674,15 @@
       </c>
       <c r="H62" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-91.464549540466223</v>
       </c>
       <c r="I62" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>8.2320561220240052</v>
       </c>
       <c r="K62">
         <f ca="1"/>
@@ -7650,7 +7690,7 @@
       </c>
       <c r="L62">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.30339433750977207</v>
       </c>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7659,7 +7699,7 @@
       </c>
       <c r="C63">
         <f ca="1"/>
-        <v>0.15576425952150941</v>
+        <v>2.5990607615361812E-3</v>
       </c>
       <c r="D63">
         <f ca="1"/>
@@ -7667,7 +7707,7 @@
       </c>
       <c r="E63" s="12">
         <f ca="1"/>
-        <v>102.72782735171053</v>
+        <v>99.628672347798542</v>
       </c>
       <c r="F63" s="11">
         <f ca="1"/>
@@ -7679,15 +7719,15 @@
       </c>
       <c r="H63" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>-91.464549540466223</v>
       </c>
       <c r="I63" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>8.1641228073323191</v>
       </c>
       <c r="K63">
         <f ca="1"/>
@@ -7695,7 +7735,7 @@
       </c>
       <c r="L63">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.37132765220145814</v>
       </c>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7704,7 +7744,7 @@
       </c>
       <c r="C64">
         <f ca="1"/>
-        <v>0.21271792266006012</v>
+        <v>2.7365353690281612E-2</v>
       </c>
       <c r="D64">
         <f ca="1"/>
@@ -7712,19 +7752,19 @@
       </c>
       <c r="E64" s="12">
         <f ca="1"/>
-        <v>103.89635030801317</v>
+        <v>100.11537357797087</v>
       </c>
       <c r="F64" s="11">
         <f ca="1"/>
-        <v>0</v>
+        <v>100.11537357797087</v>
       </c>
       <c r="G64" s="8">
         <f ca="1"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H64" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="I64" s="8">
         <f ca="1"/>
@@ -7732,7 +7772,7 @@
       </c>
       <c r="J64" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="K64">
         <f ca="1"/>
@@ -7749,7 +7789,7 @@
       </c>
       <c r="C65">
         <f ca="1"/>
-        <v>0.21948759519689068</v>
+        <v>7.9289109596839144E-2</v>
       </c>
       <c r="D65">
         <f ca="1"/>
@@ -7757,7 +7797,7 @@
       </c>
       <c r="E65" s="12">
         <f ca="1"/>
-        <v>104.02879179683966</v>
+        <v>101.15237141810624</v>
       </c>
       <c r="F65" s="11">
         <f ca="1"/>
@@ -7769,7 +7809,7 @@
       </c>
       <c r="H65" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="I65" s="8">
         <f ca="1"/>
@@ -7777,7 +7817,7 @@
       </c>
       <c r="J65" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="K65">
         <f ca="1"/>
@@ -7794,7 +7834,7 @@
       </c>
       <c r="C66">
         <f ca="1"/>
-        <v>9.8376306402575539E-2</v>
+        <v>5.0962984438448836E-2</v>
       </c>
       <c r="D66">
         <f ca="1"/>
@@ -7802,7 +7842,7 @@
       </c>
       <c r="E66" s="12">
         <f ca="1"/>
-        <v>101.53112962454345</v>
+        <v>100.57289448843036</v>
       </c>
       <c r="F66" s="11">
         <f ca="1"/>
@@ -7814,7 +7854,7 @@
       </c>
       <c r="H66" s="11">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="I66" s="8">
         <f ca="1"/>
@@ -7822,7 +7862,7 @@
       </c>
       <c r="J66" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="K66">
         <f ca="1"/>
@@ -7839,7 +7879,7 @@
       </c>
       <c r="C67">
         <f ca="1"/>
-        <v>1.1881647246253332E-2</v>
+        <v>0.17682556520947107</v>
       </c>
       <c r="D67">
         <f ca="1"/>
@@ -7847,27 +7887,27 @@
       </c>
       <c r="E67" s="12">
         <f ca="1"/>
-        <v>99.781871192329277</v>
+        <v>103.12845004014551</v>
       </c>
       <c r="F67" s="11">
         <f ca="1"/>
-        <v>-99.781871192329277</v>
+        <v>0</v>
       </c>
       <c r="G67" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="11">
         <f ca="1"/>
-        <v>-95.242315587752614</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="I67" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" s="8">
         <f ca="1"/>
-        <v>4.5395556045766625</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="K67">
         <f ca="1"/>
@@ -7875,7 +7915,7 @@
       </c>
       <c r="L67">
         <f ca="1"/>
-        <v>0.21812880767072329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7884,7 +7924,7 @@
       </c>
       <c r="C68">
         <f ca="1"/>
-        <v>-5.271700813535192E-2</v>
+        <v>0.1934683338009609</v>
       </c>
       <c r="D68">
         <f ca="1"/>
@@ -7892,7 +7932,7 @@
       </c>
       <c r="E68" s="12">
         <f ca="1"/>
-        <v>98.493128503717003</v>
+        <v>103.46401310219969</v>
       </c>
       <c r="F68" s="11">
         <f ca="1"/>
@@ -7904,15 +7944,15 @@
       </c>
       <c r="H68" s="11">
         <f ca="1"/>
-        <v>-95.242315587752614</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="I68" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" s="8">
         <f ca="1"/>
-        <v>3.2508129159643886</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="K68">
         <f ca="1"/>
@@ -7920,7 +7960,7 @@
       </c>
       <c r="L68">
         <f ca="1"/>
-        <v>1.5068714962829972</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7929,7 +7969,7 @@
       </c>
       <c r="C69">
         <f ca="1"/>
-        <v>-9.2505313785698262E-2</v>
+        <v>0.11558058321986719</v>
       </c>
       <c r="D69">
         <f ca="1"/>
@@ -7937,7 +7977,7 @@
       </c>
       <c r="E69" s="12">
         <f ca="1"/>
-        <v>97.704647131119998</v>
+        <v>101.85663675807271</v>
       </c>
       <c r="F69" s="11">
         <f ca="1"/>
@@ -7949,15 +7989,15 @@
       </c>
       <c r="H69" s="11">
         <f ca="1"/>
-        <v>-95.242315587752614</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="I69" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="8">
         <f ca="1"/>
-        <v>2.4623315433673838</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="K69">
         <f ca="1"/>
@@ -7965,7 +8005,7 @@
       </c>
       <c r="L69">
         <f ca="1"/>
-        <v>2.295352868880002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -7974,7 +8014,7 @@
       </c>
       <c r="C70">
         <f ca="1"/>
-        <v>-9.130821155286814E-2</v>
+        <v>0.12049806278878292</v>
       </c>
       <c r="D70">
         <f ca="1"/>
@@ -7982,7 +8022,7 @@
       </c>
       <c r="E70" s="12">
         <f ca="1"/>
-        <v>97.720224491239065</v>
+        <v>101.94870539873261</v>
       </c>
       <c r="F70" s="11">
         <f ca="1"/>
@@ -7994,15 +8034,15 @@
       </c>
       <c r="H70" s="11">
         <f ca="1"/>
-        <v>-95.242315587752614</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="I70" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" s="8">
         <f ca="1"/>
-        <v>2.4779089034864512</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="K70">
         <f ca="1"/>
@@ -8010,7 +8050,7 @@
       </c>
       <c r="L70">
         <f ca="1"/>
-        <v>2.2797755087609346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -8019,7 +8059,7 @@
       </c>
       <c r="C71">
         <f ca="1"/>
-        <v>-8.6092587061043668E-2</v>
+        <v>0.12693845081326197</v>
       </c>
       <c r="D71">
         <f ca="1"/>
@@ -8027,7 +8067,7 @@
       </c>
       <c r="E71" s="12">
         <f ca="1"/>
-        <v>97.814386610182197</v>
+        <v>102.07194177113563</v>
       </c>
       <c r="F71" s="11">
         <f ca="1"/>
@@ -8039,15 +8079,15 @@
       </c>
       <c r="H71" s="11">
         <f ca="1"/>
-        <v>-95.242315587752614</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="I71" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="8">
         <f ca="1"/>
-        <v>2.5720710224295829</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="K71">
         <f ca="1"/>
@@ -8055,7 +8095,7 @@
       </c>
       <c r="L71">
         <f ca="1"/>
-        <v>2.185613389817803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -8064,7 +8104,7 @@
       </c>
       <c r="C72">
         <f ca="1"/>
-        <v>-0.12658255211244224</v>
+        <v>9.8366075880725504E-2</v>
       </c>
       <c r="D72">
         <f ca="1"/>
@@ -8072,15 +8112,15 @@
       </c>
       <c r="E72" s="12">
         <f ca="1"/>
-        <v>97.017723233977435</v>
+        <v>101.48219873345587</v>
       </c>
       <c r="F72" s="11">
         <f ca="1"/>
-        <v>95.242315587752614</v>
+        <v>-8.6508240375046483</v>
       </c>
       <c r="G72" s="8">
         <f ca="1"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="11">
         <f ca="1"/>
@@ -8088,19 +8128,19 @@
       </c>
       <c r="I72" s="8">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" s="8">
         <f ca="1"/>
-        <v>97.017723233977435</v>
+        <v>0</v>
       </c>
       <c r="K72">
         <f ca="1"/>
-        <v>1.7754076462248207</v>
+        <v>8.6508240375046483</v>
       </c>
       <c r="L72">
         <f ca="1"/>
-        <v>2.9822767660225651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.55000000000000004">
